--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F32503E2-CDAE-4028-BD31-6FDFD2D48A7C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{14310F47-017B-4E1F-8FA8-04B3883656C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="1800" windowWidth="25110" windowHeight="12510" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2443" uniqueCount="1806">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2448" uniqueCount="1808">
   <si>
     <t>标识</t>
   </si>
@@ -5863,6 +5863,14 @@
   </si>
   <si>
     <t>#FF80FF</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主城的数据</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>门派的数据</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -7121,7 +7129,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1763399868250,</v>
+        <v>nTimeStamp = 1771136290550,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>36</v>
@@ -20185,7 +20193,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCB9CF1-46D3-48CB-9969-7FCDF721073B}">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.15">
@@ -20263,12 +20271,15 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>1806</v>
+      </c>
       <c r="B2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W2" t="str">
         <f>IF(ISBLANK(B2)=FALSE,IF(ISBLANK(B1),"},["&amp;B2&amp;"]={","["&amp;B2&amp;"]={"),IF(AND(ISBLANK(B2),ISBLANK(D2),ISBLANK(C2),OR(ISBLANK(B1)=FALSE,ISBLANK(D1)=FALSE,ISBLANK(C1)=FALSE)),"},},}",IF(ISBLANK(C2),"","{dwID="&amp;C2&amp;","&amp;"nFrame="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"bAllLeave=true,","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&lt;&gt;"","tKungFu={"&amp;H2&amp;"},","")&amp;IF(I2&lt;&gt;"","szNote="""&amp;I2&amp;""",","")&amp;IF(J2&lt;&gt;"","col={"&amp;J2&amp;"},","")&amp;"[3]={"&amp;IF(K2&lt;&gt;"","tMark={"&amp;K2&amp;"},","")&amp;IF(L2&lt;&gt;"","szVoice="""&amp;L2&amp;""",","")&amp;IF(M2&gt;0,"bTeamChannel=true,","")&amp;IF(N2&gt;0,"bWhisperChannel=true,","")&amp;IF(O2&gt;0,"bCenterAlarm=true,","")&amp;IF(P2&gt;0,"bScreenHead=true,","")&amp;IF(Q2&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R2&lt;&gt;"","szVoice="""&amp;R2&amp;""",","")&amp;IF(S2&gt;0,"bTeamChannel=true,","")&amp;IF(T2&gt;0,"bWhisperChannel=true,","")&amp;IF(U2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V2&lt;&gt;"","aFocus={"&amp;V2&amp;"},","")&amp;IF(X2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X2:AAA2)&amp;"},","")&amp;"},")))</f>
-        <v>[-1]={</v>
+        <v>[-2]={</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -20291,136 +20302,124 @@
         <v>1653</v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W22" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="W3:W24" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>1807</v>
+      </c>
       <c r="B4">
-        <v>689</v>
+        <v>-21</v>
       </c>
       <c r="W4" t="str">
         <f t="shared" si="0"/>
-        <v>},[689]={</v>
+        <v>},[-21]={</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C5">
-        <v>128768</v>
+        <v>103373</v>
       </c>
       <c r="D5">
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1572</v>
+        <v>1652</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1573</v>
+        <v>1653</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128768,nFrame=47,szNote="出行大炮",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="C6">
-        <v>133268</v>
-      </c>
-      <c r="D6">
-        <v>47</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1654</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1708</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="V6" t="s">
-        <v>1707</v>
+      <c r="B6">
+        <v>689</v>
       </c>
       <c r="W6" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=133268,nFrame=47,szNote="小麻雀",col={100,255,100,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="飞行·传送",nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>},[689]={</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C7">
-        <v>128796</v>
+        <v>128768</v>
       </c>
       <c r="D7">
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="V7" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128796,nFrame=47,szNote="石像",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128768,nFrame=47,szNote="出行大炮",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C8">
-        <v>128554</v>
+        <v>133268</v>
       </c>
       <c r="D8">
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1716</v>
+        <v>1654</v>
       </c>
       <c r="J8" t="s">
-        <v>1432</v>
+        <v>1708</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1717</v>
+        <v>1707</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128554,nFrame=47,szNote="红方燃烽大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=133268,nFrame=47,szNote="小麻雀",col={100,255,100,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="飞行·传送",nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C9">
-        <v>128667</v>
+        <v>128796</v>
       </c>
       <c r="D9">
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1576</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1432</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
+        <v>1574</v>
       </c>
       <c r="V9" t="s">
-        <v>1718</v>
+        <v>1575</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128667,nFrame=47,szNote="红方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128796,nFrame=47,szNote="石像",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C10">
-        <v>128666</v>
+        <v>128554</v>
       </c>
       <c r="D10">
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>1577</v>
+        <v>1716</v>
       </c>
       <c r="J10" t="s">
         <v>1432</v>
@@ -20429,22 +20428,22 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>1726</v>
+        <v>1717</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128666,nFrame=47,szNote="红方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128554,nFrame=47,szNote="红方燃烽大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C11">
-        <v>128552</v>
+        <v>128667</v>
       </c>
       <c r="D11">
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="J11" t="s">
         <v>1432</v>
@@ -20453,127 +20452,127 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1727</v>
+        <v>1718</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128552,nFrame=47,szNote="红方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128667,nFrame=47,szNote="红方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C12">
-        <v>128557</v>
+        <v>128666</v>
       </c>
       <c r="D12">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1720</v>
+        <v>1577</v>
       </c>
       <c r="J12" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="P12">
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
-      </c>
-      <c r="X12" t="s">
-        <v>1579</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>1580</v>
+        <v>{dwID=128666,nFrame=47,szNote="红方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C13">
-        <v>128556</v>
+        <v>128552</v>
       </c>
       <c r="D13">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J13" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="P13">
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·混沌元晶·洞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
-      </c>
-      <c r="X13" t="s">
-        <v>1582</v>
+        <v>{dwID=128552,nFrame=47,szNote="红方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C14">
-        <v>128555</v>
+        <v>128557</v>
       </c>
       <c r="D14">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>1583</v>
+        <v>1720</v>
       </c>
       <c r="J14" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="P14">
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128555,nFrame=47,szNote="蓝方泽渊大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
+      </c>
+      <c r="X14" t="s">
+        <v>1579</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>1580</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C15">
-        <v>128669</v>
+        <v>128556</v>
       </c>
       <c r="D15">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="J15" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="P15">
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1730</v>
+        <v>1721</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128669,nFrame=47,szNote="蓝方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·混沌元晶·洞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
+      </c>
+      <c r="X15" t="s">
+        <v>1582</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="C16">
-        <v>128668</v>
+        <v>128555</v>
       </c>
       <c r="D16">
         <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="J16" t="s">
         <v>1432</v>
@@ -20582,22 +20581,22 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128668,nFrame=47,szNote="蓝方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128555,nFrame=47,szNote="蓝方泽渊大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="17" spans="3:25" x14ac:dyDescent="0.15">
       <c r="C17">
-        <v>128553</v>
+        <v>128669</v>
       </c>
       <c r="D17">
         <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="J17" t="s">
         <v>1432</v>
@@ -20606,79 +20605,70 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128553,nFrame=47,szNote="蓝方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128669,nFrame=47,szNote="蓝方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="18" spans="3:25" x14ac:dyDescent="0.15">
       <c r="C18">
-        <v>128559</v>
+        <v>128668</v>
       </c>
       <c r="D18">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="J18" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="P18">
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
-      </c>
-      <c r="X18" t="s">
-        <v>1588</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>1580</v>
+        <v>{dwID=128668,nFrame=47,szNote="蓝方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="19" spans="3:25" x14ac:dyDescent="0.15">
       <c r="C19">
-        <v>128558</v>
+        <v>128553</v>
       </c>
       <c r="D19">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="J19" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="P19">
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·混沌元晶·皓",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
-      </c>
-      <c r="X19" t="s">
-        <v>1772</v>
+        <v>{dwID=128553,nFrame=47,szNote="蓝方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="20" spans="3:25" x14ac:dyDescent="0.15">
       <c r="C20">
-        <v>128576</v>
+        <v>128559</v>
       </c>
       <c r="D20">
         <v>57</v>
       </c>
       <c r="I20" t="s">
-        <v>1719</v>
+        <v>1587</v>
       </c>
       <c r="J20" t="s">
         <v>1439</v>
@@ -20687,46 +20677,103 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
+        <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X20" t="s">
-        <v>1773</v>
+        <v>1588</v>
       </c>
       <c r="Y20" t="s">
-        <v>1742</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="21" spans="3:25" x14ac:dyDescent="0.15">
       <c r="C21">
-        <v>128941</v>
+        <v>128558</v>
       </c>
       <c r="D21">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I21" t="s">
-        <v>1590</v>
+        <v>1589</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1439</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128941,nFrame=52,szNote="准备刷新",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="准备刷新·30秒",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·混沌元晶·皓",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
+      </c>
+      <c r="X21" t="s">
+        <v>1772</v>
       </c>
     </row>
     <row r="22" spans="3:25" x14ac:dyDescent="0.15">
+      <c r="C22">
+        <v>128576</v>
+      </c>
+      <c r="D22">
+        <v>57</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1719</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1439</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>1735</v>
+      </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
+        <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
+      </c>
+      <c r="X22" t="s">
+        <v>1773</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.15">
+      <c r="C23">
+        <v>128941</v>
+      </c>
+      <c r="D23">
+        <v>52</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1590</v>
+      </c>
+      <c r="V23" t="s">
+        <v>1736</v>
+      </c>
+      <c r="W23" t="str">
+        <f t="shared" si="0"/>
+        <v>{dwID=128941,nFrame=52,szNote="准备刷新",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="准备刷新·30秒",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.15">
+      <c r="W24" t="str">
+        <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.15">
-      <c r="W23" t="str">
-        <f t="shared" ref="W23" si="1">IF(ISBLANK(B23)=FALSE,IF(ISBLANK(B22),"},["&amp;B23&amp;"]={","["&amp;B23&amp;"]={"),IF(AND(ISBLANK(B23),ISBLANK(D23),ISBLANK(C23),OR(ISBLANK(B22)=FALSE,ISBLANK(D22)=FALSE,ISBLANK(C22)=FALSE)),"},},}",IF(ISBLANK(C23),"","{dwID="&amp;C23&amp;","&amp;"nFrame="&amp;D23&amp;","&amp;IF(E23&gt;0,"nCount="&amp;E23&amp;",","")&amp;IF(F23&gt;0,"bAllLeave=true,","")&amp;IF(G23&lt;&gt;"","szName="""&amp;G23&amp;""",","")&amp;IF(H23&lt;&gt;"","tKungFu={"&amp;H23&amp;"},","")&amp;IF(I23&lt;&gt;"","szNote="""&amp;I23&amp;""",","")&amp;IF(J23&lt;&gt;"","col={"&amp;J23&amp;"},","")&amp;"[3]={"&amp;IF(K23&lt;&gt;"","tMark={"&amp;K23&amp;"},","")&amp;IF(L23&lt;&gt;"","szVoice="""&amp;L23&amp;""",","")&amp;IF(M23&gt;0,"bTeamChannel=true,","")&amp;IF(N23&gt;0,"bWhisperChannel=true,","")&amp;IF(O23&gt;0,"bCenterAlarm=true,","")&amp;IF(P23&gt;0,"bScreenHead=true,","")&amp;IF(Q23&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R23&lt;&gt;"","szVoice="""&amp;R23&amp;""",","")&amp;IF(S23&gt;0,"bTeamChannel=true,","")&amp;IF(T23&gt;0,"bWhisperChannel=true,","")&amp;IF(U23&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V23&lt;&gt;"","aFocus={"&amp;V23&amp;"},","")&amp;IF(X23&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X23:AAA23)&amp;"},","")&amp;"},")))</f>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.15">
+      <c r="W25" t="str">
+        <f t="shared" ref="W25" si="1">IF(ISBLANK(B25)=FALSE,IF(ISBLANK(B24),"},["&amp;B25&amp;"]={","["&amp;B25&amp;"]={"),IF(AND(ISBLANK(B25),ISBLANK(D25),ISBLANK(C25),OR(ISBLANK(B24)=FALSE,ISBLANK(D24)=FALSE,ISBLANK(C24)=FALSE)),"},},}",IF(ISBLANK(C25),"","{dwID="&amp;C25&amp;","&amp;"nFrame="&amp;D25&amp;","&amp;IF(E25&gt;0,"nCount="&amp;E25&amp;",","")&amp;IF(F25&gt;0,"bAllLeave=true,","")&amp;IF(G25&lt;&gt;"","szName="""&amp;G25&amp;""",","")&amp;IF(H25&lt;&gt;"","tKungFu={"&amp;H25&amp;"},","")&amp;IF(I25&lt;&gt;"","szNote="""&amp;I25&amp;""",","")&amp;IF(J25&lt;&gt;"","col={"&amp;J25&amp;"},","")&amp;"[3]={"&amp;IF(K25&lt;&gt;"","tMark={"&amp;K25&amp;"},","")&amp;IF(L25&lt;&gt;"","szVoice="""&amp;L25&amp;""",","")&amp;IF(M25&gt;0,"bTeamChannel=true,","")&amp;IF(N25&gt;0,"bWhisperChannel=true,","")&amp;IF(O25&gt;0,"bCenterAlarm=true,","")&amp;IF(P25&gt;0,"bScreenHead=true,","")&amp;IF(Q25&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R25&lt;&gt;"","szVoice="""&amp;R25&amp;""",","")&amp;IF(S25&gt;0,"bTeamChannel=true,","")&amp;IF(T25&gt;0,"bWhisperChannel=true,","")&amp;IF(U25&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V25&lt;&gt;"","aFocus={"&amp;V25&amp;"},","")&amp;IF(X25&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X25:AAA25)&amp;"},","")&amp;"},")))</f>
         <v/>
       </c>
     </row>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1810">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4599,6 +4599,9 @@
     <t>return {BUFF={</t>
   </si>
   <si>
+    <t>九素云峰</t>
+  </si>
+  <si>
     <t>隐匿草丛</t>
   </si>
   <si>
@@ -5058,9 +5061,6 @@
     <t>{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},</t>
   </si>
   <si>
-    <t>九素云峰</t>
-  </si>
-  <si>
     <t>我方第(%d-)次鼓舞士气成功！</t>
   </si>
   <si>
@@ -5199,7 +5199,7 @@
     <t>我方·获得·麒麟珠</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
   </si>
   <si>
     <t>敌方拾取麒麟珠\n</t>
@@ -5208,7 +5208,7 @@
     <t>敌方·获得·麒麟珠</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
   </si>
   <si>
     <t>红方成功开启全局迷雾视野\n</t>
@@ -5275,6 +5275,24 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
+  </si>
+  <si>
+    <t>练习赛已经报名过了\n</t>
+  </si>
+  <si>
+    <t>武林争霸赛·练习赛·已经报名</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},</t>
+  </si>
+  <si>
+    <t>练习赛匹配超时\n</t>
+  </si>
+  <si>
+    <t>武林争霸赛·练习赛·匹配超时</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},</t>
   </si>
   <si>
     <t>5,战斗开始·野区资源·已刷新</t>
@@ -5473,7 +5491,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5605,13 +5623,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6111,7 +6122,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6120,10 +6131,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6135,7 +6146,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6147,7 +6158,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6159,7 +6170,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6171,7 +6182,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6183,7 +6194,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6693,7 +6704,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1779281392000,</v>
+        <v>nTimeStamp = 1780242087000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8619,7 +8630,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1742</v>
+        <v>1748</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8632,13 +8643,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1743</v>
+        <v>1749</v>
       </c>
       <c r="B2" t="s">
-        <v>1744</v>
+        <v>1750</v>
       </c>
       <c r="C2" t="s">
-        <v>1745</v>
+        <v>1751</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8647,13 +8658,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1746</v>
+        <v>1752</v>
       </c>
       <c r="B3" t="s">
-        <v>1747</v>
+        <v>1753</v>
       </c>
       <c r="C3" t="s">
-        <v>1748</v>
+        <v>1754</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8662,13 +8673,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1749</v>
+        <v>1755</v>
       </c>
       <c r="B4" t="s">
-        <v>1750</v>
+        <v>1756</v>
       </c>
       <c r="C4" t="s">
-        <v>1751</v>
+        <v>1757</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8677,13 +8688,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="B5" t="s">
-        <v>1753</v>
+        <v>1759</v>
       </c>
       <c r="C5" t="s">
-        <v>1754</v>
+        <v>1760</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8692,7 +8703,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1755</v>
+        <v>1761</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8701,13 +8712,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1756</v>
+        <v>1762</v>
       </c>
       <c r="B7" t="s">
-        <v>1757</v>
+        <v>1763</v>
       </c>
       <c r="C7" t="s">
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8716,13 +8727,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1759</v>
+        <v>1765</v>
       </c>
       <c r="B8" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="C8" t="s">
-        <v>1744</v>
+        <v>1750</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8731,13 +8742,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1761</v>
+        <v>1767</v>
       </c>
       <c r="B9" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
       <c r="C9" t="s">
-        <v>1747</v>
+        <v>1753</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8746,13 +8757,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1763</v>
+        <v>1769</v>
       </c>
       <c r="B10" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="C10" t="s">
-        <v>1750</v>
+        <v>1756</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8761,13 +8772,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1765</v>
+        <v>1771</v>
       </c>
       <c r="B11" t="s">
-        <v>1766</v>
+        <v>1772</v>
       </c>
       <c r="C11" t="s">
-        <v>1753</v>
+        <v>1759</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8776,7 +8787,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1767</v>
+        <v>1773</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8785,10 +8796,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1768</v>
+        <v>1774</v>
       </c>
       <c r="C13" t="s">
-        <v>1757</v>
+        <v>1763</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8797,10 +8808,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1769</v>
+        <v>1775</v>
       </c>
       <c r="C14" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8809,10 +8820,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1770</v>
+        <v>1776</v>
       </c>
       <c r="C15" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8821,10 +8832,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1771</v>
+        <v>1777</v>
       </c>
       <c r="C16" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8833,10 +8844,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C17" t="s">
         <v>1772</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1766</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8845,7 +8856,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1773</v>
+        <v>1779</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8854,7 +8865,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8863,7 +8874,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1775</v>
+        <v>1781</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8872,7 +8883,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1776</v>
+        <v>1782</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8881,7 +8892,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1777</v>
+        <v>1783</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8914,7 +8925,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8931,7 +8942,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1779</v>
+        <v>1785</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -8945,7 +8956,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1779</v>
+        <v>1785</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -8959,7 +8970,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1779</v>
+        <v>1785</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -8979,7 +8990,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -8998,7 +9009,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9009,7 +9020,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9020,7 +9031,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9036,7 +9047,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9051,7 +9062,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9062,7 +9073,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9073,7 +9084,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9089,7 +9100,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9104,7 +9115,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1782</v>
+        <v>1788</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9115,7 +9126,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1782</v>
+        <v>1788</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9126,7 +9137,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1782</v>
+        <v>1788</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9142,7 +9153,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9157,7 +9168,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9168,7 +9179,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9179,7 +9190,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9195,7 +9206,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9210,7 +9221,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1784</v>
+        <v>1790</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9221,7 +9232,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1784</v>
+        <v>1790</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9232,7 +9243,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1784</v>
+        <v>1790</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9248,7 +9259,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9263,7 +9274,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9274,7 +9285,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9285,7 +9296,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9301,7 +9312,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9316,7 +9327,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9327,7 +9338,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9338,7 +9349,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9354,7 +9365,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9369,7 +9380,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1787</v>
+        <v>1793</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9380,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1787</v>
+        <v>1793</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9391,7 +9402,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1787</v>
+        <v>1793</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9407,7 +9418,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9422,7 +9433,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9433,7 +9444,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9444,7 +9455,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9460,7 +9471,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9475,7 +9486,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9486,7 +9497,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9497,7 +9508,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9513,7 +9524,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9528,7 +9539,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1790</v>
+        <v>1796</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9539,7 +9550,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1790</v>
+        <v>1796</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9550,7 +9561,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1790</v>
+        <v>1796</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9566,7 +9577,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9581,7 +9592,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1791</v>
+        <v>1797</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9592,7 +9603,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1791</v>
+        <v>1797</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9603,7 +9614,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1791</v>
+        <v>1797</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9619,7 +9630,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9634,7 +9645,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9645,7 +9656,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9656,7 +9667,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9672,7 +9683,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9687,7 +9698,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1793</v>
+        <v>1799</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9698,7 +9709,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1793</v>
+        <v>1799</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9709,7 +9720,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1793</v>
+        <v>1799</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9725,7 +9736,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9740,7 +9751,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1794</v>
+        <v>1800</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9751,7 +9762,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1794</v>
+        <v>1800</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9762,7 +9773,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1794</v>
+        <v>1800</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9778,7 +9789,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9793,7 +9804,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1795</v>
+        <v>1801</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9804,7 +9815,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1795</v>
+        <v>1801</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9815,7 +9826,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1795</v>
+        <v>1801</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9831,7 +9842,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9846,7 +9857,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9857,7 +9868,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9868,7 +9879,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9884,7 +9895,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9899,7 +9910,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9910,7 +9921,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9921,7 +9932,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9937,7 +9948,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -9952,7 +9963,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -9963,7 +9974,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -9974,7 +9985,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -9990,7 +10001,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10005,7 +10016,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10016,7 +10027,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10027,7 +10038,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10043,7 +10054,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10058,7 +10069,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10069,7 +10080,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10080,7 +10091,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10096,7 +10107,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10111,7 +10122,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1801</v>
+        <v>1807</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10122,7 +10133,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1801</v>
+        <v>1807</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10133,7 +10144,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1801</v>
+        <v>1807</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10149,7 +10160,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10164,7 +10175,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1802</v>
+        <v>1808</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10175,7 +10186,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1802</v>
+        <v>1808</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10186,7 +10197,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1802</v>
+        <v>1808</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10202,7 +10213,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10216,7 +10227,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10226,7 +10237,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10236,7 +10247,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10252,7 +10263,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10272,7 +10283,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10292,7 +10303,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10312,7 +10323,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10332,7 +10343,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10352,7 +10363,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10372,7 +10383,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10392,7 +10403,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10412,7 +10423,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10432,7 +10443,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10452,7 +10463,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10472,7 +10483,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10492,7 +10503,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10512,7 +10523,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10532,7 +10543,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10552,7 +10563,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10572,7 +10583,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10592,7 +10603,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10612,7 +10623,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10632,7 +10643,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10652,7 +10663,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10672,7 +10683,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10692,7 +10703,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10712,7 +10723,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10732,7 +10743,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10752,7 +10763,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10772,7 +10783,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10792,7 +10803,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10812,7 +10823,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10832,7 +10843,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10852,7 +10863,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10872,7 +10883,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10892,7 +10903,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10912,7 +10923,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10932,7 +10943,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19089,6 +19100,9 @@
       </c>
     </row>
     <row r="2" spans="1:44">
+      <c r="A2" t="s">
+        <v>1516</v>
+      </c>
       <c r="B2">
         <v>689</v>
       </c>
@@ -19105,7 +19119,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="L3" t="s">
         <v>668</v>
@@ -19117,16 +19131,16 @@
         <v>1</v>
       </c>
       <c r="AH3" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="AI3">
         <v>3</v>
       </c>
       <c r="AJ3" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="AK3" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="AL3">
         <v>255</v>
@@ -19153,16 +19167,16 @@
         <v>3293</v>
       </c>
       <c r="G4" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="L4" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="U4">
         <v>1</v>
@@ -19183,10 +19197,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="K5" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="L5" t="s">
         <v>604</v>
@@ -19198,10 +19212,10 @@
         <v>40</v>
       </c>
       <c r="AJ5" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="AK5" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="AL5">
         <v>255</v>
@@ -19367,13 +19381,16 @@
         <v>1514</v>
       </c>
       <c r="AQ1" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="AR1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:45">
+      <c r="A2" t="s">
+        <v>1516</v>
+      </c>
       <c r="B2">
         <v>689</v>
       </c>
@@ -19393,10 +19410,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="L3" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="AQ3" t="str">
         <f t="shared" si="0"/>
@@ -19411,7 +19428,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="L4" t="s">
         <v>668</v>
@@ -19432,7 +19449,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="L5" t="s">
         <v>658</v>
@@ -19444,16 +19461,16 @@
         <v>1</v>
       </c>
       <c r="AH5" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="AI5">
         <v>15</v>
       </c>
       <c r="AJ5" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="AK5" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="AL5">
         <v>255</v>
@@ -19469,7 +19486,7 @@
         <v>{dwID=10260,nLevel=1,szNote="江逐月天",col={255,153,204,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="懵",nPriority=15,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,bAttention=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=7060,nFrame=8,nTime="3,敌方·江逐月天·{$sender};8,江逐月天·调息暂停",szName="敌方·江逐月天·{$sender}",nRefresh=8,key="江逐月天",},},},</v>
       </c>
       <c r="AR5" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="6" spans="1:45">
@@ -19480,16 +19497,16 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="L6" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="U6">
         <v>1</v>
@@ -19499,10 +19516,10 @@
         <v>{dwID=29176,nLevel=1,szName="封轻功",nScrutinyType=1,szNote="立足不稳",col={255,127,255,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=3442,nFrame=2,nTime=1800,szName="进入塔内·封轻功·不可骑乘",key="立足不稳",},{nClass=2,nIcon=3442,nFrame=5,nTime=2,szName="已出塔·可骑乘·可轻功",key="立足不稳",},},},</v>
       </c>
       <c r="AR6" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="AS6" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="7" spans="1:45">
@@ -19513,16 +19530,16 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="L7" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -19531,16 +19548,16 @@
         <v>10</v>
       </c>
       <c r="AE7" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="AI7">
         <v>37</v>
       </c>
       <c r="AJ7" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="AK7" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="AL7">
         <v>255</v>
@@ -19553,7 +19570,7 @@
         <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{nStackNum=10,szStackOp="&gt;",nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
       </c>
       <c r="AR7" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="8" spans="1:45">
@@ -19616,49 +19633,52 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="N1" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="O1" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="P1" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="Q1" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="R1" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="S1" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="T1" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="U1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="V1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="W1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="X1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:25">
+      <c r="A2" t="s">
+        <v>1516</v>
+      </c>
       <c r="B2">
         <v>689</v>
       </c>
@@ -19675,14 +19695,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="X3" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19693,14 +19713,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19711,14 +19731,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="X5" t="str">
         <f t="shared" ref="X5" si="1">IF(ISBLANK(B5)=FALSE,IF(ISBLANK(B4),"},["&amp;B5&amp;"]={","["&amp;B5&amp;"]={"),IF(AND(ISBLANK(B5),ISBLANK(C5),ISBLANK(D5),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C5),"","{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nIcon="&amp;E5&amp;",","")&amp;IF(F5&lt;&gt;"","szName="""&amp;F5&amp;""",","")&amp;IF(G5&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H5&gt;0,"nScrutinyType="&amp;H5&amp;",","")&amp;IF(I5&lt;&gt;"","tKungFu={"&amp;I5&amp;"},","")&amp;IF(J5&lt;&gt;"","szNote="""&amp;J5&amp;""",","")&amp;IF(K5&lt;&gt;"","col={"&amp;K5&amp;"},","")&amp;"[9]={"&amp;IF(L5&lt;&gt;"","tMark={"&amp;L5&amp;"},","")&amp;IF(M5&lt;&gt;"","szVoice="""&amp;M5&amp;""",","")&amp;IF(N5&gt;0,"bTeamChannel=true,","")&amp;IF(O5&gt;0,"bWhisperChannel=true,","")&amp;IF(P5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q5&lt;&gt;"","tMark={"&amp;Q5&amp;"},","")&amp;IF(R5&lt;&gt;"","szVoice="""&amp;R5&amp;""",","")&amp;IF(S5&gt;0,"bTeamChannel=true,","")&amp;IF(T5&gt;0,"bWhisperChannel=true,","")&amp;IF(U5&gt;0,"bCenterAlarm=true,","")&amp;IF(V5&gt;0,"bScreenHead=true,","")&amp;IF(W5&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y5:AAC5)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19729,16 +19749,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K6" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="V6">
         <v>1</v>
@@ -19784,10 +19804,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19802,43 +19822,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="L1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="M1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="N1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="O1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="P1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="Q1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="R1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="S1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="T1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="U1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -19846,7 +19866,7 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -19864,7 +19884,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -19873,7 +19893,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W24" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -19882,7 +19902,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -19900,7 +19920,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -19909,7 +19929,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -19917,6 +19937,9 @@
       </c>
     </row>
     <row r="6" spans="1:25">
+      <c r="A6" t="s">
+        <v>1516</v>
+      </c>
       <c r="B6">
         <v>689</v>
       </c>
@@ -19933,10 +19956,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="V7" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -19951,16 +19974,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="J8" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -19975,10 +19998,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="V9" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -19993,7 +20016,7 @@
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="J10" t="s">
         <v>582</v>
@@ -20002,7 +20025,7 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20017,7 +20040,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20026,7 +20049,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20041,7 +20064,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20050,7 +20073,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20065,7 +20088,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20074,7 +20097,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20089,7 +20112,7 @@
         <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="J14" t="s">
         <v>640</v>
@@ -20098,17 +20121,17 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X14" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="Y14" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -20119,7 +20142,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20128,14 +20151,14 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·混沌元晶·洞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20146,7 +20169,7 @@
         <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="J16" t="s">
         <v>582</v>
@@ -20155,7 +20178,7 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
@@ -20170,7 +20193,7 @@
         <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="J17" t="s">
         <v>582</v>
@@ -20179,7 +20202,7 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20194,7 +20217,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20203,7 +20226,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20218,7 +20241,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20227,7 +20250,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20242,7 +20265,7 @@
         <v>57</v>
       </c>
       <c r="I20" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="J20" t="s">
         <v>640</v>
@@ -20251,17 +20274,17 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X20" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="Y20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="21" spans="3:25">
@@ -20272,7 +20295,7 @@
         <v>57</v>
       </c>
       <c r="I21" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="J21" t="s">
         <v>640</v>
@@ -20281,14 +20304,14 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·混沌元晶·皓",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X21" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="22" spans="3:25">
@@ -20299,7 +20322,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20308,17 +20331,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="Y22" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20329,10 +20352,10 @@
         <v>52</v>
       </c>
       <c r="I23" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="V23" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
@@ -20375,10 +20398,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20393,40 +20416,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="K1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="L1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="O1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="P1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="Q1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="R1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="S1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20446,7 +20469,7 @@
         <v>8852</v>
       </c>
       <c r="H3" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20455,7 +20478,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20467,7 +20490,7 @@
         <v>8851</v>
       </c>
       <c r="H4" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20476,7 +20499,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20488,7 +20511,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20497,7 +20520,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20509,7 +20532,7 @@
         <v>8849</v>
       </c>
       <c r="H6" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20518,7 +20541,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20530,7 +20553,7 @@
         <v>8848</v>
       </c>
       <c r="H7" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20539,7 +20562,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20547,6 +20570,9 @@
       </c>
     </row>
     <row r="8" spans="1:22">
+      <c r="A8" t="s">
+        <v>1516</v>
+      </c>
       <c r="B8">
         <v>689</v>
       </c>
@@ -20560,7 +20586,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20572,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20619,7 +20645,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20628,31 +20654,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="I1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="J1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="K1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="L1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="M1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="N1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="O1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20660,7 +20686,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20672,25 +20698,25 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D3" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="E3" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O14" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="已报名·武林争霸赛",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="已报名·武林争霸赛",key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:16">
       <c r="A4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B4">
         <v>-2</v>
@@ -20702,13 +20728,13 @@
     </row>
     <row r="5" customFormat="1" spans="1:16">
       <c r="C5" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D5" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="E5" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -20721,12 +20747,12 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P5" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B6">
         <v>-21</v>
@@ -20738,13 +20764,13 @@
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D7" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="E7" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20757,12 +20783,12 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>1669</v>
+        <v>1516</v>
       </c>
       <c r="B8">
         <v>689</v>
@@ -20774,7 +20800,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="C9" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D9" t="s">
         <v>1670</v>
@@ -20822,7 +20848,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D12" t="s">
         <v>1677</v>
@@ -20843,7 +20869,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D13" t="s">
         <v>1680</v>
@@ -20878,7 +20904,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="27.125" customWidth="1"/>
@@ -20892,7 +20918,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -20901,28 +20927,28 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="G1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="I1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="J1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="K1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="L1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="M1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="N1" t="s">
         <v>1682</v>
@@ -20932,6 +20958,9 @@
       </c>
     </row>
     <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>1516</v>
+      </c>
       <c r="B2">
         <v>689</v>
       </c>
@@ -20945,7 +20974,7 @@
         <v>1683</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N25" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="N3:N31" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O3" t="s">
@@ -21123,7 +21152,7 @@
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
         <v>1716</v>
@@ -21141,7 +21170,7 @@
       </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
         <v>1719</v>
@@ -21177,7 +21206,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="17" spans="3:15">
+    <row r="17" spans="1:15">
       <c r="C17" t="s">
         <v>1725</v>
       </c>
@@ -21189,7 +21218,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="18" spans="3:15">
+    <row r="18" spans="1:15">
       <c r="C18" t="s">
         <v>1727</v>
       </c>
@@ -21201,7 +21230,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="19" spans="3:15">
+    <row r="19" spans="1:15">
       <c r="C19" t="s">
         <v>1729</v>
       </c>
@@ -21213,7 +21242,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="20" spans="3:15">
+    <row r="20" spans="1:15">
       <c r="C20" t="s">
         <v>1731</v>
       </c>
@@ -21225,7 +21254,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="21" spans="3:15">
+    <row r="21" spans="1:15">
       <c r="C21" t="s">
         <v>1733</v>
       </c>
@@ -21243,7 +21272,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="22" spans="3:15">
+    <row r="22" spans="1:15">
       <c r="C22" t="s">
         <v>1736</v>
       </c>
@@ -21255,7 +21284,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="23" spans="3:15">
+    <row r="23" spans="1:15">
       <c r="C23" t="s">
         <v>1738</v>
       </c>
@@ -21267,7 +21296,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="24" spans="3:15">
+    <row r="24" spans="1:15">
       <c r="C24" t="s">
         <v>1740</v>
       </c>
@@ -21279,8 +21308,104 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="3:15">
+    <row r="25" customFormat="1" spans="1:15">
+      <c r="A25" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B25">
+        <v>-2</v>
+      </c>
       <c r="N25" t="str">
+        <f t="shared" si="0"/>
+        <v>},[-2]={</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:15">
+      <c r="C26" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1743</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O26" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="C27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1746</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O27" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B28">
+        <v>-21</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="0"/>
+        <v>},[-21]={</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:15">
+      <c r="C29" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1743</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O29" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:15">
+      <c r="C30" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1746</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O30" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="N31" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="1811">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4629,7 +4629,7 @@
     <t>骑御</t>
   </si>
   <si>
-    <t>#FFFF00FF</t>
+    <t>#FFFF00DD</t>
   </si>
   <si>
     <t>#FFFF00</t>
@@ -4689,6 +4689,9 @@
     <t>#FF80FF</t>
   </si>
   <si>
+    <t>{nPriority=38,col="#FF80FFAA",nColAlpha=170,},</t>
+  </si>
+  <si>
     <t>{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},</t>
   </si>
   <si>
@@ -4749,7 +4752,7 @@
     <t>{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},</t>
   </si>
   <si>
-    <t>进战移动马</t>
+    <t>进战移动上马</t>
   </si>
   <si>
     <t>战斗移动骑乘</t>
@@ -4836,13 +4839,13 @@
     <t>红方燃烽大旗</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>红方三塔</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>红方二塔</t>
@@ -4854,7 +4857,7 @@
     <t>红方一塔</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>红方·古猿</t>
@@ -4872,7 +4875,7 @@
     <t>红方·混沌元晶·洞</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="红方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·混沌元晶·洞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},</t>
@@ -4881,25 +4884,25 @@
     <t>蓝方泽渊大旗</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>蓝方三塔</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>蓝方二塔</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>蓝方一塔</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>蓝方·古猿</t>
@@ -4914,7 +4917,7 @@
     <t>蓝方·混沌元晶·皓</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·混沌元晶·皓",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},</t>
@@ -5148,7 +5151,7 @@
     <t>战斗开始。\n</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2401,帮会联赛·即将结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},</t>
+    <t>{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},</t>
@@ -6704,7 +6707,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1780242087000,</v>
+        <v>nTimeStamp = 1781614933000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8630,7 +8633,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8643,13 +8646,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B2" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="C2" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8658,13 +8661,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B3" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C3" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8673,13 +8676,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B4" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C4" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8688,13 +8691,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B5" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="C5" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8703,7 +8706,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8712,13 +8715,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B7" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="C7" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8727,13 +8730,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B8" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C8" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8742,13 +8745,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B9" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="C9" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8757,13 +8760,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B10" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C10" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8772,13 +8775,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B11" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C11" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8787,7 +8790,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8796,10 +8799,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="C13" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8808,10 +8811,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C14" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8820,10 +8823,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="C15" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8832,10 +8835,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C16" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8844,10 +8847,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C17" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8856,7 +8859,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8865,7 +8868,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8874,7 +8877,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8883,7 +8886,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8892,7 +8895,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8925,7 +8928,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8942,7 +8945,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -8956,7 +8959,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -8970,7 +8973,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -8990,7 +8993,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9009,7 +9012,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9020,7 +9023,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9031,7 +9034,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9047,7 +9050,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9062,7 +9065,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9073,7 +9076,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9084,7 +9087,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9100,7 +9103,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9115,7 +9118,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9126,7 +9129,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9137,7 +9140,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9153,7 +9156,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9168,7 +9171,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9179,7 +9182,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9190,7 +9193,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9206,7 +9209,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9221,7 +9224,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9232,7 +9235,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9243,7 +9246,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9259,7 +9262,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9274,7 +9277,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9285,7 +9288,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9296,7 +9299,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9312,7 +9315,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9327,7 +9330,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9338,7 +9341,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9349,7 +9352,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9365,7 +9368,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9380,7 +9383,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9391,7 +9394,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9402,7 +9405,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9418,7 +9421,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9433,7 +9436,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9444,7 +9447,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9455,7 +9458,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9471,7 +9474,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9486,7 +9489,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9497,7 +9500,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9508,7 +9511,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9524,7 +9527,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9539,7 +9542,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9550,7 +9553,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9561,7 +9564,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9577,7 +9580,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9592,7 +9595,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9603,7 +9606,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9614,7 +9617,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9630,7 +9633,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9645,7 +9648,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9656,7 +9659,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9667,7 +9670,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9683,7 +9686,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9698,7 +9701,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9709,7 +9712,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9720,7 +9723,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9736,7 +9739,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9751,7 +9754,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9762,7 +9765,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9773,7 +9776,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9789,7 +9792,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9804,7 +9807,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9815,7 +9818,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9826,7 +9829,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9842,7 +9845,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9857,7 +9860,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9868,7 +9871,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9879,7 +9882,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9895,7 +9898,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9910,7 +9913,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9921,7 +9924,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9932,7 +9935,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9948,7 +9951,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -9963,7 +9966,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -9974,7 +9977,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -9985,7 +9988,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10001,7 +10004,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10016,7 +10019,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10027,7 +10030,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10038,7 +10041,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10054,7 +10057,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10069,7 +10072,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10080,7 +10083,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10091,7 +10094,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10107,7 +10110,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10122,7 +10125,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10133,7 +10136,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10144,7 +10147,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10160,7 +10163,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10175,7 +10178,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10186,7 +10189,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10197,7 +10200,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10213,7 +10216,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10227,7 +10230,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10237,7 +10240,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10247,7 +10250,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10263,7 +10266,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10283,7 +10286,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10303,7 +10306,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10323,7 +10326,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10343,7 +10346,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10363,7 +10366,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10383,7 +10386,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10403,7 +10406,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10423,7 +10426,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10443,7 +10446,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10463,7 +10466,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10483,7 +10486,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10503,7 +10506,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10523,7 +10526,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10543,7 +10546,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10563,7 +10566,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10583,7 +10586,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10603,7 +10606,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10623,7 +10626,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10643,7 +10646,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10663,7 +10666,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10683,7 +10686,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10703,7 +10706,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10723,7 +10726,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10743,7 +10746,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10763,7 +10766,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10783,7 +10786,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10803,7 +10806,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10823,7 +10826,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10843,7 +10846,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10863,7 +10866,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10883,7 +10886,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10903,7 +10906,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10923,7 +10926,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10943,7 +10946,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19130,6 +19133,9 @@
       <c r="U3">
         <v>1</v>
       </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
       <c r="AH3" t="s">
         <v>1518</v>
       </c>
@@ -19153,7 +19159,7 @@
       </c>
       <c r="AQ3" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29097,nLevel=1,szNote="隐匿草丛",col={255,204,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="藏",nPriority=3,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <v>{dwID=29097,nLevel=1,szNote="隐匿草丛",col={255,204,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="藏",nPriority=3,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -19208,6 +19214,9 @@
       <c r="S5">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
       <c r="AI5">
         <v>40</v>
       </c>
@@ -19218,14 +19227,14 @@
         <v>1527</v>
       </c>
       <c r="AL5">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="AO5">
         <v>1</v>
       </c>
       <c r="AQ5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00DD",colScreenHead="#FFFF00",nColAlpha=221,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="6" spans="1:44">
@@ -19252,6 +19261,9 @@
   <sheetPr/>
   <dimension ref="A1:AS9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="11" max="11" width="14.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:45">
       <c r="A1" t="s">
@@ -19460,6 +19472,9 @@
       <c r="U5">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
       <c r="AH5" t="s">
         <v>1533</v>
       </c>
@@ -19483,7 +19498,7 @@
       </c>
       <c r="AQ5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=10260,nLevel=1,szNote="江逐月天",col={255,153,204,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="懵",nPriority=15,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,bAttention=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=7060,nFrame=8,nTime="3,敌方·江逐月天·{$sender};8,江逐月天·调息暂停",szName="敌方·江逐月天·{$sender}",nRefresh=8,key="江逐月天",},},},</v>
+        <v>{dwID=10260,nLevel=1,szNote="江逐月天",col={255,153,204,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="懵",nPriority=15,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,bAttention=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=7060,nFrame=8,nTime="3,敌方·江逐月天·{$sender};8,江逐月天·调息暂停",szName="敌方·江逐月天·{$sender}",nRefresh=8,key="江逐月天",},},},</v>
       </c>
       <c r="AR5" t="s">
         <v>1536</v>
@@ -19544,6 +19559,9 @@
       <c r="U7">
         <v>1</v>
       </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
       <c r="AD7">
         <v>10</v>
       </c>
@@ -19565,12 +19583,15 @@
       <c r="AO7">
         <v>1</v>
       </c>
+      <c r="AP7" t="s">
+        <v>1546</v>
+      </c>
       <c r="AQ7" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{nStackNum=10,szStackOp="&gt;",nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
+        <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nStackNum=10,szStackOp="&gt;",nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,bScreenHead=true,},{nPriority=38,col="#FF80FFAA",nColAlpha=170,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
       </c>
       <c r="AR7" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="8" spans="1:45">
@@ -19633,43 +19654,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="M1" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="N1" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="O1" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="P1" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="Q1" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="R1" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="S1" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="T1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="U1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="V1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="W1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="X1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
@@ -19695,14 +19716,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="X3" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19713,14 +19734,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19731,14 +19752,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="X5" t="str">
-        <f t="shared" ref="X5" si="1">IF(ISBLANK(B5)=FALSE,IF(ISBLANK(B4),"},["&amp;B5&amp;"]={","["&amp;B5&amp;"]={"),IF(AND(ISBLANK(B5),ISBLANK(C5),ISBLANK(D5),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C5),"","{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nIcon="&amp;E5&amp;",","")&amp;IF(F5&lt;&gt;"","szName="""&amp;F5&amp;""",","")&amp;IF(G5&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H5&gt;0,"nScrutinyType="&amp;H5&amp;",","")&amp;IF(I5&lt;&gt;"","tKungFu={"&amp;I5&amp;"},","")&amp;IF(J5&lt;&gt;"","szNote="""&amp;J5&amp;""",","")&amp;IF(K5&lt;&gt;"","col={"&amp;K5&amp;"},","")&amp;"[9]={"&amp;IF(L5&lt;&gt;"","tMark={"&amp;L5&amp;"},","")&amp;IF(M5&lt;&gt;"","szVoice="""&amp;M5&amp;""",","")&amp;IF(N5&gt;0,"bTeamChannel=true,","")&amp;IF(O5&gt;0,"bWhisperChannel=true,","")&amp;IF(P5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q5&lt;&gt;"","tMark={"&amp;Q5&amp;"},","")&amp;IF(R5&lt;&gt;"","szVoice="""&amp;R5&amp;""",","")&amp;IF(S5&gt;0,"bTeamChannel=true,","")&amp;IF(T5&gt;0,"bWhisperChannel=true,","")&amp;IF(U5&gt;0,"bCenterAlarm=true,","")&amp;IF(V5&gt;0,"bScreenHead=true,","")&amp;IF(W5&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y5:AAC5)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19749,23 +19770,23 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="K6" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="V6">
         <v>1</v>
       </c>
       <c r="X6" t="str">
-        <f>IF(ISBLANK(B6)=FALSE,IF(ISBLANK(B4),"},["&amp;B6&amp;"]={","["&amp;B6&amp;"]={"),IF(AND(ISBLANK(B6),ISBLANK(C6),ISBLANK(D6),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C6),"","{dwID="&amp;C6&amp;","&amp;"nLevel="&amp;D6&amp;","&amp;IF(E6&gt;0,"nIcon="&amp;E6&amp;",","")&amp;IF(F6&lt;&gt;"","szName="""&amp;F6&amp;""",","")&amp;IF(G6&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H6&gt;0,"nScrutinyType="&amp;H6&amp;",","")&amp;IF(I6&lt;&gt;"","tKungFu={"&amp;I6&amp;"},","")&amp;IF(J6&lt;&gt;"","szNote="""&amp;J6&amp;""",","")&amp;IF(K6&lt;&gt;"","col={"&amp;K6&amp;"},","")&amp;"[9]={"&amp;IF(L6&lt;&gt;"","tMark={"&amp;L6&amp;"},","")&amp;IF(M6&lt;&gt;"","szVoice="""&amp;M6&amp;""",","")&amp;IF(N6&gt;0,"bTeamChannel=true,","")&amp;IF(O6&gt;0,"bWhisperChannel=true,","")&amp;IF(P6&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q6&lt;&gt;"","tMark={"&amp;Q6&amp;"},","")&amp;IF(R6&lt;&gt;"","szVoice="""&amp;R6&amp;""",","")&amp;IF(S6&gt;0,"bTeamChannel=true,","")&amp;IF(T6&gt;0,"bWhisperChannel=true,","")&amp;IF(U6&gt;0,"bCenterAlarm=true,","")&amp;IF(V6&gt;0,"bScreenHead=true,","")&amp;IF(W6&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y6&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y6:AAC6)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=38096,nLevel=1,szName="进战移动马",nScrutinyType=2,szNote="战斗移动骑乘",col={255,255,100,},[9]={},[8]={bScreenHead=true,},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=38096,nLevel=1,szName="进战移动上马",nScrutinyType=2,szNote="战斗移动骑乘",col={255,255,100,},[9]={},[8]={bScreenHead=true,},},</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -19804,10 +19825,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19822,43 +19843,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="L1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="M1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="N1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="O1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="P1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="Q1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="R1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="S1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="T1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="U1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -19866,7 +19887,7 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -19884,7 +19905,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -19893,7 +19914,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W24" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -19902,7 +19923,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -19920,7 +19941,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -19929,7 +19950,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -19956,10 +19977,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="V7" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -19974,16 +19995,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="J8" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -19998,10 +20019,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="V9" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20016,7 +20037,7 @@
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="J10" t="s">
         <v>582</v>
@@ -20025,11 +20046,11 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128554,nFrame=47,szNote="红方燃烽大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128554,nFrame=47,szNote="红方燃烽大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -20040,7 +20061,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20049,11 +20070,11 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128667,nFrame=47,szNote="红方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128667,nFrame=47,szNote="红方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -20064,7 +20085,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20073,7 +20094,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20088,7 +20109,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20097,11 +20118,11 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128552,nFrame=47,szNote="红方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128552,nFrame=47,szNote="红方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -20112,7 +20133,7 @@
         <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J14" t="s">
         <v>640</v>
@@ -20121,17 +20142,17 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X14" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="Y14" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -20142,7 +20163,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20151,14 +20172,14 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·混沌元晶·洞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
+        <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20169,7 +20190,7 @@
         <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="J16" t="s">
         <v>582</v>
@@ -20178,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128555,nFrame=47,szNote="蓝方泽渊大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128555,nFrame=47,szNote="蓝方泽渊大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="17" spans="3:25">
@@ -20193,7 +20214,7 @@
         <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J17" t="s">
         <v>582</v>
@@ -20202,11 +20223,11 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128669,nFrame=47,szNote="蓝方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128669,nFrame=47,szNote="蓝方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="18" spans="3:25">
@@ -20217,7 +20238,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20226,11 +20247,11 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128668,nFrame=47,szNote="蓝方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128668,nFrame=47,szNote="蓝方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="19" spans="3:25">
@@ -20241,7 +20262,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20250,11 +20271,11 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128553,nFrame=47,szNote="蓝方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128553,nFrame=47,szNote="蓝方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="20" spans="3:25">
@@ -20265,7 +20286,7 @@
         <v>57</v>
       </c>
       <c r="I20" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="J20" t="s">
         <v>640</v>
@@ -20274,17 +20295,17 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X20" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="Y20" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="21" spans="3:25">
@@ -20295,7 +20316,7 @@
         <v>57</v>
       </c>
       <c r="I21" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="J21" t="s">
         <v>640</v>
@@ -20304,14 +20325,14 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·混沌元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·混沌元晶·皓",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X21" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="22" spans="3:25">
@@ -20322,7 +20343,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20331,17 +20352,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="Y22" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20352,10 +20373,10 @@
         <v>52</v>
       </c>
       <c r="I23" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="V23" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
@@ -20398,10 +20419,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20416,40 +20437,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="K1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="N1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="O1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="P1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="Q1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="R1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="S1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20469,7 +20490,7 @@
         <v>8852</v>
       </c>
       <c r="H3" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20478,7 +20499,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20490,7 +20511,7 @@
         <v>8851</v>
       </c>
       <c r="H4" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20499,7 +20520,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20511,7 +20532,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20520,7 +20541,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20532,7 +20553,7 @@
         <v>8849</v>
       </c>
       <c r="H6" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20541,7 +20562,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20553,7 +20574,7 @@
         <v>8848</v>
       </c>
       <c r="H7" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20562,7 +20583,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20586,7 +20607,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20598,7 +20619,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20645,7 +20666,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20654,31 +20675,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="I1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="J1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="K1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="L1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="M1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="N1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="O1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20686,7 +20707,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20698,25 +20719,25 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D3" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="E3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O14" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="已报名·武林争霸赛",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="已报名·武林争霸赛",key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:16">
       <c r="A4" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B4">
         <v>-2</v>
@@ -20728,13 +20749,13 @@
     </row>
     <row r="5" customFormat="1" spans="1:16">
       <c r="C5" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D5" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E5" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -20747,12 +20768,12 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P5" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B6">
         <v>-21</v>
@@ -20764,13 +20785,13 @@
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D7" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E7" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20783,7 +20804,7 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -20800,13 +20821,13 @@
     </row>
     <row r="9" spans="1:16">
       <c r="C9" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D9" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="E9" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20819,42 +20840,42 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P9" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="D10" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="O10" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="D11" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P11" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D12" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E12" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -20864,18 +20885,18 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D13" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="E13" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -20885,7 +20906,7 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -20918,7 +20939,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -20927,31 +20948,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="I1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="J1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="K1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="L1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="M1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="N1" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -20971,88 +20992,88 @@
     </row>
     <row r="3" spans="1:18">
       <c r="C3" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N31" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="P3" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="Q3" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="R3" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="C4" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="P4" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="Q4" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="R4" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="C5" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="P5" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="Q5" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="R5" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="C6" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2401,帮会联赛·即将结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
+        <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="P6" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="C7" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="D7" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="E7" t="s">
         <v>582</v>
@@ -21067,10 +21088,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="C8" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D8" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="E8" t="s">
         <v>582</v>
@@ -21086,24 +21107,24 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="C9" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="C10" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -21113,39 +21134,39 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="C11" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="C12" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="C13" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="D13" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21155,15 +21176,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="C14" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D14" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21173,27 +21194,27 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="C15" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="C16" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D16" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21203,63 +21224,63 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="C17" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="C18" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="C19" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="C21" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="D21" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -21269,48 +21290,48 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="C22" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O22" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="C23" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="C24" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:15">
       <c r="A25" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B25">
         <v>-2</v>
@@ -21322,10 +21343,10 @@
     </row>
     <row r="26" customFormat="1" spans="1:15">
       <c r="C26" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D26" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -21335,15 +21356,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="C27" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="D27" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -21353,12 +21374,12 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O27" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B28">
         <v>-21</v>
@@ -21370,10 +21391,10 @@
     </row>
     <row r="29" customFormat="1" spans="1:15">
       <c r="C29" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D29" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21383,15 +21404,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:15">
       <c r="C30" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="D30" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -21401,7 +21422,7 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="31" spans="1:15">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="1811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="1821">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4836,34 +4836,40 @@
     <t>{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
+    <t>红方箭塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},</t>
+  </si>
+  <si>
+    <t>红方三塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>红方二塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="红方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>红方一塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
     <t>红方燃烽大旗</t>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
-    <t>红方三塔</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="红方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>红方二塔</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="红方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>红方一塔</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
     <t>红方·古猿</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},</t>
@@ -4881,34 +4887,40 @@
     <t>{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},</t>
   </si>
   <si>
+    <t>蓝方箭塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="==",nValue=100,},},</t>
+  </si>
+  <si>
+    <t>蓝方三塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>蓝方二塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>蓝方一塔</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
     <t>蓝方泽渊大旗</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>蓝方三塔</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>蓝方二塔</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>蓝方一塔</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>蓝方·古猿</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},</t>
@@ -4917,7 +4929,7 @@
     <t>蓝方·混沌元晶·皓</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},</t>
@@ -4926,7 +4938,7 @@
     <t>九渊麒麟</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},</t>
@@ -5046,13 +5058,22 @@
     <t>%</t>
   </si>
   <si>
+    <t>【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！</t>
+  </si>
+  <si>
+    <t>武林争霸赛·正式开启</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",key="武林争霸赛",},</t>
+  </si>
+  <si>
     <t>[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！</t>
   </si>
   <si>
-    <t>已报名·武林争霸赛</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="已报名·武林争霸赛",key="武林争霸赛",},</t>
+    <t>武林争霸赛·已经报名</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",key="武林争霸赛",},</t>
   </si>
   <si>
     <t>^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！</t>
@@ -5296,6 +5317,15 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},</t>
+  </si>
+  <si>
+    <t>未到报名时间，或请重新打开界面!\n</t>
+  </si>
+  <si>
+    <t>武林争霸赛·未到报名时间</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},</t>
   </si>
   <si>
     <t>5,战斗开始·野区资源·已刷新</t>
@@ -6707,7 +6737,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1781614933000,</v>
+        <v>nTimeStamp = 1781700467000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8633,7 +8663,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8646,13 +8676,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1750</v>
+        <v>1760</v>
       </c>
       <c r="B2" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="C2" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8661,13 +8691,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1753</v>
+        <v>1763</v>
       </c>
       <c r="B3" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="C3" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8676,13 +8706,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1756</v>
+        <v>1766</v>
       </c>
       <c r="B4" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="C4" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8691,13 +8721,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="B5" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="C5" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8706,7 +8736,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8715,13 +8745,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="B7" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="C7" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8730,13 +8760,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="B8" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="C8" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8745,13 +8775,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
       <c r="B9" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="C9" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8760,13 +8790,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
       <c r="B10" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="C10" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8775,13 +8805,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
       <c r="B11" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="C11" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8790,7 +8820,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8799,10 +8829,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="C13" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8811,10 +8841,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="C14" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8823,10 +8853,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1777</v>
+        <v>1787</v>
       </c>
       <c r="C15" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8835,10 +8865,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="C16" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8847,10 +8877,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="C17" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8859,7 +8889,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8868,7 +8898,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8877,7 +8907,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8886,7 +8916,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8895,7 +8925,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8928,7 +8958,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8945,7 +8975,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -8959,7 +8989,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -8973,7 +9003,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -8993,7 +9023,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9012,7 +9042,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9023,7 +9053,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9034,7 +9064,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9050,7 +9080,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9065,7 +9095,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9076,7 +9106,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9087,7 +9117,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9103,7 +9133,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9118,7 +9148,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9129,7 +9159,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9140,7 +9170,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9156,7 +9186,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9171,7 +9201,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9182,7 +9212,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9193,7 +9223,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9209,7 +9239,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9224,7 +9254,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9235,7 +9265,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9246,7 +9276,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9262,7 +9292,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9277,7 +9307,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9288,7 +9318,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9299,7 +9329,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9315,7 +9345,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9330,7 +9360,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9341,7 +9371,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9352,7 +9382,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9368,7 +9398,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9383,7 +9413,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9394,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9405,7 +9435,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9421,7 +9451,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9436,7 +9466,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9447,7 +9477,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9458,7 +9488,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9474,7 +9504,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9489,7 +9519,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9500,7 +9530,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9511,7 +9541,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9527,7 +9557,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9542,7 +9572,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9553,7 +9583,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9564,7 +9594,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9580,7 +9610,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9595,7 +9625,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9606,7 +9636,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9617,7 +9647,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9633,7 +9663,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9648,7 +9678,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9659,7 +9689,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9670,7 +9700,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9686,7 +9716,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9701,7 +9731,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9712,7 +9742,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9723,7 +9753,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9739,7 +9769,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9754,7 +9784,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9765,7 +9795,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9776,7 +9806,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9792,7 +9822,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9807,7 +9837,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9818,7 +9848,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9829,7 +9859,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9845,7 +9875,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9860,7 +9890,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9871,7 +9901,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9882,7 +9912,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9898,7 +9928,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9913,7 +9943,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9924,7 +9954,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9935,7 +9965,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9951,7 +9981,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -9966,7 +9996,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -9977,7 +10007,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -9988,7 +10018,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10004,7 +10034,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10019,7 +10049,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10030,7 +10060,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10041,7 +10071,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10057,7 +10087,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10072,7 +10102,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10083,7 +10113,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10094,7 +10124,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10110,7 +10140,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10125,7 +10155,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10136,7 +10166,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10147,7 +10177,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10163,7 +10193,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10178,7 +10208,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10189,7 +10219,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10200,7 +10230,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10216,7 +10246,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10230,7 +10260,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10240,7 +10270,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10250,7 +10280,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10266,7 +10296,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10286,7 +10316,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10306,7 +10336,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10326,7 +10356,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10346,7 +10376,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10366,7 +10396,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10386,7 +10416,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10406,7 +10436,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10426,7 +10456,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10446,7 +10476,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10466,7 +10496,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10486,7 +10516,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10506,7 +10536,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10526,7 +10556,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10546,7 +10576,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10566,7 +10596,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10586,7 +10616,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10606,7 +10636,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10626,7 +10656,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10646,7 +10676,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10666,7 +10696,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10686,7 +10716,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10706,7 +10736,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10726,7 +10756,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10746,7 +10776,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10766,7 +10796,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10786,7 +10816,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10806,7 +10836,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10826,7 +10856,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10846,7 +10876,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10866,7 +10896,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10886,7 +10916,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10906,7 +10936,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10926,7 +10956,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10946,7 +10976,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19805,7 +19835,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="9" max="9" width="21.375" customWidth="1"/>
@@ -19917,7 +19947,7 @@
         <v>1586</v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W24" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -20031,26 +20061,20 @@
     </row>
     <row r="10" spans="1:25">
       <c r="C10">
-        <v>128554</v>
+        <v>128733</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s">
         <v>1595</v>
       </c>
-      <c r="J10" t="s">
-        <v>582</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
       <c r="V10" t="s">
         <v>1596</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128554,nFrame=47,szNote="红方燃烽大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128733,nFrame=52,szNote="红方箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -20098,7 +20122,7 @@
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128666,nFrame=47,szNote="红方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128666,nFrame=47,szNote="红方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -20122,21 +20146,21 @@
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128552,nFrame=47,szNote="红方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128552,nFrame=47,szNote="红方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="C14">
-        <v>128557</v>
+        <v>128554</v>
       </c>
       <c r="D14">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I14" t="s">
         <v>1603</v>
       </c>
       <c r="J14" t="s">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -20146,24 +20170,18 @@
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
-      </c>
-      <c r="X14" t="s">
-        <v>1605</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>1606</v>
+        <v>{dwID=128554,nFrame=47,szNote="红方燃烽大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="C15">
-        <v>128556</v>
+        <v>128557</v>
       </c>
       <c r="D15">
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20172,67 +20190,67 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
+        <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1609</v>
+        <v>1607</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>1608</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="C16">
-        <v>128555</v>
+        <v>128556</v>
       </c>
       <c r="D16">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="J16" t="s">
-        <v>582</v>
+        <v>640</v>
       </c>
       <c r="P16">
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128555,nFrame=47,szNote="蓝方泽渊大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="17" spans="3:25">
+        <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
+      </c>
+      <c r="X16" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="3:25">
       <c r="C17">
-        <v>128669</v>
+        <v>128732</v>
       </c>
       <c r="D17">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I17" t="s">
         <v>1612</v>
       </c>
-      <c r="J17" t="s">
-        <v>582</v>
-      </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
       <c r="V17" t="s">
         <v>1613</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128669,nFrame=47,szNote="蓝方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128732,nFrame=52,szNote="蓝方箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="18" spans="3:25">
       <c r="C18">
-        <v>128668</v>
+        <v>128669</v>
       </c>
       <c r="D18">
         <v>47</v>
@@ -20251,12 +20269,12 @@
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128668,nFrame=47,szNote="蓝方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128669,nFrame=47,szNote="蓝方三塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·三塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·三塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="19" spans="3:25">
       <c r="C19">
-        <v>128553</v>
+        <v>128668</v>
       </c>
       <c r="D19">
         <v>47</v>
@@ -20275,21 +20293,21 @@
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128553,nFrame=47,szNote="蓝方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128668,nFrame=47,szNote="蓝方二塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·二塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·二塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="20" spans="3:25">
       <c r="C20">
-        <v>128559</v>
+        <v>128553</v>
       </c>
       <c r="D20">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I20" t="s">
         <v>1618</v>
       </c>
       <c r="J20" t="s">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -20299,51 +20317,42 @@
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
-      </c>
-      <c r="X20" t="s">
-        <v>1620</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>1606</v>
+        <v>{dwID=128553,nFrame=47,szNote="蓝方一塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·一塔·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·一塔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="21" spans="3:25">
       <c r="C21">
-        <v>128558</v>
+        <v>128555</v>
       </c>
       <c r="D21">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="J21" t="s">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="P21">
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
-      </c>
-      <c r="X21" t="s">
-        <v>1623</v>
+        <v>{dwID=128555,nFrame=47,szNote="蓝方泽渊大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·大旗·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·大旗",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="22" spans="3:25">
       <c r="C22">
-        <v>128576</v>
+        <v>128559</v>
       </c>
       <c r="D22">
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20352,46 +20361,103 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
+        <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="Y22" t="s">
-        <v>1627</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="23" spans="3:25">
       <c r="C23">
-        <v>128941</v>
+        <v>128558</v>
       </c>
       <c r="D23">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1628</v>
+        <v>1625</v>
+      </c>
+      <c r="J23" t="s">
+        <v>640</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128941,nFrame=52,szNote="准备刷新",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="准备刷新·30秒",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
+      </c>
+      <c r="X23" t="s">
+        <v>1627</v>
       </c>
     </row>
     <row r="24" spans="3:25">
+      <c r="C24">
+        <v>128576</v>
+      </c>
+      <c r="D24">
+        <v>57</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1628</v>
+      </c>
+      <c r="J24" t="s">
+        <v>640</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>1629</v>
+      </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
+        <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
+      </c>
+      <c r="X24" t="s">
+        <v>1630</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25">
+      <c r="C25">
+        <v>128941</v>
+      </c>
+      <c r="D25">
+        <v>52</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1632</v>
+      </c>
+      <c r="V25" t="s">
+        <v>1633</v>
+      </c>
+      <c r="W25" t="str">
+        <f t="shared" si="0"/>
+        <v>{dwID=128941,nFrame=52,szNote="准备刷新",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="准备刷新·30秒",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25">
+      <c r="W26" t="str">
+        <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
     </row>
-    <row r="25" spans="3:25">
-      <c r="W25" t="str">
-        <f t="shared" ref="W25" si="1">IF(ISBLANK(B25)=FALSE,IF(ISBLANK(B24),"},["&amp;B25&amp;"]={","["&amp;B25&amp;"]={"),IF(AND(ISBLANK(B25),ISBLANK(D25),ISBLANK(C25),OR(ISBLANK(B24)=FALSE,ISBLANK(D24)=FALSE,ISBLANK(C24)=FALSE)),"},},}",IF(ISBLANK(C25),"","{dwID="&amp;C25&amp;","&amp;"nFrame="&amp;D25&amp;","&amp;IF(E25&gt;0,"nCount="&amp;E25&amp;",","")&amp;IF(F25&gt;0,"bAllLeave=true,","")&amp;IF(G25&lt;&gt;"","szName="""&amp;G25&amp;""",","")&amp;IF(H25&lt;&gt;"","tKungFu={"&amp;H25&amp;"},","")&amp;IF(I25&lt;&gt;"","szNote="""&amp;I25&amp;""",","")&amp;IF(J25&lt;&gt;"","col={"&amp;J25&amp;"},","")&amp;"[3]={"&amp;IF(K25&lt;&gt;"","tMark={"&amp;K25&amp;"},","")&amp;IF(L25&lt;&gt;"","szVoice="""&amp;L25&amp;""",","")&amp;IF(M25&gt;0,"bTeamChannel=true,","")&amp;IF(N25&gt;0,"bWhisperChannel=true,","")&amp;IF(O25&gt;0,"bCenterAlarm=true,","")&amp;IF(P25&gt;0,"bScreenHead=true,","")&amp;IF(Q25&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R25&lt;&gt;"","szVoice="""&amp;R25&amp;""",","")&amp;IF(S25&gt;0,"bTeamChannel=true,","")&amp;IF(T25&gt;0,"bWhisperChannel=true,","")&amp;IF(U25&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V25&lt;&gt;"","aFocus={"&amp;V25&amp;"},","")&amp;IF(X25&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X25:AAA25)&amp;"},","")&amp;"},")))</f>
+    <row r="27" spans="3:25">
+      <c r="W27" t="str">
+        <f t="shared" ref="W27" si="1">IF(ISBLANK(B27)=FALSE,IF(ISBLANK(B26),"},["&amp;B27&amp;"]={","["&amp;B27&amp;"]={"),IF(AND(ISBLANK(B27),ISBLANK(D27),ISBLANK(C27),OR(ISBLANK(B26)=FALSE,ISBLANK(D26)=FALSE,ISBLANK(C26)=FALSE)),"},},}",IF(ISBLANK(C27),"","{dwID="&amp;C27&amp;","&amp;"nFrame="&amp;D27&amp;","&amp;IF(E27&gt;0,"nCount="&amp;E27&amp;",","")&amp;IF(F27&gt;0,"bAllLeave=true,","")&amp;IF(G27&lt;&gt;"","szName="""&amp;G27&amp;""",","")&amp;IF(H27&lt;&gt;"","tKungFu={"&amp;H27&amp;"},","")&amp;IF(I27&lt;&gt;"","szNote="""&amp;I27&amp;""",","")&amp;IF(J27&lt;&gt;"","col={"&amp;J27&amp;"},","")&amp;"[3]={"&amp;IF(K27&lt;&gt;"","tMark={"&amp;K27&amp;"},","")&amp;IF(L27&lt;&gt;"","szVoice="""&amp;L27&amp;""",","")&amp;IF(M27&gt;0,"bTeamChannel=true,","")&amp;IF(N27&gt;0,"bWhisperChannel=true,","")&amp;IF(O27&gt;0,"bCenterAlarm=true,","")&amp;IF(P27&gt;0,"bScreenHead=true,","")&amp;IF(Q27&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R27&lt;&gt;"","szVoice="""&amp;R27&amp;""",","")&amp;IF(S27&gt;0,"bTeamChannel=true,","")&amp;IF(T27&gt;0,"bWhisperChannel=true,","")&amp;IF(U27&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V27&lt;&gt;"","aFocus={"&amp;V27&amp;"},","")&amp;IF(X27&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X27:AAA27)&amp;"},","")&amp;"},")))</f>
         <v/>
       </c>
     </row>
@@ -20437,40 +20503,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="K1" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="L1" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="M1" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="N1" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="O1" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="P1" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="Q1" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="R1" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="S1" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20490,7 +20556,7 @@
         <v>8852</v>
       </c>
       <c r="H3" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20499,7 +20565,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20511,7 +20577,7 @@
         <v>8851</v>
       </c>
       <c r="H4" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20520,7 +20586,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20532,7 +20598,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20541,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20553,7 +20619,7 @@
         <v>8849</v>
       </c>
       <c r="H6" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20562,7 +20628,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20574,7 +20640,7 @@
         <v>8848</v>
       </c>
       <c r="H7" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20583,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20607,7 +20673,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20619,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20648,7 +20714,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="58.875" customWidth="1"/>
@@ -20666,7 +20732,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20675,31 +20741,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="H1" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="I1" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="J1" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="K1" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="L1" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="M1" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="N1" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="O1" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20707,7 +20773,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20719,198 +20785,216 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="D3" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="E3" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="O3" t="str">
-        <f t="shared" ref="O3:O14" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="已报名·武林争霸赛",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="已报名·武林争霸赛",key="武林争霸赛",},},},</v>
+        <f t="shared" ref="O3:O15" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1667</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:16">
-      <c r="A4" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B4">
-        <v>-2</v>
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="C4" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1673</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
-        <v>},[-2]={</v>
+        <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1674</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
-      <c r="C5" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1669</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+      <c r="A5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B5">
+        <v>-2</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
-      </c>
-      <c r="P5" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B6">
-        <v>-21</v>
+        <v>},[-2]={</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:16">
+      <c r="C6" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1676</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" si="0"/>
-        <v>},[-21]={</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:16">
-      <c r="C7" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1669</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
+        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
+      </c>
+      <c r="P6" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B7">
+        <v>-21</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
-      </c>
-      <c r="P7" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>1516</v>
-      </c>
-      <c r="B8">
-        <v>689</v>
+        <v>},[-21]={</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:16">
+      <c r="C8" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1676</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" si="0"/>
-        <v>},[689]={</v>
+        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1677</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="C9" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1672</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
+      <c r="A9" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B9">
+        <v>689</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
-      </c>
-      <c r="P9" t="s">
-        <v>1673</v>
+        <v>},[689]={</v>
       </c>
     </row>
     <row r="10" spans="1:16">
+      <c r="C10" t="s">
+        <v>1668</v>
+      </c>
       <c r="D10" t="s">
-        <v>1674</v>
+        <v>1678</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="O10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
+        <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="D11" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
+        <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P11" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="C12" t="s">
-        <v>1664</v>
-      </c>
       <c r="D12" t="s">
-        <v>1678</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1679</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
+        <v>1683</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="D13" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="E13" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="0"/>
+        <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+      </c>
+      <c r="P13" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="C14" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
-      <c r="P13" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="O14" t="str">
+      <c r="P14" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="O15" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
@@ -20925,7 +21009,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="27.125" customWidth="1"/>
@@ -20939,7 +21023,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -20948,31 +21032,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="G1" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="H1" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="I1" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="J1" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="K1" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="L1" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="M1" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="N1" t="s">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -20992,88 +21076,88 @@
     </row>
     <row r="3" spans="1:18">
       <c r="C3" t="s">
-        <v>1684</v>
+        <v>1691</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N31" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="N3:N33" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1685</v>
+        <v>1692</v>
       </c>
       <c r="P3" t="s">
-        <v>1686</v>
+        <v>1693</v>
       </c>
       <c r="Q3" t="s">
-        <v>1687</v>
+        <v>1694</v>
       </c>
       <c r="R3" t="s">
-        <v>1688</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="C4" t="s">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="P4" t="s">
-        <v>1691</v>
+        <v>1698</v>
       </c>
       <c r="Q4" t="s">
-        <v>1692</v>
+        <v>1699</v>
       </c>
       <c r="R4" t="s">
-        <v>1693</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="C5" t="s">
-        <v>1694</v>
+        <v>1701</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1695</v>
+        <v>1702</v>
       </c>
       <c r="P5" t="s">
-        <v>1696</v>
+        <v>1703</v>
       </c>
       <c r="Q5" t="s">
-        <v>1697</v>
+        <v>1704</v>
       </c>
       <c r="R5" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="C6" t="s">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1700</v>
+        <v>1707</v>
       </c>
       <c r="P6" t="s">
-        <v>1701</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="C7" t="s">
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="D7" t="s">
-        <v>1703</v>
+        <v>1710</v>
       </c>
       <c r="E7" t="s">
         <v>582</v>
@@ -21088,10 +21172,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="C8" t="s">
-        <v>1704</v>
+        <v>1711</v>
       </c>
       <c r="D8" t="s">
-        <v>1705</v>
+        <v>1712</v>
       </c>
       <c r="E8" t="s">
         <v>582</v>
@@ -21107,24 +21191,24 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1706</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="C9" t="s">
-        <v>1707</v>
+        <v>1714</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1708</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="C10" t="s">
-        <v>1709</v>
+        <v>1716</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -21134,39 +21218,39 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1710</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="C11" t="s">
-        <v>1711</v>
+        <v>1718</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1712</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="C12" t="s">
-        <v>1713</v>
+        <v>1720</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1714</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="C13" t="s">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="D13" t="s">
-        <v>1716</v>
+        <v>1723</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21176,15 +21260,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1717</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="C14" t="s">
-        <v>1718</v>
+        <v>1725</v>
       </c>
       <c r="D14" t="s">
-        <v>1719</v>
+        <v>1726</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21194,27 +21278,27 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1720</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="C15" t="s">
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1722</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="C16" t="s">
-        <v>1723</v>
+        <v>1730</v>
       </c>
       <c r="D16" t="s">
-        <v>1724</v>
+        <v>1731</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21224,63 +21308,63 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1725</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="C17" t="s">
-        <v>1726</v>
+        <v>1733</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1727</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="C18" t="s">
-        <v>1728</v>
+        <v>1735</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1729</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="C19" t="s">
-        <v>1730</v>
+        <v>1737</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1731</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" t="s">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1733</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="C21" t="s">
-        <v>1734</v>
+        <v>1741</v>
       </c>
       <c r="D21" t="s">
-        <v>1735</v>
+        <v>1742</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -21290,43 +21374,43 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1736</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="C22" t="s">
-        <v>1737</v>
+        <v>1744</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O22" t="s">
-        <v>1738</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="C23" t="s">
-        <v>1739</v>
+        <v>1746</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1740</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="C24" t="s">
-        <v>1741</v>
+        <v>1748</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1742</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:15">
@@ -21343,10 +21427,10 @@
     </row>
     <row r="26" customFormat="1" spans="1:15">
       <c r="C26" t="s">
-        <v>1743</v>
+        <v>1750</v>
       </c>
       <c r="D26" t="s">
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -21356,15 +21440,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1745</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="C27" t="s">
-        <v>1746</v>
+        <v>1753</v>
       </c>
       <c r="D27" t="s">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -21374,59 +21458,89 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O27" t="s">
-        <v>1748</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B28">
-        <v>-21</v>
+      <c r="C28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1757</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
-        <v>},[-21]={</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:15">
-      <c r="C29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
+        <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O28" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B29">
+        <v>-21</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
-      </c>
-      <c r="O29" t="s">
-        <v>1745</v>
+        <v>},[-21]={</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:15">
       <c r="C30" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="D30" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="K30">
         <v>1</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
+        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O30" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:15">
+      <c r="C31" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="0"/>
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
-      <c r="O30" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="N31" t="str">
+      <c r="O31" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:15">
+      <c r="C32" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1757</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O32" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="33" spans="14:14">
+      <c r="N33" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -5064,7 +5064,7 @@
     <t>武林争霸赛·正式开启</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",key="武林争霸赛",},</t>
+    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},</t>
   </si>
   <si>
     <t>[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！</t>
@@ -5073,7 +5073,7 @@
     <t>武林争霸赛·已经报名</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",key="武林争霸赛",},</t>
+    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},</t>
   </si>
   <si>
     <t>^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！</t>
@@ -6737,7 +6737,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1781700467000,</v>
+        <v>nTimeStamp = 1782304041000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -20795,7 +20795,7 @@
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O15" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",key="武林争霸赛",},},},</v>
+        <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
         <v>1671</v>
@@ -20813,7 +20813,7 @@
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",key="武林争霸赛",},},},</v>
+        <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
         <v>1674</v>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="1821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="1819">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4680,16 +4680,10 @@
     <t>经脉受损</t>
   </si>
   <si>
-    <t>&gt;</t>
-  </si>
-  <si>
     <t>#FF80FFFF</t>
   </si>
   <si>
     <t>#FF80FF</t>
-  </si>
-  <si>
-    <t>{nPriority=38,col="#FF80FFAA",nColAlpha=170,},</t>
   </si>
   <si>
     <t>{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},</t>
@@ -6737,7 +6731,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1782304041000,</v>
+        <v>nTimeStamp = 1784310889000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8663,7 +8657,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8676,13 +8670,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C2" t="s">
         <v>1760</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1762</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8691,13 +8685,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C3" t="s">
         <v>1763</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1764</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1765</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8706,13 +8700,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C4" t="s">
         <v>1766</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1767</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1768</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8721,13 +8715,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C5" t="s">
         <v>1769</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1770</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1771</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8736,7 +8730,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8745,13 +8739,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C7" t="s">
         <v>1773</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1775</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8760,13 +8754,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="B8" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="C8" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8775,13 +8769,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="B9" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="C9" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8790,13 +8784,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B10" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="C10" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8805,13 +8799,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="B11" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="C11" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8820,7 +8814,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8829,10 +8823,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="C13" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8841,10 +8835,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="C14" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8853,10 +8847,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="C15" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8865,10 +8859,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="C16" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8877,10 +8871,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="C17" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8889,7 +8883,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8898,7 +8892,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8907,7 +8901,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8916,7 +8910,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8925,7 +8919,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8958,7 +8952,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8975,7 +8969,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -8989,7 +8983,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9003,7 +8997,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9023,7 +9017,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9042,7 +9036,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9053,7 +9047,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9064,7 +9058,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9080,7 +9074,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9095,7 +9089,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9106,7 +9100,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9117,7 +9111,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9133,7 +9127,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9148,7 +9142,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9159,7 +9153,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9170,7 +9164,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9186,7 +9180,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9201,7 +9195,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9212,7 +9206,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9223,7 +9217,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9239,7 +9233,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9254,7 +9248,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9265,7 +9259,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9276,7 +9270,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9292,7 +9286,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9307,7 +9301,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9318,7 +9312,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9329,7 +9323,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9345,7 +9339,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9360,7 +9354,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9371,7 +9365,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9382,7 +9376,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9398,7 +9392,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9413,7 +9407,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9424,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9435,7 +9429,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9451,7 +9445,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9466,7 +9460,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9477,7 +9471,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9488,7 +9482,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9504,7 +9498,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9519,7 +9513,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9530,7 +9524,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9541,7 +9535,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9557,7 +9551,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9572,7 +9566,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9583,7 +9577,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9594,7 +9588,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9610,7 +9604,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9625,7 +9619,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9636,7 +9630,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9647,7 +9641,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9663,7 +9657,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9678,7 +9672,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9689,7 +9683,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9700,7 +9694,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9716,7 +9710,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9731,7 +9725,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9742,7 +9736,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9753,7 +9747,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9769,7 +9763,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9784,7 +9778,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9795,7 +9789,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9806,7 +9800,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9822,7 +9816,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9837,7 +9831,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9848,7 +9842,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9859,7 +9853,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9875,7 +9869,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9890,7 +9884,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9901,7 +9895,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9912,7 +9906,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9928,7 +9922,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9943,7 +9937,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9954,7 +9948,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9965,7 +9959,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9981,7 +9975,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -9996,7 +9990,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10007,7 +10001,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10018,7 +10012,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10034,7 +10028,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10049,7 +10043,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10060,7 +10054,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10071,7 +10065,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10087,7 +10081,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10102,7 +10096,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10113,7 +10107,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10124,7 +10118,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10140,7 +10134,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10155,7 +10149,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10166,7 +10160,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10177,7 +10171,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10193,7 +10187,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10208,7 +10202,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10219,7 +10213,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10230,7 +10224,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10246,7 +10240,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10260,7 +10254,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10270,7 +10264,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10280,7 +10274,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10296,7 +10290,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10316,7 +10310,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10336,7 +10330,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10356,7 +10350,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10376,7 +10370,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10396,7 +10390,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10416,7 +10410,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10436,7 +10430,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10456,7 +10450,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10476,7 +10470,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10496,7 +10490,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10516,7 +10510,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10536,7 +10530,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10556,7 +10550,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10576,7 +10570,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10596,7 +10590,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10616,7 +10610,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10636,7 +10630,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10656,7 +10650,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10676,7 +10670,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10696,7 +10690,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10716,7 +10710,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10736,7 +10730,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10756,7 +10750,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10776,7 +10770,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10796,7 +10790,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10816,7 +10810,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10836,7 +10830,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10856,7 +10850,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10876,7 +10870,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10896,7 +10890,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10916,7 +10910,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10936,7 +10930,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10956,7 +10950,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10976,7 +10970,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19437,7 +19431,7 @@
         <v>689</v>
       </c>
       <c r="AQ2" t="str">
-        <f t="shared" ref="AQ2:AQ9" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
+        <f>IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
         <v>[689]={</v>
       </c>
     </row>
@@ -19458,7 +19452,7 @@
         <v>1530</v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AQ3:AQ8" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·15尺伤害距离",col={128,238,255,},[1]={},[2]={},},</v>
       </c>
     </row>
@@ -19592,36 +19586,24 @@
       <c r="W7">
         <v>1</v>
       </c>
-      <c r="AD7">
-        <v>10</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>1543</v>
-      </c>
       <c r="AI7">
         <v>37</v>
       </c>
       <c r="AJ7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AK7" t="s">
         <v>1544</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>1545</v>
       </c>
       <c r="AL7">
         <v>255</v>
       </c>
-      <c r="AO7">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>1546</v>
-      </c>
       <c r="AQ7" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nStackNum=10,szStackOp="&gt;",nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,bScreenHead=true,},{nPriority=38,col="#FF80FFAA",nColAlpha=170,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
+        <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
       </c>
       <c r="AR7" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="8" spans="1:45">
@@ -19632,7 +19614,7 @@
     </row>
     <row r="9" spans="1:45">
       <c r="AQ9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B9&lt;&gt;"",IF(IFERROR(VALUE(C8),0)&lt;=0,"["&amp;B9&amp;"]={","},["&amp;B9&amp;"]={"),IF(C9&gt;0,"{dwID="&amp;C9&amp;","&amp;"nLevel="&amp;D9&amp;","&amp;IF(E9&gt;0,"nCount="&amp;E9&amp;",","")&amp;IF(F9&gt;0,"nIcon="&amp;F9&amp;",","")&amp;IF(G9&lt;&gt;"","szName="""&amp;G9&amp;""",","")&amp;IF(H9&gt;0,"bCheckLevel=true,","")&amp;IF(I9&gt;0,"nScrutinyType="&amp;I9&amp;",","")&amp;IF(J9&lt;&gt;"","tKungFu={"&amp;J9&amp;"},","")&amp;IF(K9&lt;&gt;"","szNote="""&amp;K9&amp;""",","")&amp;IF(L9&lt;&gt;"","col={"&amp;L9&amp;"},","")&amp;"[1]={"&amp;IF(M9&lt;&gt;"","tMark={"&amp;M9&amp;"},","")&amp;IF(N9&lt;&gt;"","szVoice="""&amp;N9&amp;""",","")&amp;IF(O9&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P9&gt;0,"bTeamChannel=true,","")&amp;IF(Q9&gt;0,"bWhisperChannel=true,","")&amp;IF(R9&gt;0,"bCenterAlarm=true,","")&amp;IF(S9&gt;0,"bScreenHead=true,","")&amp;IF(T9&gt;0,"bPartyBuffList=true,","")&amp;IF(U9&gt;0,"bBuffList=true,","")&amp;IF(V9&gt;0,"bFullScreen=true,","")&amp;IF(W9&gt;0,"bTeamPanel=true,","")&amp;IF(X9&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y9&lt;&gt;"","szVoice="""&amp;Y9&amp;""",","")&amp;IF(Z9&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA9&gt;0,"bTeamChannel=true,","")&amp;IF(AB9&gt;0,"bWhisperChannel=true,","")&amp;IF(AC9&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD9&gt;0,AH9&lt;&gt;"",AI9&gt;0,AJ9&lt;&gt;"",AK9&lt;&gt;"",AL9&gt;0,AM9&gt;0,AN9&gt;0,AO9&gt;0),"aCataclysmBuff={{"&amp;IF(AD9&gt;0,"nStackNum="&amp;AD9&amp;",","")&amp;IF(AE9&lt;&gt;"","szStackOp="""&amp;AE9&amp;""",","")&amp;IF(AF9&gt;0,"bOnlyMine=true,","")&amp;IF(AG9&gt;0,"bOnlyMe=true,","")&amp;IF(AH9&lt;&gt;"","szReminder="""&amp;AH9&amp;""",","")&amp;IF(AI9&gt;0,"nPriority="&amp;AI9&amp;",","")&amp;IF(AJ9&lt;&gt;"","col="""&amp;AJ9&amp;""",","")&amp;IF(AK9&lt;&gt;"","colScreenHead="""&amp;AK9&amp;""",","")&amp;IF(AL9&gt;0,"nColAlpha="&amp;AL9&amp;",","")&amp;IF(AM9&gt;0,"bAttention=true,","")&amp;IF(AN9&gt;0,"bCaution=true,","")&amp;IF(AO9&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP9&amp;"},","")&amp;IF(AR9&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR9:AAC9)&amp;"},","")&amp;"},",IF(C8&gt;0,"},","")&amp;IF(AND(B9="",C9="",OR(B8&lt;&gt;"",C8&lt;&gt;"")),"},}","")))</f>
         <v/>
       </c>
     </row>
@@ -19684,43 +19666,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="N1" t="s">
         <v>1548</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>1549</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>1550</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>1551</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>1552</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>1553</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>1554</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>1555</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>1556</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>1557</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>1558</v>
-      </c>
-      <c r="W1" t="s">
-        <v>1559</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1560</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
@@ -19746,14 +19728,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="X3" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19764,14 +19746,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19782,14 +19764,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="X5" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19800,16 +19782,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="K6" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="V6">
         <v>1</v>
@@ -19855,10 +19837,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F1" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19873,43 +19855,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="M1" t="s">
         <v>1572</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>1573</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>1574</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>1575</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>1576</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>1577</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>1578</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>1579</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>1580</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1582</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -19917,7 +19899,7 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -19935,7 +19917,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -19944,7 +19926,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -19953,7 +19935,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -19971,7 +19953,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -19980,7 +19962,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -20007,10 +19989,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="V7" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -20025,16 +20007,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="J8" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -20049,10 +20031,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="V9" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20067,10 +20049,10 @@
         <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="V10" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20085,7 +20067,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20094,7 +20076,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20109,7 +20091,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20118,7 +20100,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20133,7 +20115,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20142,7 +20124,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20157,7 +20139,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="J14" t="s">
         <v>582</v>
@@ -20166,7 +20148,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
@@ -20181,7 +20163,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20190,17 +20172,17 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="Y15" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20211,7 +20193,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="J16" t="s">
         <v>640</v>
@@ -20220,14 +20202,14 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X16" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="3:25">
@@ -20238,10 +20220,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="V17" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20256,7 +20238,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20265,7 +20247,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20280,7 +20262,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20289,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20304,7 +20286,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J20" t="s">
         <v>582</v>
@@ -20313,7 +20295,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
@@ -20328,7 +20310,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="J21" t="s">
         <v>582</v>
@@ -20337,7 +20319,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -20352,7 +20334,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20361,17 +20343,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="Y22" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20382,7 +20364,7 @@
         <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="J23" t="s">
         <v>640</v>
@@ -20391,14 +20373,14 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X23" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="24" spans="3:25">
@@ -20409,7 +20391,7 @@
         <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="J24" t="s">
         <v>640</v>
@@ -20418,17 +20400,17 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X24" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="Y24" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="25" spans="3:25">
@@ -20439,10 +20421,10 @@
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="V25" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
@@ -20485,10 +20467,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="E1" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20503,40 +20485,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="L1" t="s">
         <v>1634</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>1635</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>1636</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>1637</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>1638</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>1639</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>1640</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>1641</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1642</v>
-      </c>
-      <c r="S1" t="s">
-        <v>1643</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20556,7 +20538,7 @@
         <v>8852</v>
       </c>
       <c r="H3" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20565,7 +20547,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20577,7 +20559,7 @@
         <v>8851</v>
       </c>
       <c r="H4" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20586,7 +20568,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20598,7 +20580,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20607,7 +20589,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20619,7 +20601,7 @@
         <v>8849</v>
       </c>
       <c r="H6" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20628,7 +20610,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20640,7 +20622,7 @@
         <v>8848</v>
       </c>
       <c r="H7" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20649,7 +20631,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20673,7 +20655,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20685,7 +20667,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20732,7 +20714,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20741,31 +20723,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I1" t="s">
         <v>1658</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>1659</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>1660</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>1661</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>1662</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>1663</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>1664</v>
-      </c>
-      <c r="N1" t="s">
-        <v>1665</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1666</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20773,7 +20755,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20785,43 +20767,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E3" t="s">
         <v>1668</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1669</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1670</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O15" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D4" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="E4" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
       <c r="A5" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B5">
         <v>-2</v>
@@ -20833,13 +20815,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D6" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="E6" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20852,12 +20834,12 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B7">
         <v>-21</v>
@@ -20869,13 +20851,13 @@
     </row>
     <row r="8" customFormat="1" spans="1:16">
       <c r="C8" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D8" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="E8" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -20888,7 +20870,7 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P8" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -20905,13 +20887,13 @@
     </row>
     <row r="10" spans="1:16">
       <c r="C10" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D10" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="E10" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -20924,42 +20906,42 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="D11" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P11" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="D12" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D13" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="E13" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -20969,18 +20951,18 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D14" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="E14" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -20990,7 +20972,7 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -21023,7 +21005,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21032,31 +21014,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H1" t="s">
         <v>1658</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>1659</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>1660</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>1661</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>1662</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>1663</v>
       </c>
-      <c r="L1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1665</v>
-      </c>
       <c r="N1" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21076,88 +21058,88 @@
     </row>
     <row r="3" spans="1:18">
       <c r="C3" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N33" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="P3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="Q3" t="s">
         <v>1692</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>1693</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>1694</v>
-      </c>
-      <c r="R3" t="s">
-        <v>1695</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="C4" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="Q4" t="s">
         <v>1697</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>1698</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>1699</v>
-      </c>
-      <c r="R4" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="C5" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O5" t="s">
+        <v>1700</v>
+      </c>
+      <c r="P5" t="s">
+        <v>1701</v>
+      </c>
+      <c r="Q5" t="s">
         <v>1702</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
         <v>1703</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>1704</v>
-      </c>
-      <c r="R5" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="C6" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="P6" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="C7" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D7" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="E7" t="s">
         <v>582</v>
@@ -21172,10 +21154,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="C8" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D8" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="E8" t="s">
         <v>582</v>
@@ -21191,24 +21173,24 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="C9" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="C10" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -21218,39 +21200,39 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="C11" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="C12" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="C13" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="D13" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21260,15 +21242,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="C14" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="D14" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21278,27 +21260,27 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="C15" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="C16" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D16" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21308,63 +21290,63 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="C17" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="C18" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="C19" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="C21" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="D21" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -21374,48 +21356,48 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="C22" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O22" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="C23" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="C24" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:15">
       <c r="A25" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B25">
         <v>-2</v>
@@ -21427,10 +21409,10 @@
     </row>
     <row r="26" customFormat="1" spans="1:15">
       <c r="C26" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="D26" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -21440,15 +21422,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="C27" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="D27" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -21458,27 +21440,27 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O27" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="C28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="D28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B29">
         <v>-21</v>
@@ -21490,10 +21472,10 @@
     </row>
     <row r="30" customFormat="1" spans="1:15">
       <c r="C30" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="D30" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -21503,15 +21485,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:15">
       <c r="C31" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="D31" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -21521,22 +21503,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O31" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:15">
       <c r="C32" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="D32" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="33" spans="14:14">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="1819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="1824">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5115,6 +5115,24 @@
     <t>蓝方·击伤·九渊麒麟</t>
   </si>
   <si>
+    <t>我方拾取麒麟珠\n</t>
+  </si>
+  <si>
+    <t>我方·获得·麒麟珠</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>敌方拾取麒麟珠\n</t>
+  </si>
+  <si>
+    <t>敌方·获得·麒麟珠</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
     <t>return {CHAT={</t>
   </si>
   <si>
@@ -5211,19 +5229,16 @@
     <t>{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},</t>
   </si>
   <si>
-    <t>我方拾取麒麟珠\n</t>
-  </si>
-  <si>
-    <t>我方·获得·麒麟珠</t>
+    <t>红方成功击败了九渊麒麟\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>蓝方成功击败了九渊麒麟\n</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>敌方拾取麒麟珠\n</t>
-  </si>
-  <si>
-    <t>敌方·获得·麒麟珠</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
@@ -6731,7 +6746,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1784310889000,</v>
+        <v>nTimeStamp = 1784725365000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8657,7 +8672,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8670,13 +8685,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="B2" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="C2" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8685,13 +8700,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1761</v>
+        <v>1766</v>
       </c>
       <c r="B3" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="C3" t="s">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8700,13 +8715,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="B4" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="C4" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8715,13 +8730,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="B5" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="C5" t="s">
-        <v>1769</v>
+        <v>1774</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8730,7 +8745,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8739,13 +8754,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="B7" t="s">
-        <v>1772</v>
+        <v>1777</v>
       </c>
       <c r="C7" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8754,13 +8769,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1774</v>
+        <v>1779</v>
       </c>
       <c r="B8" t="s">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="C8" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8769,13 +8784,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="B9" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="C9" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8784,13 +8799,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="B10" t="s">
-        <v>1779</v>
+        <v>1784</v>
       </c>
       <c r="C10" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8799,13 +8814,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1780</v>
+        <v>1785</v>
       </c>
       <c r="B11" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="C11" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8814,7 +8829,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1782</v>
+        <v>1787</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8823,10 +8838,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1783</v>
+        <v>1788</v>
       </c>
       <c r="C13" t="s">
-        <v>1772</v>
+        <v>1777</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8835,10 +8850,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="C14" t="s">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8847,10 +8862,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="C15" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8859,10 +8874,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
       <c r="C16" t="s">
-        <v>1779</v>
+        <v>1784</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8871,10 +8886,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="C17" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8883,7 +8898,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8892,7 +8907,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8901,7 +8916,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8910,7 +8925,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1791</v>
+        <v>1796</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8919,7 +8934,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1792</v>
+        <v>1797</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8952,7 +8967,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8969,7 +8984,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -8983,7 +8998,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -8997,7 +9012,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9017,7 +9032,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9036,7 +9051,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9047,7 +9062,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9058,7 +9073,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9074,7 +9089,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9089,7 +9104,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9100,7 +9115,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9111,7 +9126,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9127,7 +9142,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9142,7 +9157,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9153,7 +9168,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9164,7 +9179,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9180,7 +9195,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9195,7 +9210,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9206,7 +9221,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9217,7 +9232,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9233,7 +9248,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9248,7 +9263,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9259,7 +9274,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9270,7 +9285,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9286,7 +9301,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9301,7 +9316,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9312,7 +9327,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9323,7 +9338,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9339,7 +9354,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9354,7 +9369,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9365,7 +9380,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9376,7 +9391,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9392,7 +9407,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9407,7 +9422,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9418,7 +9433,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9429,7 +9444,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9445,7 +9460,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9460,7 +9475,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9471,7 +9486,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9482,7 +9497,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9498,7 +9513,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9513,7 +9528,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9524,7 +9539,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9535,7 +9550,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9551,7 +9566,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9566,7 +9581,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9577,7 +9592,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9588,7 +9603,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9604,7 +9619,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9619,7 +9634,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9630,7 +9645,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9641,7 +9656,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9657,7 +9672,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9672,7 +9687,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9683,7 +9698,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9694,7 +9709,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9710,7 +9725,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9725,7 +9740,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9736,7 +9751,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9747,7 +9762,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9763,7 +9778,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9778,7 +9793,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9789,7 +9804,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9800,7 +9815,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9816,7 +9831,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9831,7 +9846,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9842,7 +9857,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9853,7 +9868,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9869,7 +9884,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9884,7 +9899,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9895,7 +9910,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9906,7 +9921,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9922,7 +9937,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9937,7 +9952,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9948,7 +9963,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9959,7 +9974,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9975,7 +9990,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -9990,7 +10005,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10001,7 +10016,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10012,7 +10027,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10028,7 +10043,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10043,7 +10058,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10054,7 +10069,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10065,7 +10080,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10081,7 +10096,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10096,7 +10111,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10107,7 +10122,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10118,7 +10133,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10134,7 +10149,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10149,7 +10164,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10160,7 +10175,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10171,7 +10186,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10187,7 +10202,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10202,7 +10217,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10213,7 +10228,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10224,7 +10239,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10240,7 +10255,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10254,7 +10269,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10264,7 +10279,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10274,7 +10289,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10290,7 +10305,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10310,7 +10325,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10330,7 +10345,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10350,7 +10365,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10370,7 +10385,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10390,7 +10405,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10410,7 +10425,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10430,7 +10445,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10450,7 +10465,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10470,7 +10485,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10490,7 +10505,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10510,7 +10525,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10530,7 +10545,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10550,7 +10565,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10570,7 +10585,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10590,7 +10605,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10610,7 +10625,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10630,7 +10645,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10650,7 +10665,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10670,7 +10685,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10690,7 +10705,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10710,7 +10725,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10730,7 +10745,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10750,7 +10765,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10770,7 +10785,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10790,7 +10805,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10810,7 +10825,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10830,7 +10845,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10850,7 +10865,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10870,7 +10885,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10890,7 +10905,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10910,7 +10925,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10930,7 +10945,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10950,7 +10965,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10970,7 +10985,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19452,7 +19467,7 @@
         <v>1530</v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ8" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AQ3:AQ9" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·15尺伤害距离",col={128,238,255,},[1]={},[2]={},},</v>
       </c>
     </row>
@@ -19614,7 +19629,7 @@
     </row>
     <row r="9" spans="1:45">
       <c r="AQ9" t="str">
-        <f>IF(B9&lt;&gt;"",IF(IFERROR(VALUE(C8),0)&lt;=0,"["&amp;B9&amp;"]={","},["&amp;B9&amp;"]={"),IF(C9&gt;0,"{dwID="&amp;C9&amp;","&amp;"nLevel="&amp;D9&amp;","&amp;IF(E9&gt;0,"nCount="&amp;E9&amp;",","")&amp;IF(F9&gt;0,"nIcon="&amp;F9&amp;",","")&amp;IF(G9&lt;&gt;"","szName="""&amp;G9&amp;""",","")&amp;IF(H9&gt;0,"bCheckLevel=true,","")&amp;IF(I9&gt;0,"nScrutinyType="&amp;I9&amp;",","")&amp;IF(J9&lt;&gt;"","tKungFu={"&amp;J9&amp;"},","")&amp;IF(K9&lt;&gt;"","szNote="""&amp;K9&amp;""",","")&amp;IF(L9&lt;&gt;"","col={"&amp;L9&amp;"},","")&amp;"[1]={"&amp;IF(M9&lt;&gt;"","tMark={"&amp;M9&amp;"},","")&amp;IF(N9&lt;&gt;"","szVoice="""&amp;N9&amp;""",","")&amp;IF(O9&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P9&gt;0,"bTeamChannel=true,","")&amp;IF(Q9&gt;0,"bWhisperChannel=true,","")&amp;IF(R9&gt;0,"bCenterAlarm=true,","")&amp;IF(S9&gt;0,"bScreenHead=true,","")&amp;IF(T9&gt;0,"bPartyBuffList=true,","")&amp;IF(U9&gt;0,"bBuffList=true,","")&amp;IF(V9&gt;0,"bFullScreen=true,","")&amp;IF(W9&gt;0,"bTeamPanel=true,","")&amp;IF(X9&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y9&lt;&gt;"","szVoice="""&amp;Y9&amp;""",","")&amp;IF(Z9&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA9&gt;0,"bTeamChannel=true,","")&amp;IF(AB9&gt;0,"bWhisperChannel=true,","")&amp;IF(AC9&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD9&gt;0,AH9&lt;&gt;"",AI9&gt;0,AJ9&lt;&gt;"",AK9&lt;&gt;"",AL9&gt;0,AM9&gt;0,AN9&gt;0,AO9&gt;0),"aCataclysmBuff={{"&amp;IF(AD9&gt;0,"nStackNum="&amp;AD9&amp;",","")&amp;IF(AE9&lt;&gt;"","szStackOp="""&amp;AE9&amp;""",","")&amp;IF(AF9&gt;0,"bOnlyMine=true,","")&amp;IF(AG9&gt;0,"bOnlyMe=true,","")&amp;IF(AH9&lt;&gt;"","szReminder="""&amp;AH9&amp;""",","")&amp;IF(AI9&gt;0,"nPriority="&amp;AI9&amp;",","")&amp;IF(AJ9&lt;&gt;"","col="""&amp;AJ9&amp;""",","")&amp;IF(AK9&lt;&gt;"","colScreenHead="""&amp;AK9&amp;""",","")&amp;IF(AL9&gt;0,"nColAlpha="&amp;AL9&amp;",","")&amp;IF(AM9&gt;0,"bAttention=true,","")&amp;IF(AN9&gt;0,"bCaution=true,","")&amp;IF(AO9&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP9&amp;"},","")&amp;IF(AR9&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR9:AAC9)&amp;"},","")&amp;"},",IF(C8&gt;0,"},","")&amp;IF(AND(B9="",C9="",OR(B8&lt;&gt;"",C8&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -20696,7 +20711,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="58.875" customWidth="1"/>
@@ -20776,7 +20791,7 @@
         <v>1668</v>
       </c>
       <c r="O3" t="str">
-        <f t="shared" ref="O3:O15" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="O3:O17" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
@@ -20976,7 +20991,49 @@
       </c>
     </row>
     <row r="15" spans="1:16">
+      <c r="C15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
       <c r="O15" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+      </c>
+      <c r="P15" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="C16" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="17" spans="15:15">
+      <c r="O17" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
@@ -20991,7 +21048,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="27.125" customWidth="1"/>
@@ -21038,7 +21095,7 @@
         <v>1663</v>
       </c>
       <c r="N1" t="s">
-        <v>1688</v>
+        <v>1694</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21058,88 +21115,88 @@
     </row>
     <row r="3" spans="1:18">
       <c r="C3" t="s">
-        <v>1689</v>
+        <v>1695</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N33" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1690</v>
+        <v>1696</v>
       </c>
       <c r="P3" t="s">
-        <v>1691</v>
+        <v>1697</v>
       </c>
       <c r="Q3" t="s">
-        <v>1692</v>
+        <v>1698</v>
       </c>
       <c r="R3" t="s">
-        <v>1693</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="C4" t="s">
-        <v>1694</v>
+        <v>1700</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1695</v>
+        <v>1701</v>
       </c>
       <c r="P4" t="s">
-        <v>1696</v>
+        <v>1702</v>
       </c>
       <c r="Q4" t="s">
-        <v>1697</v>
+        <v>1703</v>
       </c>
       <c r="R4" t="s">
-        <v>1698</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="C5" t="s">
-        <v>1699</v>
+        <v>1705</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1700</v>
+        <v>1706</v>
       </c>
       <c r="P5" t="s">
-        <v>1701</v>
+        <v>1707</v>
       </c>
       <c r="Q5" t="s">
-        <v>1702</v>
+        <v>1708</v>
       </c>
       <c r="R5" t="s">
-        <v>1703</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="C6" t="s">
-        <v>1704</v>
+        <v>1710</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1705</v>
+        <v>1711</v>
       </c>
       <c r="P6" t="s">
-        <v>1706</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="C7" t="s">
-        <v>1707</v>
+        <v>1713</v>
       </c>
       <c r="D7" t="s">
-        <v>1708</v>
+        <v>1714</v>
       </c>
       <c r="E7" t="s">
         <v>582</v>
@@ -21154,10 +21211,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="C8" t="s">
-        <v>1709</v>
+        <v>1715</v>
       </c>
       <c r="D8" t="s">
-        <v>1710</v>
+        <v>1716</v>
       </c>
       <c r="E8" t="s">
         <v>582</v>
@@ -21173,24 +21230,24 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1711</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="C9" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1713</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="C10" t="s">
-        <v>1714</v>
+        <v>1720</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -21200,94 +21257,100 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1715</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="C11" t="s">
-        <v>1716</v>
+        <v>1722</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1717</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="C12" t="s">
-        <v>1718</v>
+        <v>1724</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1719</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="C13" t="s">
-        <v>1720</v>
+        <v>1726</v>
       </c>
       <c r="D13" t="s">
-        <v>1721</v>
+        <v>1684</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="C14" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="D14" t="s">
-        <v>1724</v>
+        <v>1687</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="C15" t="s">
-        <v>1726</v>
+        <v>1688</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
+        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="C16" t="s">
-        <v>1728</v>
+        <v>1691</v>
       </c>
       <c r="D16" t="s">
-        <v>1729</v>
+        <v>1692</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
+        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
         <v>1730</v>
@@ -21299,7 +21362,7 @@
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
+        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O17" t="s">
         <v>1732</v>
@@ -21309,51 +21372,51 @@
       <c r="C18" t="s">
         <v>1733</v>
       </c>
+      <c r="D18" t="s">
+        <v>1734</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="C19" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
+        <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
+        <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="C21" t="s">
-        <v>1739</v>
-      </c>
-      <c r="D21" t="s">
         <v>1740</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
+        <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O21" t="s">
         <v>1741</v>
@@ -21365,7 +21428,7 @@
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
+        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O22" t="s">
         <v>1743</v>
@@ -21375,154 +21438,184 @@
       <c r="C23" t="s">
         <v>1744</v>
       </c>
+      <c r="D23" t="s">
+        <v>1745</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="C24" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
+        <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:15">
-      <c r="A25" t="s">
-        <v>1582</v>
-      </c>
-      <c r="B25">
-        <v>-2</v>
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="C25" t="s">
+        <v>1749</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
-        <v>},[-2]={</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:15">
+        <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+      </c>
+      <c r="O25" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="C26" t="s">
-        <v>1748</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1749</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
+        <v>1751</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+        <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="C27" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D27" t="s">
         <v>1752</v>
       </c>
-      <c r="K27">
-        <v>1</v>
+    </row>
+    <row r="27" customFormat="1" spans="1:15">
+      <c r="A27" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B27">
+        <v>-2</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
-      </c>
-      <c r="O27" t="s">
+        <v>},[-2]={</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:15">
+      <c r="C28" t="s">
         <v>1753</v>
       </c>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>1754</v>
       </c>
-      <c r="D28" t="s">
-        <v>1755</v>
+      <c r="K28">
+        <v>1</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
+        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="C29" t="s">
         <v>1756</v>
       </c>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" t="s">
-        <v>1585</v>
-      </c>
-      <c r="B29">
-        <v>-21</v>
+      <c r="D29" t="s">
+        <v>1757</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
-        <v>},[-21]={</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:15">
+        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O29" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="C30" t="s">
-        <v>1748</v>
+        <v>1759</v>
       </c>
       <c r="D30" t="s">
-        <v>1749</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
+        <v>1760</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+        <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:15">
-      <c r="C31" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1752</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B31">
+        <v>-21</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
-      </c>
-      <c r="O31" t="s">
-        <v>1753</v>
+        <v>},[-21]={</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:15">
       <c r="C32" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D32" t="s">
         <v>1754</v>
       </c>
-      <c r="D32" t="s">
-        <v>1755</v>
+      <c r="K32">
+        <v>1</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="0"/>
+        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O32" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="3:15">
+      <c r="C33" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1757</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O33" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="3:15">
+      <c r="C34" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
-      <c r="O32" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="33" spans="14:14">
-      <c r="N33" t="str">
+      <c r="O34" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="35" spans="3:15">
+      <c r="N35" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1829">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4689,6 +4689,15 @@
     <t>{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},</t>
   </si>
   <si>
+    <t>主城的数据</t>
+  </si>
+  <si>
+    <t>消极参战</t>
+  </si>
+  <si>
+    <t>门派地图的数据</t>
+  </si>
+  <si>
     <t>标记.招式释放</t>
   </si>
   <si>
@@ -4797,9 +4806,6 @@
     <t>return {NPC={</t>
   </si>
   <si>
-    <t>主城的数据</t>
-  </si>
-  <si>
     <t>帮会联赛·闻千瞬</t>
   </si>
   <si>
@@ -5068,6 +5074,15 @@
   </si>
   <si>
     <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},</t>
+  </si>
+  <si>
+    <t>^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！</t>
+  </si>
+  <si>
+    <t>[{$1}]·取消报名·《武林争霸赛·{$2}》</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},</t>
   </si>
   <si>
     <t>^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！</t>
@@ -6746,7 +6761,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1784725365000,</v>
+        <v>nTimeStamp = 1785328522000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8672,7 +8687,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8685,13 +8700,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="B2" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="C2" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8700,13 +8715,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="B3" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="C3" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8715,13 +8730,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1769</v>
+        <v>1774</v>
       </c>
       <c r="B4" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="C4" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8730,13 +8745,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1772</v>
+        <v>1777</v>
       </c>
       <c r="B5" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="C5" t="s">
-        <v>1774</v>
+        <v>1779</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8745,7 +8760,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8754,13 +8769,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="B7" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="C7" t="s">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8769,13 +8784,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1779</v>
+        <v>1784</v>
       </c>
       <c r="B8" t="s">
-        <v>1780</v>
+        <v>1785</v>
       </c>
       <c r="C8" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8784,13 +8799,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="B9" t="s">
-        <v>1782</v>
+        <v>1787</v>
       </c>
       <c r="C9" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8799,13 +8814,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1783</v>
+        <v>1788</v>
       </c>
       <c r="B10" t="s">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="C10" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8814,13 +8829,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="B11" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
       <c r="C11" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8829,7 +8844,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8838,10 +8853,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="C13" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8850,10 +8865,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="C14" t="s">
-        <v>1780</v>
+        <v>1785</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8862,10 +8877,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="C15" t="s">
-        <v>1782</v>
+        <v>1787</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8874,10 +8889,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1791</v>
+        <v>1796</v>
       </c>
       <c r="C16" t="s">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8886,10 +8901,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1792</v>
+        <v>1797</v>
       </c>
       <c r="C17" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8898,7 +8913,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8907,7 +8922,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8916,7 +8931,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8925,7 +8940,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8934,7 +8949,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8967,7 +8982,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8984,7 +8999,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -8998,7 +9013,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9012,7 +9027,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9032,7 +9047,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9051,7 +9066,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9062,7 +9077,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9073,7 +9088,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9089,7 +9104,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9104,7 +9119,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9115,7 +9130,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9126,7 +9141,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9142,7 +9157,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9157,7 +9172,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9168,7 +9183,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9179,7 +9194,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9195,7 +9210,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9210,7 +9225,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9221,7 +9236,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9232,7 +9247,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9248,7 +9263,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9263,7 +9278,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9274,7 +9289,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9285,7 +9300,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9301,7 +9316,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9316,7 +9331,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9327,7 +9342,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9338,7 +9353,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9354,7 +9369,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9369,7 +9384,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9380,7 +9395,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9391,7 +9406,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9407,7 +9422,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9422,7 +9437,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9433,7 +9448,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9444,7 +9459,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9460,7 +9475,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9475,7 +9490,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9486,7 +9501,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9497,7 +9512,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9513,7 +9528,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9528,7 +9543,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9539,7 +9554,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9550,7 +9565,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9566,7 +9581,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9581,7 +9596,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9592,7 +9607,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9603,7 +9618,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9619,7 +9634,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9634,7 +9649,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9645,7 +9660,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9656,7 +9671,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9672,7 +9687,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9687,7 +9702,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9698,7 +9713,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9709,7 +9724,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9725,7 +9740,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9740,7 +9755,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9751,7 +9766,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9762,7 +9777,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9778,7 +9793,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9793,7 +9808,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9804,7 +9819,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9815,7 +9830,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9831,7 +9846,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9846,7 +9861,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9857,7 +9872,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9868,7 +9883,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9884,7 +9899,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9899,7 +9914,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9910,7 +9925,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9921,7 +9936,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9937,7 +9952,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9952,7 +9967,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9963,7 +9978,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9974,7 +9989,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9990,7 +10005,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10005,7 +10020,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10016,7 +10031,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10027,7 +10042,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10043,7 +10058,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10058,7 +10073,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10069,7 +10084,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10080,7 +10095,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10096,7 +10111,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10111,7 +10126,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10122,7 +10137,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10133,7 +10148,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10149,7 +10164,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10164,7 +10179,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10175,7 +10190,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10186,7 +10201,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10202,7 +10217,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10217,7 +10232,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10228,7 +10243,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10239,7 +10254,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10255,7 +10270,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10269,7 +10284,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1823</v>
+        <v>1828</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10279,7 +10294,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1823</v>
+        <v>1828</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10289,7 +10304,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1823</v>
+        <v>1828</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10305,7 +10320,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10325,7 +10340,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10345,7 +10360,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10365,7 +10380,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10385,7 +10400,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10405,7 +10420,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10425,7 +10440,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10445,7 +10460,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10465,7 +10480,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10485,7 +10500,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10505,7 +10520,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10525,7 +10540,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10545,7 +10560,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10565,7 +10580,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10585,7 +10600,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10605,7 +10620,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10625,7 +10640,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10645,7 +10660,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10665,7 +10680,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10685,7 +10700,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10705,7 +10720,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10725,7 +10740,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10745,7 +10760,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10765,7 +10780,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10785,7 +10800,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10805,7 +10820,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10825,7 +10840,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10845,7 +10860,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10865,7 +10880,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10885,7 +10900,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10905,7 +10920,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10925,7 +10940,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10945,7 +10960,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10965,7 +10980,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10985,7 +11000,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19298,7 +19313,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS9"/>
+  <dimension ref="A1:AS12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="11" max="11" width="14.875" customWidth="1"/>
@@ -19467,7 +19482,7 @@
         <v>1530</v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ9" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AQ3:AQ12" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·15尺伤害距离",col={128,238,255,},[1]={},[2]={},},</v>
       </c>
     </row>
@@ -19622,15 +19637,81 @@
       </c>
     </row>
     <row r="8" spans="1:45">
+      <c r="A8" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B8">
+        <v>-2</v>
+      </c>
       <c r="AQ8" t="str">
         <f t="shared" si="0"/>
-        <v>},},}</v>
+        <v>},[-2]={</v>
       </c>
     </row>
     <row r="9" spans="1:45">
+      <c r="C9">
+        <v>18913</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1547</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
       <c r="AQ9" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>{dwID=18913,nLevel=1,nScrutinyType=2,szNote="消极参战",[1]={bBuffList=true,bTeamPanel=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:45">
+      <c r="A10" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B10">
+        <v>-21</v>
+      </c>
+      <c r="AQ10" t="str">
+        <f t="shared" si="0"/>
+        <v>},[-21]={</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:45">
+      <c r="C11">
+        <v>18913</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1547</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="str">
+        <f t="shared" si="0"/>
+        <v>{dwID=18913,nLevel=1,nScrutinyType=2,szNote="消极参战",[1]={bBuffList=true,bTeamPanel=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45">
+      <c r="AQ12" t="str">
+        <f t="shared" si="0"/>
+        <v>},},}</v>
       </c>
     </row>
   </sheetData>
@@ -19681,43 +19762,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
       <c r="M1" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="N1" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
       <c r="O1" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="P1" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="Q1" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="R1" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="S1" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="T1" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="U1" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="V1" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="W1" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="X1" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
@@ -19743,14 +19824,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="X3" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19761,14 +19842,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19779,14 +19860,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="X5" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19797,16 +19878,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
       <c r="K6" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="V6">
         <v>1</v>
@@ -19852,10 +19933,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="F1" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19870,43 +19951,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="L1" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="M1" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="N1" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="O1" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="P1" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="Q1" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="R1" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="S1" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="T1" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="U1" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -19914,7 +19995,7 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1582</v>
+        <v>1546</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -19932,7 +20013,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -19941,7 +20022,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -19950,7 +20031,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -19968,7 +20049,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -19977,7 +20058,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -20004,10 +20085,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="V7" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -20022,16 +20103,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="J8" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -20046,10 +20127,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="V9" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20064,10 +20145,10 @@
         <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="V10" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20082,7 +20163,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20091,7 +20172,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20106,7 +20187,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20115,7 +20196,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20130,7 +20211,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20139,7 +20220,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20154,7 +20235,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="J14" t="s">
         <v>582</v>
@@ -20163,7 +20244,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
@@ -20178,7 +20259,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20187,17 +20268,17 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="Y15" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20208,7 +20289,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="J16" t="s">
         <v>640</v>
@@ -20217,14 +20298,14 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X16" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="3:25">
@@ -20235,10 +20316,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="V17" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20253,7 +20334,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20262,7 +20343,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20277,7 +20358,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20286,7 +20367,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20301,7 +20382,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="J20" t="s">
         <v>582</v>
@@ -20310,7 +20391,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
@@ -20325,7 +20406,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="J21" t="s">
         <v>582</v>
@@ -20334,7 +20415,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -20349,7 +20430,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20358,17 +20439,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="Y22" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20379,7 +20460,7 @@
         <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="J23" t="s">
         <v>640</v>
@@ -20388,14 +20469,14 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X23" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="24" spans="3:25">
@@ -20406,7 +20487,7 @@
         <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="J24" t="s">
         <v>640</v>
@@ -20415,17 +20496,17 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X24" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="Y24" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="25" spans="3:25">
@@ -20436,10 +20517,10 @@
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="V25" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
@@ -20482,10 +20563,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="E1" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20500,40 +20581,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K1" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="L1" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M1" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="N1" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="O1" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="P1" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="Q1" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="R1" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="S1" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20553,7 +20634,7 @@
         <v>8852</v>
       </c>
       <c r="H3" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20562,7 +20643,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20574,7 +20655,7 @@
         <v>8851</v>
       </c>
       <c r="H4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20583,7 +20664,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20595,7 +20676,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20604,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20616,7 +20697,7 @@
         <v>8849</v>
       </c>
       <c r="H6" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20625,7 +20706,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20637,7 +20718,7 @@
         <v>8848</v>
       </c>
       <c r="H7" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20646,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20670,7 +20751,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20682,7 +20763,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20711,7 +20792,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="58.875" customWidth="1"/>
@@ -20729,7 +20810,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20738,31 +20819,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="H1" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="I1" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="J1" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="K1" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="L1" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="M1" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="N1" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="O1" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20770,7 +20851,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20782,43 +20863,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="D3" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="E3" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="O3" t="str">
-        <f t="shared" ref="O3:O17" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="D4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="E4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
       <c r="A5" t="s">
-        <v>1582</v>
+        <v>1546</v>
       </c>
       <c r="B5">
         <v>-2</v>
@@ -20830,13 +20911,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="D6" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="E6" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20846,69 +20927,81 @@
       </c>
       <c r="O6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
+        <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>1585</v>
-      </c>
-      <c r="B7">
-        <v>-21</v>
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:16">
+      <c r="C7" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" si="0"/>
-        <v>},[-21]={</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:16">
-      <c r="C8" t="s">
-        <v>1666</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1673</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1674</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
+        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B8">
+        <v>-21</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
-      </c>
-      <c r="P8" t="s">
+        <v>},[-21]={</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:16">
+      <c r="C9" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D9" t="s">
         <v>1675</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>1516</v>
-      </c>
-      <c r="B9">
-        <v>689</v>
+      <c r="E9" t="s">
+        <v>1676</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="0"/>
-        <v>},[689]={</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
+      </c>
+      <c r="P9" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:16">
       <c r="C10" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="D10" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="E10" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -20918,81 +21011,75 @@
       </c>
       <c r="O10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
+        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="D11" t="s">
-        <v>1679</v>
+      <c r="A11" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B11">
+        <v>689</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
-      </c>
-      <c r="P11" t="s">
-        <v>1680</v>
+        <v>},[689]={</v>
       </c>
     </row>
     <row r="12" spans="1:16">
+      <c r="C12" t="s">
+        <v>1668</v>
+      </c>
       <c r="D12" t="s">
         <v>1681</v>
       </c>
+      <c r="E12" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
       <c r="O12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
+        <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="C13" t="s">
-        <v>1666</v>
-      </c>
       <c r="D13" t="s">
-        <v>1683</v>
-      </c>
-      <c r="E13" t="s">
         <v>1684</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P13" t="s">
         <v>1685</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="C14" t="s">
-        <v>1666</v>
-      </c>
       <c r="D14" t="s">
         <v>1686</v>
       </c>
-      <c r="E14" t="s">
-        <v>1687</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
       <c r="O14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="C15" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="D15" t="s">
         <v>1688</v>
@@ -21005,7 +21092,7 @@
       </c>
       <c r="O15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
         <v>1690</v>
@@ -21013,7 +21100,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="C16" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="D16" t="s">
         <v>1691</v>
@@ -21026,14 +21113,56 @@
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
+        <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="17" spans="3:16">
+      <c r="C17" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+      </c>
+      <c r="P17" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16">
+      <c r="C18" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="0"/>
         <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
-      <c r="P16" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="17" spans="15:15">
-      <c r="O17" t="str">
+      <c r="P18" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16">
+      <c r="O19" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
@@ -21062,7 +21191,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21071,31 +21200,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="G1" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="H1" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="I1" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="J1" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="K1" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="L1" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="M1" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="N1" t="s">
-        <v>1694</v>
+        <v>1699</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21115,88 +21244,88 @@
     </row>
     <row r="3" spans="1:18">
       <c r="C3" t="s">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="P3" t="s">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="Q3" t="s">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="R3" t="s">
-        <v>1699</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="C4" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
       <c r="P4" t="s">
-        <v>1702</v>
+        <v>1707</v>
       </c>
       <c r="Q4" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="R4" t="s">
-        <v>1704</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="C5" t="s">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="P5" t="s">
-        <v>1707</v>
+        <v>1712</v>
       </c>
       <c r="Q5" t="s">
-        <v>1708</v>
+        <v>1713</v>
       </c>
       <c r="R5" t="s">
-        <v>1709</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="C6" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="P6" t="s">
-        <v>1712</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="C7" t="s">
-        <v>1713</v>
+        <v>1718</v>
       </c>
       <c r="D7" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="E7" t="s">
         <v>582</v>
@@ -21211,10 +21340,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="C8" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="D8" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="E8" t="s">
         <v>582</v>
@@ -21230,24 +21359,24 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="C9" t="s">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1719</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="C10" t="s">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -21257,39 +21386,39 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1721</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="C11" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="C12" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="C13" t="s">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="D13" t="s">
-        <v>1684</v>
+        <v>1689</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21299,15 +21428,15 @@
         <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1727</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="C14" t="s">
-        <v>1728</v>
+        <v>1733</v>
       </c>
       <c r="D14" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21317,15 +21446,15 @@
         <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1727</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="C15" t="s">
-        <v>1688</v>
+        <v>1693</v>
       </c>
       <c r="D15" t="s">
-        <v>1689</v>
+        <v>1694</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -21335,15 +21464,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1729</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="C16" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="D16" t="s">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21353,27 +21482,27 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1730</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="C17" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1732</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="C18" t="s">
-        <v>1733</v>
+        <v>1738</v>
       </c>
       <c r="D18" t="s">
-        <v>1734</v>
+        <v>1739</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -21383,63 +21512,63 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1735</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="C19" t="s">
-        <v>1736</v>
+        <v>1741</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1737</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" t="s">
-        <v>1738</v>
+        <v>1743</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1739</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="C21" t="s">
-        <v>1740</v>
+        <v>1745</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1741</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="C22" t="s">
-        <v>1742</v>
+        <v>1747</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O22" t="s">
-        <v>1743</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="C23" t="s">
-        <v>1744</v>
+        <v>1749</v>
       </c>
       <c r="D23" t="s">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -21449,48 +21578,48 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="C24" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1748</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="C25" t="s">
-        <v>1749</v>
+        <v>1754</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1750</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="C26" t="s">
-        <v>1751</v>
+        <v>1756</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1752</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:15">
       <c r="A27" t="s">
-        <v>1582</v>
+        <v>1546</v>
       </c>
       <c r="B27">
         <v>-2</v>
@@ -21502,10 +21631,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:15">
       <c r="C28" t="s">
-        <v>1753</v>
+        <v>1758</v>
       </c>
       <c r="D28" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -21515,15 +21644,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="C29" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="D29" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21533,27 +21662,27 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="C30" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="D30" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1761</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B31">
         <v>-21</v>
@@ -21565,10 +21694,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:15">
       <c r="C32" t="s">
-        <v>1753</v>
+        <v>1758</v>
       </c>
       <c r="D32" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21578,15 +21707,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="3:15">
       <c r="C33" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="D33" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21596,22 +21725,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="3:15">
       <c r="C34" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="D34" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
-        <v>1761</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="35" spans="3:15">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -5058,6 +5058,15 @@
     <t>%</t>
   </si>
   <si>
+    <t>[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！</t>
+  </si>
+  <si>
+    <t>武林争霸赛·已经报名</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},</t>
+  </si>
+  <si>
     <t>【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！</t>
   </si>
   <si>
@@ -5067,13 +5076,13 @@
     <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},</t>
   </si>
   <si>
-    <t>[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！</t>
-  </si>
-  <si>
-    <t>武林争霸赛·已经报名</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},</t>
+    <t>^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！</t>
+  </si>
+  <si>
+    <t>[{$1}]·{$4}报名·《{$2}·{$3}》</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},</t>
   </si>
   <si>
     <t>^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！</t>
@@ -5085,13 +5094,49 @@
     <t>{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},</t>
   </si>
   <si>
-    <t>^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！</t>
-  </si>
-  <si>
-    <t>[{$1}]·{$4}报名·《{$2}·{$3}》</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},</t>
+    <t>敌方拾取麒麟珠\n</t>
+  </si>
+  <si>
+    <t>敌方·获得·麒麟珠</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>我方拾取麒麟珠\n</t>
+  </si>
+  <si>
+    <t>我方·获得·麒麟珠</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>蓝方成功击败了九渊麒麟</t>
+  </si>
+  <si>
+    <t>蓝方·击伤·九渊麒麟</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了九渊麒麟</t>
+  </si>
+  <si>
+    <t>红方·击伤·九渊麒麟</t>
+  </si>
+  <si>
+    <t>我方大旗已被摧毁，本场比赛结束！</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},</t>
+  </si>
+  <si>
+    <t>成功摧毁敌方大旗，您获得本场比赛胜利！</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},</t>
   </si>
   <si>
     <t>我方第(%d-)次鼓舞士气成功！</t>
@@ -5103,54 +5148,168 @@
     <t>{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},</t>
   </si>
   <si>
-    <t>成功摧毁敌方大旗，您获得本场比赛胜利！</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},</t>
-  </si>
-  <si>
-    <t>我方大旗已被摧毁，本场比赛结束！</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},</t>
-  </si>
-  <si>
-    <t>红方成功击败了九渊麒麟</t>
-  </si>
-  <si>
-    <t>红方·击伤·九渊麒麟</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>蓝方成功击败了九渊麒麟</t>
-  </si>
-  <si>
-    <t>蓝方·击伤·九渊麒麟</t>
-  </si>
-  <si>
-    <t>我方拾取麒麟珠\n</t>
-  </si>
-  <si>
-    <t>我方·获得·麒麟珠</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>敌方拾取麒麟珠\n</t>
-  </si>
-  <si>
-    <t>敌方·获得·麒麟珠</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
     <t>return {CHAT={</t>
   </si>
   <si>
+    <t>蓝方成功击败了古猿\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
+  </si>
+  <si>
+    <t>蓝方成功击败了混沌元晶·皓\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},</t>
+  </si>
+  <si>
+    <t>蓝方成功击败了混沌元晶·洞\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},</t>
+  </si>
+  <si>
+    <t>蓝方成功修复大旗10%耐久度\n</t>
+  </si>
+  <si>
+    <t>蓝方·修补·大旗</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},</t>
+  </si>
+  <si>
+    <t>蓝方成功开启全局迷雾视野\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了古猿\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了混沌元晶·皓\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了混沌元晶·洞\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},</t>
+  </si>
+  <si>
+    <t>红方成功修复大旗10%耐久度\n</t>
+  </si>
+  <si>
+    <t>红方·修补·大旗</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},</t>
+  </si>
+  <si>
+    <t>红方成功开启全局迷雾视野\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>蓝方成功击败了九渊麒麟\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了九渊麒麟\n</t>
+  </si>
+  <si>
+    <t>敌方箭塔被摧毁\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},</t>
+  </si>
+  <si>
+    <t>我方箭塔被摧毁\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},</t>
+  </si>
+  <si>
+    <t>我方(.-)路(.-)塔箭塔被攻击</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},</t>
+  </si>
+  <si>
+    <t>我方大旗遭到攻击\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},</t>
+  </si>
+  <si>
+    <t>九渊麒麟已重生！\n</t>
+  </si>
+  <si>
+    <t>九渊麒麟·已经刷新</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},</t>
+  </si>
+  <si>
+    <t>小麻雀收取了你九十九银。\n</t>
+  </si>
+  <si>
+    <t>麻雀·传送</t>
+  </si>
+  <si>
+    <t>战斗开始。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},</t>
+  </si>
+  <si>
+    <t>战斗将在120秒后开始。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},</t>
+  </si>
+  <si>
+    <t>战斗将在180秒后开始。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},</t>
+  </si>
+  <si>
     <t>战斗将在240秒后开始。\n</t>
   </si>
   <si>
@@ -5164,165 +5323,6 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},</t>
-  </si>
-  <si>
-    <t>战斗将在180秒后开始。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},</t>
-  </si>
-  <si>
-    <t>战斗将在120秒后开始。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},</t>
-  </si>
-  <si>
-    <t>战斗开始。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},</t>
-  </si>
-  <si>
-    <t>小麻雀收取了你九十九银。\n</t>
-  </si>
-  <si>
-    <t>麻雀·传送</t>
-  </si>
-  <si>
-    <t>九渊麒麟已重生！\n</t>
-  </si>
-  <si>
-    <t>九渊麒麟·已经刷新</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>我方大旗遭到攻击\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},</t>
-  </si>
-  <si>
-    <t>我方(.-)路(.-)塔箭塔被攻击</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},</t>
-  </si>
-  <si>
-    <t>我方箭塔被摧毁\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},</t>
-  </si>
-  <si>
-    <t>敌方箭塔被摧毁\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},</t>
-  </si>
-  <si>
-    <t>红方成功击败了九渊麒麟\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>蓝方成功击败了九渊麒麟\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
-  </si>
-  <si>
-    <t>红方成功开启全局迷雾视野\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},</t>
-  </si>
-  <si>
-    <t>红方成功修复大旗10%耐久度\n</t>
-  </si>
-  <si>
-    <t>红方·修补·大旗</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},</t>
-  </si>
-  <si>
-    <t>红方成功击败了混沌元晶·洞\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},</t>
-  </si>
-  <si>
-    <t>红方成功击败了混沌元晶·皓\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},</t>
-  </si>
-  <si>
-    <t>红方成功击败了古猿\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
-  </si>
-  <si>
-    <t>蓝方成功开启全局迷雾视野\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},</t>
-  </si>
-  <si>
-    <t>蓝方成功修复大旗10%耐久度\n</t>
-  </si>
-  <si>
-    <t>蓝方·修补·大旗</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},</t>
-  </si>
-  <si>
-    <t>蓝方成功击败了混沌元晶·洞\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},</t>
-  </si>
-  <si>
-    <t>蓝方成功击败了混沌元晶·皓\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},</t>
-  </si>
-  <si>
-    <t>蓝方成功击败了古猿\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
   </si>
   <si>
     <t>练习赛已经报名过了\n</t>
@@ -6761,7 +6761,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1785328522000,</v>
+        <v>nTimeStamp = 1786119069000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
+        <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
         <v>1671</v>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
+        <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
         <v>1674</v>
@@ -20927,7 +20927,7 @@
       </c>
       <c r="O6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
+        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
         <v>1677</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="O7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
+        <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
         <v>1680</v>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="O9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
+        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P9" t="s">
         <v>1677</v>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="O10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
+        <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
         <v>1680</v>
@@ -21039,42 +21039,57 @@
       <c r="E12" t="s">
         <v>1682</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
       <c r="L12">
         <v>1</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
+        <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
         <v>1683</v>
       </c>
     </row>
     <row r="13" spans="1:16">
+      <c r="C13" t="s">
+        <v>1668</v>
+      </c>
       <c r="D13" t="s">
         <v>1684</v>
       </c>
+      <c r="E13" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
       <c r="O13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
+        <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="14" spans="1:16">
+      <c r="C14" t="s">
+        <v>1668</v>
+      </c>
       <c r="D14" t="s">
-        <v>1686</v>
+        <v>1687</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1688</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
       </c>
       <c r="O14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
+        <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -21082,10 +21097,10 @@
         <v>1668</v>
       </c>
       <c r="D15" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="E15" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -21095,46 +21110,28 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="C16" t="s">
-        <v>1668</v>
-      </c>
       <c r="D16" t="s">
-        <v>1691</v>
-      </c>
-      <c r="E16" t="s">
         <v>1692</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P16" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="17" spans="3:16">
-      <c r="C17" t="s">
-        <v>1668</v>
-      </c>
       <c r="D17" t="s">
-        <v>1693</v>
-      </c>
-      <c r="E17" t="s">
         <v>1694</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P17" t="s">
         <v>1695</v>
@@ -21150,12 +21147,15 @@
       <c r="E18" t="s">
         <v>1697</v>
       </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
       <c r="L18">
         <v>1</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P18" t="s">
         <v>1698</v>
@@ -21168,6 +21168,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A12:P18">
+    <sortCondition ref="A12:A18" descending="1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -21183,7 +21186,7 @@
     <col min="3" max="3" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>1476</v>
       </c>
@@ -21230,7 +21233,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>1516</v>
       </c>
@@ -21242,382 +21245,382 @@
         <v>[689]={</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:15">
       <c r="C3" t="s">
         <v>1700</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
+        <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
         <v>1701</v>
       </c>
-      <c r="P3" t="s">
+    </row>
+    <row r="4" spans="1:15">
+      <c r="C4" t="s">
         <v>1702</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>1703</v>
-      </c>
-      <c r="R3" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="C4" t="s">
-        <v>1705</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
+        <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1706</v>
-      </c>
-      <c r="P4" t="s">
-        <v>1707</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>1708</v>
-      </c>
-      <c r="R4" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="C5" t="s">
-        <v>1710</v>
+        <v>1704</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
+        <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1711</v>
-      </c>
-      <c r="P5" t="s">
-        <v>1712</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>1713</v>
-      </c>
-      <c r="R5" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="C6" t="s">
-        <v>1715</v>
+        <v>1706</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
+        <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1716</v>
-      </c>
-      <c r="P6" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1718</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1719</v>
-      </c>
-      <c r="E7" t="s">
-        <v>582</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
+        <v>1709</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="小麻雀收取了你九十九银。\n",szNote="麻雀·传送",col={255,255,255,},[20]={bScreenHead=true,},},</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="C8" t="s">
-        <v>1720</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1721</v>
-      </c>
-      <c r="E8" t="s">
-        <v>582</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
+        <v>1711</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="C9" t="s">
-        <v>1723</v>
+        <v>1713</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
+        <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="C10" t="s">
-        <v>1725</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
+        <v>1715</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
+        <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="C11" t="s">
-        <v>1727</v>
+        <v>1717</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1718</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
+        <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="C12" t="s">
-        <v>1729</v>
+        <v>1720</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
+        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1731</v>
+        <v>1681</v>
       </c>
       <c r="D13" t="s">
-        <v>1689</v>
+        <v>1682</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1733</v>
+        <v>1684</v>
       </c>
       <c r="D14" t="s">
-        <v>1692</v>
+        <v>1685</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1693</v>
+        <v>1724</v>
       </c>
       <c r="D15" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1696</v>
+        <v>1726</v>
       </c>
       <c r="D16" t="s">
-        <v>1697</v>
+        <v>1691</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1736</v>
+        <v>1727</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
+        <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1738</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1739</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
+        <v>1729</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
+        <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1741</v>
+        <v>1731</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
+        <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1743</v>
+        <v>1733</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="C21" t="s">
-        <v>1745</v>
+        <v>1735</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E21" t="s">
+        <v>582</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
+        <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1747</v>
+        <v>1738</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E22" t="s">
+        <v>582</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
-      </c>
-      <c r="O22" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>{szContent="小麻雀收取了你九十九银。\n",szNote="麻雀·传送",col={255,255,255,},[20]={bScreenHead=true,},},</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1749</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1750</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
+        <v>1740</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
+        <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>1741</v>
+      </c>
+      <c r="P23" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1752</v>
+        <v>1743</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
+        <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>1744</v>
+      </c>
+      <c r="P24" t="s">
+        <v>1745</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>1746</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1754</v>
+        <v>1748</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>1749</v>
+      </c>
+      <c r="P25" t="s">
+        <v>1750</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>1751</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
+        <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O26" t="s">
+        <v>1754</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1755</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>1756</v>
+      </c>
+      <c r="R26" t="s">
         <v>1757</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:15">
+    <row r="27" customFormat="1" spans="1:18">
       <c r="A27" t="s">
         <v>1546</v>
       </c>
@@ -21629,7 +21632,7 @@
         <v>},[-2]={</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:15">
+    <row r="28" customFormat="1" spans="1:18">
       <c r="C28" t="s">
         <v>1758</v>
       </c>
@@ -21647,7 +21650,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:18">
       <c r="C29" t="s">
         <v>1761</v>
       </c>
@@ -21665,7 +21668,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:18">
       <c r="C30" t="s">
         <v>1764</v>
       </c>
@@ -21680,7 +21683,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
         <v>1587</v>
       </c>
@@ -21692,7 +21695,7 @@
         <v>},[-21]={</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:15">
+    <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
         <v>1758</v>
       </c>
@@ -21750,6 +21753,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A3:R26">
+    <sortCondition ref="A3:A26" descending="1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="1826">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4753,15 +4753,6 @@
   </si>
   <si>
     <t>{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},</t>
-  </si>
-  <si>
-    <t>进战移动上马</t>
-  </si>
-  <si>
-    <t>战斗移动骑乘</t>
-  </si>
-  <si>
-    <t>255,255,100,</t>
   </si>
   <si>
     <t>数量</t>
@@ -6761,7 +6752,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786119069000,</v>
+        <v>nTimeStamp = 1786703205000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8687,7 +8678,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8700,13 +8691,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="B2" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="C2" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8715,13 +8706,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="B3" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="C3" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8730,13 +8721,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="B4" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="C4" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8745,13 +8736,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="B5" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="C5" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8760,7 +8751,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8769,13 +8760,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="B7" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="C7" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8784,13 +8775,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="B8" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="C8" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8799,13 +8790,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="B9" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
       <c r="C9" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8814,13 +8805,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="B10" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="C10" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8829,13 +8820,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
       <c r="B11" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="C11" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8844,7 +8835,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8853,10 +8844,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
       <c r="C13" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8865,10 +8856,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="C14" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8877,10 +8868,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="C15" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8889,10 +8880,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="C16" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8901,10 +8892,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
       <c r="C17" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8913,7 +8904,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8922,7 +8913,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8931,7 +8922,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8940,7 +8931,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8949,7 +8940,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8982,7 +8973,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8999,7 +8990,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -9013,7 +9004,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9027,7 +9018,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9047,7 +9038,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9066,7 +9057,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9077,7 +9068,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9088,7 +9079,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9104,7 +9095,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9119,7 +9110,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9130,7 +9121,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9141,7 +9132,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9157,7 +9148,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9172,7 +9163,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9183,7 +9174,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9194,7 +9185,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9210,7 +9201,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9225,7 +9216,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9236,7 +9227,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9247,7 +9238,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9263,7 +9254,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9278,7 +9269,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9289,7 +9280,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9300,7 +9291,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9316,7 +9307,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9331,7 +9322,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9342,7 +9333,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9353,7 +9344,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9369,7 +9360,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9384,7 +9375,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9395,7 +9386,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9406,7 +9397,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9422,7 +9413,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9437,7 +9428,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9448,7 +9439,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9459,7 +9450,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9475,7 +9466,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9490,7 +9481,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9501,7 +9492,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9512,7 +9503,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9528,7 +9519,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9543,7 +9534,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9554,7 +9545,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9565,7 +9556,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9581,7 +9572,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9596,7 +9587,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9607,7 +9598,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9618,7 +9609,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9634,7 +9625,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9649,7 +9640,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9660,7 +9651,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9671,7 +9662,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9687,7 +9678,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9702,7 +9693,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9713,7 +9704,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9724,7 +9715,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9740,7 +9731,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9755,7 +9746,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9766,7 +9757,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9777,7 +9768,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9793,7 +9784,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9808,7 +9799,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9819,7 +9810,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9830,7 +9821,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9846,7 +9837,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9861,7 +9852,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9872,7 +9863,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9883,7 +9874,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9899,7 +9890,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9914,7 +9905,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9925,7 +9916,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9936,7 +9927,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9952,7 +9943,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9967,7 +9958,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9978,7 +9969,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9989,7 +9980,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -10005,7 +9996,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10020,7 +10011,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10031,7 +10022,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10042,7 +10033,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10058,7 +10049,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10073,7 +10064,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10084,7 +10075,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10095,7 +10086,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10111,7 +10102,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10126,7 +10117,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10137,7 +10128,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10148,7 +10139,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10164,7 +10155,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10179,7 +10170,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10190,7 +10181,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10201,7 +10192,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10217,7 +10208,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10232,7 +10223,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10243,7 +10234,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10254,7 +10245,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10270,7 +10261,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10284,7 +10275,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10294,7 +10285,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10304,7 +10295,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10320,7 +10311,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10340,7 +10331,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10360,7 +10351,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10380,7 +10371,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10400,7 +10391,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10420,7 +10411,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10440,7 +10431,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10460,7 +10451,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10480,7 +10471,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10500,7 +10491,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10520,7 +10511,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10540,7 +10531,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10560,7 +10551,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10580,7 +10571,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10600,7 +10591,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10620,7 +10611,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10640,7 +10631,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10660,7 +10651,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10680,7 +10671,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10700,7 +10691,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10720,7 +10711,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10740,7 +10731,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10760,7 +10751,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10780,7 +10771,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10800,7 +10791,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10820,7 +10811,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10840,7 +10831,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10860,7 +10851,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10880,7 +10871,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10900,7 +10891,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10920,7 +10911,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10940,7 +10931,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10960,7 +10951,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10980,7 +10971,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -11000,7 +10991,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19724,8 +19715,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
@@ -19812,7 +19803,7 @@
         <v>689</v>
       </c>
       <c r="X2" t="str">
-        <f t="shared" ref="X2:X7" si="0">IF(ISBLANK(B2)=FALSE,IF(ISBLANK(B1),"},["&amp;B2&amp;"]={","["&amp;B2&amp;"]={"),IF(AND(ISBLANK(B2),ISBLANK(C2),ISBLANK(D2),OR(ISBLANK(B1)=FALSE,ISBLANK(C1)=FALSE,ISBLANK(D1)=FALSE)),"},},}",IF(ISBLANK(C2),"","{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nIcon="&amp;E2&amp;",","")&amp;IF(F2&lt;&gt;"","szName="""&amp;F2&amp;""",","")&amp;IF(G2&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H2&gt;0,"nScrutinyType="&amp;H2&amp;",","")&amp;IF(I2&lt;&gt;"","tKungFu={"&amp;I2&amp;"},","")&amp;IF(J2&lt;&gt;"","szNote="""&amp;J2&amp;""",","")&amp;IF(K2&lt;&gt;"","col={"&amp;K2&amp;"},","")&amp;"[9]={"&amp;IF(L2&lt;&gt;"","tMark={"&amp;L2&amp;"},","")&amp;IF(M2&lt;&gt;"","szVoice="""&amp;M2&amp;""",","")&amp;IF(N2&gt;0,"bTeamChannel=true,","")&amp;IF(O2&gt;0,"bWhisperChannel=true,","")&amp;IF(P2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q2&lt;&gt;"","tMark={"&amp;Q2&amp;"},","")&amp;IF(R2&lt;&gt;"","szVoice="""&amp;R2&amp;""",","")&amp;IF(S2&gt;0,"bTeamChannel=true,","")&amp;IF(T2&gt;0,"bWhisperChannel=true,","")&amp;IF(U2&gt;0,"bCenterAlarm=true,","")&amp;IF(V2&gt;0,"bScreenHead=true,","")&amp;IF(W2&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y2:AAC2)&amp;"},","")&amp;"},")))</f>
+        <f>IF(ISBLANK(B2)=FALSE,IF(ISBLANK(B1),"},["&amp;B2&amp;"]={","["&amp;B2&amp;"]={"),IF(AND(ISBLANK(B2),ISBLANK(C2),ISBLANK(D2),OR(ISBLANK(B1)=FALSE,ISBLANK(C1)=FALSE,ISBLANK(D1)=FALSE)),"},},}",IF(ISBLANK(C2),"","{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nIcon="&amp;E2&amp;",","")&amp;IF(F2&lt;&gt;"","szName="""&amp;F2&amp;""",","")&amp;IF(G2&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H2&gt;0,"nScrutinyType="&amp;H2&amp;",","")&amp;IF(I2&lt;&gt;"","tKungFu={"&amp;I2&amp;"},","")&amp;IF(J2&lt;&gt;"","szNote="""&amp;J2&amp;""",","")&amp;IF(K2&lt;&gt;"","col={"&amp;K2&amp;"},","")&amp;"[9]={"&amp;IF(L2&lt;&gt;"","tMark={"&amp;L2&amp;"},","")&amp;IF(M2&lt;&gt;"","szVoice="""&amp;M2&amp;""",","")&amp;IF(N2&gt;0,"bTeamChannel=true,","")&amp;IF(O2&gt;0,"bWhisperChannel=true,","")&amp;IF(P2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q2&lt;&gt;"","tMark={"&amp;Q2&amp;"},","")&amp;IF(R2&lt;&gt;"","szVoice="""&amp;R2&amp;""",","")&amp;IF(S2&gt;0,"bTeamChannel=true,","")&amp;IF(T2&gt;0,"bWhisperChannel=true,","")&amp;IF(U2&gt;0,"bCenterAlarm=true,","")&amp;IF(V2&gt;0,"bScreenHead=true,","")&amp;IF(W2&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y2:AAC2)&amp;"},","")&amp;"},")))</f>
         <v>[689]={</v>
       </c>
     </row>
@@ -19827,7 +19818,7 @@
         <v>1562</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(D3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(D2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nIcon="&amp;E3&amp;",","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H3&gt;0,"nScrutinyType="&amp;H3&amp;",","")&amp;IF(I3&lt;&gt;"","tKungFu={"&amp;I3&amp;"},","")&amp;IF(J3&lt;&gt;"","szNote="""&amp;J3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;"[9]={"&amp;IF(L3&lt;&gt;"","tMark={"&amp;L3&amp;"},","")&amp;IF(M3&lt;&gt;"","szVoice="""&amp;M3&amp;""",","")&amp;IF(N3&gt;0,"bTeamChannel=true,","")&amp;IF(O3&gt;0,"bWhisperChannel=true,","")&amp;IF(P3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q3&lt;&gt;"","tMark={"&amp;Q3&amp;"},","")&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;IF(V3&gt;0,"bScreenHead=true,","")&amp;IF(W3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y3:AAC3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
@@ -19845,7 +19836,7 @@
         <v>1564</v>
       </c>
       <c r="X4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(B4)=FALSE,IF(ISBLANK(B3),"},["&amp;B4&amp;"]={","["&amp;B4&amp;"]={"),IF(AND(ISBLANK(B4),ISBLANK(C4),ISBLANK(D4),OR(ISBLANK(B3)=FALSE,ISBLANK(C3)=FALSE,ISBLANK(D3)=FALSE)),"},},}",IF(ISBLANK(C4),"","{dwID="&amp;C4&amp;","&amp;"nLevel="&amp;D4&amp;","&amp;IF(E4&gt;0,"nIcon="&amp;E4&amp;",","")&amp;IF(F4&lt;&gt;"","szName="""&amp;F4&amp;""",","")&amp;IF(G4&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H4&gt;0,"nScrutinyType="&amp;H4&amp;",","")&amp;IF(I4&lt;&gt;"","tKungFu={"&amp;I4&amp;"},","")&amp;IF(J4&lt;&gt;"","szNote="""&amp;J4&amp;""",","")&amp;IF(K4&lt;&gt;"","col={"&amp;K4&amp;"},","")&amp;"[9]={"&amp;IF(L4&lt;&gt;"","tMark={"&amp;L4&amp;"},","")&amp;IF(M4&lt;&gt;"","szVoice="""&amp;M4&amp;""",","")&amp;IF(N4&gt;0,"bTeamChannel=true,","")&amp;IF(O4&gt;0,"bWhisperChannel=true,","")&amp;IF(P4&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q4&lt;&gt;"","tMark={"&amp;Q4&amp;"},","")&amp;IF(R4&lt;&gt;"","szVoice="""&amp;R4&amp;""",","")&amp;IF(S4&gt;0,"bTeamChannel=true,","")&amp;IF(T4&gt;0,"bWhisperChannel=true,","")&amp;IF(U4&gt;0,"bCenterAlarm=true,","")&amp;IF(V4&gt;0,"bScreenHead=true,","")&amp;IF(W4&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y4&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y4:AAC4)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
@@ -19863,7 +19854,7 @@
         <v>1566</v>
       </c>
       <c r="X5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(B5)=FALSE,IF(ISBLANK(B4),"},["&amp;B5&amp;"]={","["&amp;B5&amp;"]={"),IF(AND(ISBLANK(B5),ISBLANK(C5),ISBLANK(D5),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C5),"","{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nIcon="&amp;E5&amp;",","")&amp;IF(F5&lt;&gt;"","szName="""&amp;F5&amp;""",","")&amp;IF(G5&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H5&gt;0,"nScrutinyType="&amp;H5&amp;",","")&amp;IF(I5&lt;&gt;"","tKungFu={"&amp;I5&amp;"},","")&amp;IF(J5&lt;&gt;"","szNote="""&amp;J5&amp;""",","")&amp;IF(K5&lt;&gt;"","col={"&amp;K5&amp;"},","")&amp;"[9]={"&amp;IF(L5&lt;&gt;"","tMark={"&amp;L5&amp;"},","")&amp;IF(M5&lt;&gt;"","szVoice="""&amp;M5&amp;""",","")&amp;IF(N5&gt;0,"bTeamChannel=true,","")&amp;IF(O5&gt;0,"bWhisperChannel=true,","")&amp;IF(P5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q5&lt;&gt;"","tMark={"&amp;Q5&amp;"},","")&amp;IF(R5&lt;&gt;"","szVoice="""&amp;R5&amp;""",","")&amp;IF(S5&gt;0,"bTeamChannel=true,","")&amp;IF(T5&gt;0,"bWhisperChannel=true,","")&amp;IF(U5&gt;0,"bCenterAlarm=true,","")&amp;IF(V5&gt;0,"bScreenHead=true,","")&amp;IF(W5&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y5:AAC5)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
@@ -19871,35 +19862,8 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="C6">
-        <v>38096</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1568</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1569</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1570</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
       <c r="X6" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=38096,nLevel=1,szName="进战移动上马",nScrutinyType=2,szNote="战斗移动骑乘",col={255,255,100,},[9]={},[8]={bScreenHead=true,},},</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="X7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(B6)=FALSE,IF(ISBLANK(B5),"},["&amp;B6&amp;"]={","["&amp;B6&amp;"]={"),IF(AND(ISBLANK(B6),ISBLANK(C6),ISBLANK(D6),OR(ISBLANK(B5)=FALSE,ISBLANK(C5)=FALSE,ISBLANK(D5)=FALSE)),"},},}",IF(ISBLANK(C6),"","{dwID="&amp;C6&amp;","&amp;"nLevel="&amp;D6&amp;","&amp;IF(E6&gt;0,"nIcon="&amp;E6&amp;",","")&amp;IF(F6&lt;&gt;"","szName="""&amp;F6&amp;""",","")&amp;IF(G6&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H6&gt;0,"nScrutinyType="&amp;H6&amp;",","")&amp;IF(I6&lt;&gt;"","tKungFu={"&amp;I6&amp;"},","")&amp;IF(J6&lt;&gt;"","szNote="""&amp;J6&amp;""",","")&amp;IF(K6&lt;&gt;"","col={"&amp;K6&amp;"},","")&amp;"[9]={"&amp;IF(L6&lt;&gt;"","tMark={"&amp;L6&amp;"},","")&amp;IF(M6&lt;&gt;"","szVoice="""&amp;M6&amp;""",","")&amp;IF(N6&gt;0,"bTeamChannel=true,","")&amp;IF(O6&gt;0,"bWhisperChannel=true,","")&amp;IF(P6&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q6&lt;&gt;"","tMark={"&amp;Q6&amp;"},","")&amp;IF(R6&lt;&gt;"","szVoice="""&amp;R6&amp;""",","")&amp;IF(S6&gt;0,"bTeamChannel=true,","")&amp;IF(T6&gt;0,"bWhisperChannel=true,","")&amp;IF(U6&gt;0,"bCenterAlarm=true,","")&amp;IF(V6&gt;0,"bScreenHead=true,","")&amp;IF(W6&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y6&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y6:AAC6)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>
@@ -19933,10 +19897,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="F1" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19951,43 +19915,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="N1" t="s">
         <v>1573</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>1574</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>1575</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>1576</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>1577</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>1578</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>1579</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>1580</v>
-      </c>
-      <c r="S1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1582</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1583</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -20013,7 +19977,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -20022,7 +19986,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20031,7 +19995,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -20049,7 +20013,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -20058,7 +20022,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -20085,10 +20049,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="V7" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -20103,16 +20067,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="J8" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -20127,10 +20091,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="V9" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20145,10 +20109,10 @@
         <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="V10" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20163,7 +20127,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20172,7 +20136,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20187,7 +20151,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20196,7 +20160,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20211,7 +20175,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20220,7 +20184,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20235,7 +20199,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="J14" t="s">
         <v>582</v>
@@ -20244,7 +20208,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
@@ -20259,7 +20223,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20268,17 +20232,17 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="Y15" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20289,7 +20253,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="J16" t="s">
         <v>640</v>
@@ -20298,14 +20262,14 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X16" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="3:25">
@@ -20316,10 +20280,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="V17" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20334,7 +20298,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20343,7 +20307,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20358,7 +20322,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20367,7 +20331,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20382,7 +20346,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="J20" t="s">
         <v>582</v>
@@ -20391,7 +20355,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
@@ -20406,7 +20370,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="J21" t="s">
         <v>582</v>
@@ -20415,7 +20379,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -20430,7 +20394,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20439,17 +20403,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="Y22" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20460,7 +20424,7 @@
         <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="J23" t="s">
         <v>640</v>
@@ -20469,14 +20433,14 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X23" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="24" spans="3:25">
@@ -20487,7 +20451,7 @@
         <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="J24" t="s">
         <v>640</v>
@@ -20496,17 +20460,17 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X24" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="Y24" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="25" spans="3:25">
@@ -20517,10 +20481,10 @@
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="V25" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
@@ -20563,10 +20527,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="E1" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20581,40 +20545,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="M1" t="s">
         <v>1634</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>1635</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>1636</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>1637</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>1638</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>1639</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>1640</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1642</v>
-      </c>
-      <c r="S1" t="s">
-        <v>1643</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20634,7 +20598,7 @@
         <v>8852</v>
       </c>
       <c r="H3" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20643,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20655,7 +20619,7 @@
         <v>8851</v>
       </c>
       <c r="H4" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20664,7 +20628,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20676,7 +20640,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20685,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20697,7 +20661,7 @@
         <v>8849</v>
       </c>
       <c r="H6" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20706,7 +20670,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20718,7 +20682,7 @@
         <v>8848</v>
       </c>
       <c r="H7" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20727,7 +20691,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20751,7 +20715,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20763,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20810,7 +20774,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20819,31 +20783,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="J1" t="s">
         <v>1658</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>1659</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>1660</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>1661</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>1662</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>1663</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="N1" t="s">
-        <v>1665</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1666</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20851,7 +20815,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20863,38 +20827,38 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D3" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="E3" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D4" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="E4" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
@@ -20911,13 +20875,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D6" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="E6" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20930,18 +20894,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D7" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="E7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20954,12 +20918,12 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="B8">
         <v>-21</v>
@@ -20971,13 +20935,13 @@
     </row>
     <row r="9" customFormat="1" spans="1:16">
       <c r="C9" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D9" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="E9" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20990,18 +20954,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P9" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:16">
       <c r="C10" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D10" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="E10" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -21014,7 +20978,7 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -21031,13 +20995,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D12" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="E12" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -21047,18 +21011,18 @@
         <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D13" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="E13" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -21068,18 +21032,18 @@
         <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D14" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="E14" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -21089,18 +21053,18 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="C15" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D15" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="E15" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -21110,42 +21074,42 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="D16" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P16" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="17" spans="3:16">
       <c r="D17" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P17" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="D18" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="E18" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -21158,7 +21122,7 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P18" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="19" spans="3:16">
@@ -21194,7 +21158,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21203,31 +21167,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I1" t="s">
         <v>1658</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>1659</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>1660</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>1661</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>1662</v>
       </c>
-      <c r="K1" t="s">
-        <v>1663</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1665</v>
-      </c>
       <c r="N1" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21247,46 +21211,46 @@
     </row>
     <row r="3" spans="1:15">
       <c r="C3" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="C5" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="C6" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="D6" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -21296,63 +21260,63 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O7" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="C8" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="C9" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="C10" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="C11" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="D11" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -21362,27 +21326,27 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="C12" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="D13" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21392,15 +21356,15 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="D14" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21410,15 +21374,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="D15" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -21428,15 +21392,15 @@
         <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="D16" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21446,36 +21410,36 @@
         <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -21485,27 +21449,27 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="C21" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="D21" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="E21" t="s">
         <v>582</v>
@@ -21521,15 +21485,15 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="D22" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="E22" t="s">
         <v>582</v>
@@ -21544,80 +21508,80 @@
     </row>
     <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="P23" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O24" t="s">
+        <v>1741</v>
+      </c>
+      <c r="P24" t="s">
+        <v>1742</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>1743</v>
+      </c>
+      <c r="R24" t="s">
         <v>1744</v>
-      </c>
-      <c r="P24" t="s">
-        <v>1745</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>1746</v>
-      </c>
-      <c r="R24" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O25" t="s">
+        <v>1746</v>
+      </c>
+      <c r="P25" t="s">
+        <v>1747</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>1748</v>
+      </c>
+      <c r="R25" t="s">
         <v>1749</v>
-      </c>
-      <c r="P25" t="s">
-        <v>1750</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>1751</v>
-      </c>
-      <c r="R25" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O26" t="s">
+        <v>1751</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1752</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>1753</v>
+      </c>
+      <c r="R26" t="s">
         <v>1754</v>
-      </c>
-      <c r="P26" t="s">
-        <v>1755</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>1756</v>
-      </c>
-      <c r="R26" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:18">
@@ -21634,10 +21598,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:18">
       <c r="C28" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="D28" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -21647,15 +21611,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="D29" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21665,27 +21629,27 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="C30" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="D30" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="B31">
         <v>-21</v>
@@ -21697,10 +21661,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="D32" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21710,15 +21674,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="3:15">
       <c r="C33" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="D33" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21728,22 +21692,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="3:15">
       <c r="C34" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="D34" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="35" spans="3:15">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="1826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1827">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4602,6 +4602,33 @@
     <t>九素云峰</t>
   </si>
   <si>
+    <t>骑御中</t>
+  </si>
+  <si>
+    <t>骑御</t>
+  </si>
+  <si>
+    <t>#FFFF00DD</t>
+  </si>
+  <si>
+    <t>#FFFF00</t>
+  </si>
+  <si>
+    <t>塔内</t>
+  </si>
+  <si>
+    <t>被防御塔瞄准</t>
+  </si>
+  <si>
+    <t>255,127,255,</t>
+  </si>
+  <si>
+    <t>抗摔</t>
+  </si>
+  <si>
+    <t>家园卫士出门抗摔</t>
+  </si>
+  <si>
     <t>隐匿草丛</t>
   </si>
   <si>
@@ -4614,27 +4641,6 @@
     <t>#FFCC00</t>
   </si>
   <si>
-    <t>塔内</t>
-  </si>
-  <si>
-    <t>被防御塔瞄准</t>
-  </si>
-  <si>
-    <t>255,127,255,</t>
-  </si>
-  <si>
-    <t>骑御中</t>
-  </si>
-  <si>
-    <t>骑御</t>
-  </si>
-  <si>
-    <t>#FFFF00DD</t>
-  </si>
-  <si>
-    <t>#FFFF00</t>
-  </si>
-  <si>
     <t>return {DEBUFF={</t>
   </si>
   <si>
@@ -4695,7 +4701,7 @@
     <t>消极参战</t>
   </si>
   <si>
-    <t>门派地图的数据</t>
+    <t>门派的数据</t>
   </si>
   <si>
     <t>标记.招式释放</t>
@@ -4803,9 +4809,6 @@
     <t>{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
-    <t>门派的数据</t>
-  </si>
-  <si>
     <t>出行大炮</t>
   </si>
   <si>
@@ -4977,34 +4980,34 @@
     <t>return {DOODAD={</t>
   </si>
   <si>
+    <t>联赛八强服务器宝堆</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="联赛·八强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>联赛四强服务器宝堆</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="联赛·四强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>联赛季军服务器宝堆</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="联赛·季军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>联赛亚军服务器宝堆</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="联赛·亚军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
     <t>联赛冠军服务器宝堆</t>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="联赛·冠军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>联赛亚军服务器宝堆</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="联赛·亚军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>联赛季军服务器宝堆</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="联赛·季军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>联赛四强服务器宝堆</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="联赛·四强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>联赛八强服务器宝堆</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="联赛·八强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>麒麟珠</t>
@@ -6752,7 +6755,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786703205000,</v>
+        <v>nTimeStamp = 1787145398000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8678,7 +8681,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8691,13 +8694,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B2" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8706,13 +8709,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B3" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C3" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8721,13 +8724,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B4" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C4" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8736,13 +8739,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B5" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C5" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8751,7 +8754,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8760,13 +8763,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B7" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C7" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8775,13 +8778,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B8" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C8" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8790,13 +8793,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B9" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="C9" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8805,13 +8808,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B10" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C10" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8820,13 +8823,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B11" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C11" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8835,7 +8838,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8844,10 +8847,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="C13" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8856,10 +8859,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C14" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8868,10 +8871,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="C15" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8880,10 +8883,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C16" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8892,10 +8895,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="C17" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8904,7 +8907,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8913,7 +8916,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8922,7 +8925,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8931,7 +8934,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8940,7 +8943,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8973,7 +8976,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8990,7 +8993,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -9004,7 +9007,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9018,7 +9021,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9038,7 +9041,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9057,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9068,7 +9071,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9079,7 +9082,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9095,7 +9098,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9110,7 +9113,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9121,7 +9124,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9132,7 +9135,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9148,7 +9151,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9163,7 +9166,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9174,7 +9177,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9185,7 +9188,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9201,7 +9204,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9216,7 +9219,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9227,7 +9230,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9238,7 +9241,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9254,7 +9257,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9269,7 +9272,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9280,7 +9283,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9291,7 +9294,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9307,7 +9310,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9322,7 +9325,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9333,7 +9336,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9344,7 +9347,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9360,7 +9363,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9375,7 +9378,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9386,7 +9389,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9397,7 +9400,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9413,7 +9416,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9428,7 +9431,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9439,7 +9442,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9450,7 +9453,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9466,7 +9469,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9481,7 +9484,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9492,7 +9495,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9503,7 +9506,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9519,7 +9522,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9534,7 +9537,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9545,7 +9548,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9556,7 +9559,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9572,7 +9575,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9587,7 +9590,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9598,7 +9601,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9609,7 +9612,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9625,7 +9628,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9640,7 +9643,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9651,7 +9654,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9662,7 +9665,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9678,7 +9681,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9693,7 +9696,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9704,7 +9707,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9715,7 +9718,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9731,7 +9734,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9746,7 +9749,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9757,7 +9760,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9768,7 +9771,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9784,7 +9787,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9799,7 +9802,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9810,7 +9813,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9821,7 +9824,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9837,7 +9840,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9852,7 +9855,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9863,7 +9866,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9874,7 +9877,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9890,7 +9893,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9905,7 +9908,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9916,7 +9919,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9927,7 +9930,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9943,7 +9946,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9958,7 +9961,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9969,7 +9972,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9980,7 +9983,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9996,7 +9999,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10011,7 +10014,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10022,7 +10025,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10033,7 +10036,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10049,7 +10052,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10064,7 +10067,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10075,7 +10078,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10086,7 +10089,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10102,7 +10105,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10117,7 +10120,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10128,7 +10131,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10139,7 +10142,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10155,7 +10158,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10170,7 +10173,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10181,7 +10184,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10192,7 +10195,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10208,7 +10211,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10223,7 +10226,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10234,7 +10237,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10245,7 +10248,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10261,7 +10264,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10275,7 +10278,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10285,7 +10288,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10295,7 +10298,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10311,7 +10314,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10331,7 +10334,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10351,7 +10354,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10371,7 +10374,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10391,7 +10394,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10411,7 +10414,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10431,7 +10434,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10451,7 +10454,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10471,7 +10474,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10491,7 +10494,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10511,7 +10514,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10531,7 +10534,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10551,7 +10554,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10571,7 +10574,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10591,7 +10594,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10611,7 +10614,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10631,7 +10634,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10651,7 +10654,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10671,7 +10674,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10691,7 +10694,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10711,7 +10714,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10731,7 +10734,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10751,7 +10754,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10771,7 +10774,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10791,7 +10794,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10811,7 +10814,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10831,7 +10834,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10851,7 +10854,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10871,7 +10874,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10891,7 +10894,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10911,7 +10914,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10931,7 +10934,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10951,7 +10954,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10971,7 +10974,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10991,7 +10994,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19006,8 +19009,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:AR8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="29" max="29" width="12.875" customWidth="1"/>
     <col min="30" max="30" width="13" customWidth="1"/>
@@ -19155,37 +19158,34 @@
         <v>689</v>
       </c>
       <c r="AQ2" t="str">
-        <f t="shared" ref="AQ2:AQ7" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AQ2:AQ8" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
         <v>[689]={</v>
       </c>
     </row>
     <row r="3" spans="1:44">
       <c r="C3">
-        <v>29097</v>
+        <v>244</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="G3" t="s">
+        <v>1517</v>
+      </c>
       <c r="K3" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="L3" t="s">
-        <v>668</v>
+        <v>604</v>
       </c>
       <c r="S3">
         <v>1</v>
       </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
       <c r="W3">
         <v>1</v>
       </c>
-      <c r="AH3" t="s">
-        <v>1518</v>
-      </c>
       <c r="AI3">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="s">
         <v>1519</v>
@@ -19194,17 +19194,14 @@
         <v>1520</v>
       </c>
       <c r="AL3">
-        <v>255</v>
-      </c>
-      <c r="AM3">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="AO3">
         <v>1</v>
       </c>
       <c r="AQ3" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29097,nLevel=1,szNote="隐匿草丛",col={255,204,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="藏",nPriority=3,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00DD",colScreenHead="#FFFF00",nColAlpha=221,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -19242,54 +19239,87 @@
     </row>
     <row r="5" spans="1:44">
       <c r="C5">
-        <v>244</v>
+        <v>29019</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>77</v>
+      </c>
       <c r="G5" t="s">
         <v>1524</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="K5" t="s">
         <v>1525</v>
       </c>
-      <c r="L5" t="s">
-        <v>604</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
-      <c r="AI5">
-        <v>40</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>1526</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>1527</v>
-      </c>
-      <c r="AL5">
-        <v>221</v>
-      </c>
-      <c r="AO5">
+      <c r="U5">
         <v>1</v>
       </c>
       <c r="AQ5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00DD",colScreenHead="#FFFF00",nColAlpha=221,bScreenHead=true,},},},</v>
+        <v>{dwID=29019,nLevel=1,nIcon=77,szName="抗摔",nScrutinyType=1,szNote="家园卫士出门抗摔",[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="6" spans="1:44">
+      <c r="C6">
+        <v>29097</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="L6" t="s">
+        <v>668</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="AI6">
+        <v>3</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>1528</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>1529</v>
+      </c>
+      <c r="AL6">
+        <v>255</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
       <c r="AQ6" t="str">
         <f t="shared" si="0"/>
-        <v>},},}</v>
+        <v>{dwID=29097,nLevel=1,szNote="隐匿草丛",col={255,204,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="藏",nPriority=3,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="7" spans="1:44">
       <c r="AQ7" t="str">
+        <f t="shared" si="0"/>
+        <v>},},}</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44">
+      <c r="AQ8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -19438,7 +19468,7 @@
         <v>1514</v>
       </c>
       <c r="AQ1" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="AR1" t="s">
         <v>316</v>
@@ -19467,10 +19497,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="L3" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="AQ3" t="str">
         <f t="shared" ref="AQ3:AQ12" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
@@ -19485,7 +19515,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="L4" t="s">
         <v>668</v>
@@ -19506,7 +19536,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="L5" t="s">
         <v>658</v>
@@ -19521,16 +19551,16 @@
         <v>1</v>
       </c>
       <c r="AH5" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="AI5">
         <v>15</v>
       </c>
       <c r="AJ5" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="AK5" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="AL5">
         <v>255</v>
@@ -19546,7 +19576,7 @@
         <v>{dwID=10260,nLevel=1,szNote="江逐月天",col={255,153,204,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="懵",nPriority=15,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,bAttention=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=7060,nFrame=8,nTime="3,敌方·江逐月天·{$sender};8,江逐月天·调息暂停",szName="敌方·江逐月天·{$sender}",nRefresh=8,key="江逐月天",},},},</v>
       </c>
       <c r="AR5" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="6" spans="1:45">
@@ -19557,13 +19587,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="L6" t="s">
         <v>1523</v>
@@ -19576,10 +19606,10 @@
         <v>{dwID=29176,nLevel=1,szName="封轻功",nScrutinyType=1,szNote="立足不稳",col={255,127,255,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=3442,nFrame=2,nTime=1800,szName="进入塔内·封轻功·不可骑乘",key="立足不稳",},{nClass=2,nIcon=3442,nFrame=5,nTime=2,szName="已出塔·可骑乘·可轻功",key="立足不稳",},},},</v>
       </c>
       <c r="AR6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="AS6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="7" spans="1:45">
@@ -19590,13 +19620,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L7" t="s">
         <v>1523</v>
@@ -19611,10 +19641,10 @@
         <v>37</v>
       </c>
       <c r="AJ7" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="AK7" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="AL7">
         <v>255</v>
@@ -19624,12 +19654,12 @@
         <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
       </c>
       <c r="AR7" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="8" spans="1:45">
       <c r="A8" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B8">
         <v>-2</v>
@@ -19650,7 +19680,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -19665,7 +19695,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:45">
       <c r="A10" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B10">
         <v>-21</v>
@@ -19686,7 +19716,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="U11">
         <v>1</v>
@@ -19753,43 +19783,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="M1" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N1" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="O1" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="P1" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="Q1" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="R1" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="S1" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="T1" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="U1" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="V1" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="W1" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="X1" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
@@ -19815,14 +19845,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="X3" t="str">
         <f>IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(D3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(D2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nIcon="&amp;E3&amp;",","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H3&gt;0,"nScrutinyType="&amp;H3&amp;",","")&amp;IF(I3&lt;&gt;"","tKungFu={"&amp;I3&amp;"},","")&amp;IF(J3&lt;&gt;"","szNote="""&amp;J3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;"[9]={"&amp;IF(L3&lt;&gt;"","tMark={"&amp;L3&amp;"},","")&amp;IF(M3&lt;&gt;"","szVoice="""&amp;M3&amp;""",","")&amp;IF(N3&gt;0,"bTeamChannel=true,","")&amp;IF(O3&gt;0,"bWhisperChannel=true,","")&amp;IF(P3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q3&lt;&gt;"","tMark={"&amp;Q3&amp;"},","")&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;IF(V3&gt;0,"bScreenHead=true,","")&amp;IF(W3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y3:AAC3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19833,14 +19863,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="X4" t="str">
         <f>IF(ISBLANK(B4)=FALSE,IF(ISBLANK(B3),"},["&amp;B4&amp;"]={","["&amp;B4&amp;"]={"),IF(AND(ISBLANK(B4),ISBLANK(C4),ISBLANK(D4),OR(ISBLANK(B3)=FALSE,ISBLANK(C3)=FALSE,ISBLANK(D3)=FALSE)),"},},}",IF(ISBLANK(C4),"","{dwID="&amp;C4&amp;","&amp;"nLevel="&amp;D4&amp;","&amp;IF(E4&gt;0,"nIcon="&amp;E4&amp;",","")&amp;IF(F4&lt;&gt;"","szName="""&amp;F4&amp;""",","")&amp;IF(G4&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H4&gt;0,"nScrutinyType="&amp;H4&amp;",","")&amp;IF(I4&lt;&gt;"","tKungFu={"&amp;I4&amp;"},","")&amp;IF(J4&lt;&gt;"","szNote="""&amp;J4&amp;""",","")&amp;IF(K4&lt;&gt;"","col={"&amp;K4&amp;"},","")&amp;"[9]={"&amp;IF(L4&lt;&gt;"","tMark={"&amp;L4&amp;"},","")&amp;IF(M4&lt;&gt;"","szVoice="""&amp;M4&amp;""",","")&amp;IF(N4&gt;0,"bTeamChannel=true,","")&amp;IF(O4&gt;0,"bWhisperChannel=true,","")&amp;IF(P4&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q4&lt;&gt;"","tMark={"&amp;Q4&amp;"},","")&amp;IF(R4&lt;&gt;"","szVoice="""&amp;R4&amp;""",","")&amp;IF(S4&gt;0,"bTeamChannel=true,","")&amp;IF(T4&gt;0,"bWhisperChannel=true,","")&amp;IF(U4&gt;0,"bCenterAlarm=true,","")&amp;IF(V4&gt;0,"bScreenHead=true,","")&amp;IF(W4&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y4&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y4:AAC4)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19851,14 +19881,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="X5" t="str">
         <f>IF(ISBLANK(B5)=FALSE,IF(ISBLANK(B4),"},["&amp;B5&amp;"]={","["&amp;B5&amp;"]={"),IF(AND(ISBLANK(B5),ISBLANK(C5),ISBLANK(D5),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C5),"","{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nIcon="&amp;E5&amp;",","")&amp;IF(F5&lt;&gt;"","szName="""&amp;F5&amp;""",","")&amp;IF(G5&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H5&gt;0,"nScrutinyType="&amp;H5&amp;",","")&amp;IF(I5&lt;&gt;"","tKungFu={"&amp;I5&amp;"},","")&amp;IF(J5&lt;&gt;"","szNote="""&amp;J5&amp;""",","")&amp;IF(K5&lt;&gt;"","col={"&amp;K5&amp;"},","")&amp;"[9]={"&amp;IF(L5&lt;&gt;"","tMark={"&amp;L5&amp;"},","")&amp;IF(M5&lt;&gt;"","szVoice="""&amp;M5&amp;""",","")&amp;IF(N5&gt;0,"bTeamChannel=true,","")&amp;IF(O5&gt;0,"bWhisperChannel=true,","")&amp;IF(P5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q5&lt;&gt;"","tMark={"&amp;Q5&amp;"},","")&amp;IF(R5&lt;&gt;"","szVoice="""&amp;R5&amp;""",","")&amp;IF(S5&gt;0,"bTeamChannel=true,","")&amp;IF(T5&gt;0,"bWhisperChannel=true,","")&amp;IF(U5&gt;0,"bCenterAlarm=true,","")&amp;IF(V5&gt;0,"bScreenHead=true,","")&amp;IF(W5&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y5:AAC5)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19897,10 +19927,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F1" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19915,43 +19945,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="L1" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="M1" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="N1" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="O1" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="P1" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="Q1" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="R1" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="S1" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="T1" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="U1" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -19959,7 +19989,7 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -19977,7 +20007,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -19986,7 +20016,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -19995,7 +20025,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1584</v>
+        <v>1550</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -20013,7 +20043,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -20022,7 +20052,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -20049,10 +20079,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="V7" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -20067,16 +20097,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="J8" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -20091,10 +20121,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="V9" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20109,10 +20139,10 @@
         <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="V10" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20127,7 +20157,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20136,7 +20166,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20151,7 +20181,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20160,7 +20190,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20175,7 +20205,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20184,7 +20214,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20199,7 +20229,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="J14" t="s">
         <v>582</v>
@@ -20208,7 +20238,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
@@ -20223,7 +20253,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20232,17 +20262,17 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="Y15" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20253,7 +20283,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="J16" t="s">
         <v>640</v>
@@ -20262,14 +20292,14 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X16" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="3:25">
@@ -20280,10 +20310,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="V17" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20298,7 +20328,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20307,7 +20337,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20322,7 +20352,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20331,7 +20361,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20346,7 +20376,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="J20" t="s">
         <v>582</v>
@@ -20355,7 +20385,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
@@ -20370,7 +20400,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="J21" t="s">
         <v>582</v>
@@ -20379,7 +20409,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -20394,7 +20424,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20403,17 +20433,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="Y22" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20424,7 +20454,7 @@
         <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="J23" t="s">
         <v>640</v>
@@ -20433,14 +20463,14 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X23" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="24" spans="3:25">
@@ -20451,7 +20481,7 @@
         <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="J24" t="s">
         <v>640</v>
@@ -20460,17 +20490,17 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X24" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Y24" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="25" spans="3:25">
@@ -20481,10 +20511,10 @@
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="V25" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
@@ -20527,10 +20557,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="E1" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20545,46 +20575,49 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="K1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="L1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="M1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="N1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="O1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="P1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="Q1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="R1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="S1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:22">
+      <c r="A2" t="s">
+        <v>1548</v>
+      </c>
       <c r="B2">
         <v>-2</v>
       </c>
@@ -20595,10 +20628,10 @@
     </row>
     <row r="3" spans="1:22">
       <c r="C3">
-        <v>8852</v>
+        <v>8848</v>
       </c>
       <c r="H3" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20607,19 +20640,19 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=8852,szNote="联赛冠军服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·冠军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8848,szNote="联赛八强服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·八强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="C4">
-        <v>8851</v>
+        <v>8849</v>
       </c>
       <c r="H4" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20628,11 +20661,11 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8851,szNote="联赛亚军服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·亚军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8849,szNote="联赛四强服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·四强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -20640,7 +20673,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20649,7 +20682,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20658,10 +20691,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="C6">
-        <v>8849</v>
+        <v>8851</v>
       </c>
       <c r="H6" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20670,19 +20703,19 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8849,szNote="联赛四强服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·四强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8851,szNote="联赛亚军服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·亚军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="C7">
-        <v>8848</v>
+        <v>8852</v>
       </c>
       <c r="H7" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20691,11 +20724,11 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8848,szNote="联赛八强服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·八强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8852,szNote="联赛冠军服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·冠军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -20715,7 +20748,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20727,7 +20760,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20747,6 +20780,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A3:V7">
+    <sortCondition ref="A3:A7" descending="1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -20774,7 +20810,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20783,31 +20819,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="I1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="J1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="K1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="L1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="M1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="N1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="O1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20815,7 +20851,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20827,43 +20863,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="E3" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="E4" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
       <c r="A5" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B5">
         <v>-2</v>
@@ -20875,13 +20911,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D6" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="E6" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20894,18 +20930,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D7" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="E7" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20918,12 +20954,12 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>1584</v>
+        <v>1550</v>
       </c>
       <c r="B8">
         <v>-21</v>
@@ -20935,13 +20971,13 @@
     </row>
     <row r="9" customFormat="1" spans="1:16">
       <c r="C9" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D9" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="E9" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20954,18 +20990,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P9" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:16">
       <c r="C10" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D10" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="E10" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -20978,7 +21014,7 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -20995,13 +21031,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D12" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E12" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -21011,18 +21047,18 @@
         <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D13" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="E13" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -21032,18 +21068,18 @@
         <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D14" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="E14" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -21053,18 +21089,18 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="C15" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D15" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="E15" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -21074,42 +21110,42 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="D16" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P16" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="17" spans="3:16">
       <c r="D17" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P17" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D18" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="E18" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -21122,7 +21158,7 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P18" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="19" spans="3:16">
@@ -21158,7 +21194,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21167,31 +21203,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="G1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="I1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="J1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="K1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="L1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="M1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="N1" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21211,46 +21247,46 @@
     </row>
     <row r="3" spans="1:15">
       <c r="C3" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="C5" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="C6" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D6" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -21260,63 +21296,63 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="C8" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="C9" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="C10" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="C11" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="D11" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -21326,27 +21362,27 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="C12" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="D13" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21356,15 +21392,15 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="D14" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21374,15 +21410,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="D15" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -21392,15 +21428,15 @@
         <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="D16" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21410,36 +21446,36 @@
         <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -21449,27 +21485,27 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="C21" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="D21" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="E21" t="s">
         <v>582</v>
@@ -21485,15 +21521,15 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D22" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E22" t="s">
         <v>582</v>
@@ -21508,85 +21544,85 @@
     </row>
     <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="P23" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="P24" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="Q24" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="R24" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="P25" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="Q25" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="R25" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="P26" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="Q26" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="R26" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:18">
       <c r="A27" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B27">
         <v>-2</v>
@@ -21598,10 +21634,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:18">
       <c r="C28" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="D28" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -21611,15 +21647,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D29" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21629,27 +21665,27 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="C30" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D30" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>1584</v>
+        <v>1550</v>
       </c>
       <c r="B31">
         <v>-21</v>
@@ -21661,10 +21697,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="D32" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21674,15 +21710,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="3:15">
       <c r="C33" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D33" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21692,22 +21728,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="3:15">
       <c r="C34" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D34" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="35" spans="3:15">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1828">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4620,58 +4620,61 @@
     <t>被防御塔瞄准</t>
   </si>
   <si>
+    <t>153,26,26,</t>
+  </si>
+  <si>
+    <t>抗摔</t>
+  </si>
+  <si>
+    <t>家园卫士出门抗摔</t>
+  </si>
+  <si>
+    <t>隐匿草丛</t>
+  </si>
+  <si>
+    <t>藏</t>
+  </si>
+  <si>
+    <t>#FFCC00FF</t>
+  </si>
+  <si>
+    <t>#FFCC00</t>
+  </si>
+  <si>
+    <t>return {DEBUFF={</t>
+  </si>
+  <si>
+    <t>九素化生·15尺伤害距离</t>
+  </si>
+  <si>
+    <t>128,238,255,</t>
+  </si>
+  <si>
+    <t>麒麟佑</t>
+  </si>
+  <si>
+    <t>江逐月天</t>
+  </si>
+  <si>
+    <t>懵</t>
+  </si>
+  <si>
+    <t>#FF99CCFF</t>
+  </si>
+  <si>
+    <t>#FF99CC</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=7060,nFrame=8,nTime="3,敌方·江逐月天·{$sender};8,江逐月天·调息暂停",szName="敌方·江逐月天·{$sender}",nRefresh=8,key="江逐月天",},</t>
+  </si>
+  <si>
+    <t>封轻功</t>
+  </si>
+  <si>
+    <t>立足不稳</t>
+  </si>
+  <si>
     <t>255,127,255,</t>
-  </si>
-  <si>
-    <t>抗摔</t>
-  </si>
-  <si>
-    <t>家园卫士出门抗摔</t>
-  </si>
-  <si>
-    <t>隐匿草丛</t>
-  </si>
-  <si>
-    <t>藏</t>
-  </si>
-  <si>
-    <t>#FFCC00FF</t>
-  </si>
-  <si>
-    <t>#FFCC00</t>
-  </si>
-  <si>
-    <t>return {DEBUFF={</t>
-  </si>
-  <si>
-    <t>九素化生·15尺伤害距离</t>
-  </si>
-  <si>
-    <t>128,238,255,</t>
-  </si>
-  <si>
-    <t>麒麟佑</t>
-  </si>
-  <si>
-    <t>江逐月天</t>
-  </si>
-  <si>
-    <t>懵</t>
-  </si>
-  <si>
-    <t>#FF99CCFF</t>
-  </si>
-  <si>
-    <t>#FF99CC</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=7060,nFrame=8,nTime="3,敌方·江逐月天·{$sender};8,江逐月天·调息暂停",szName="敌方·江逐月天·{$sender}",nRefresh=8,key="江逐月天",},</t>
-  </si>
-  <si>
-    <t>封轻功</t>
-  </si>
-  <si>
-    <t>立足不稳</t>
   </si>
   <si>
     <t>{nClass=1,nIcon=3442,nFrame=2,nTime=1800,szName="进入塔内·封轻功·不可骑乘",key="立足不稳",},</t>
@@ -6755,7 +6758,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1787145398000,</v>
+        <v>nTimeStamp = 1787747567000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8681,7 +8684,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8694,13 +8697,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="C2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8709,13 +8712,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B3" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C3" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8724,13 +8727,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B4" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="C4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8739,13 +8742,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B5" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8754,7 +8757,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8763,13 +8766,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B7" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="C7" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8778,13 +8781,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B8" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C8" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8793,13 +8796,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B9" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C9" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8808,13 +8811,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B10" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C10" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8823,13 +8826,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B11" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C11" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8838,7 +8841,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8847,10 +8850,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C13" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8859,10 +8862,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="C14" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8871,10 +8874,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C15" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8883,10 +8886,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="C16" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8895,10 +8898,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C17" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8907,7 +8910,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8916,7 +8919,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8925,7 +8928,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8934,7 +8937,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8943,7 +8946,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8976,7 +8979,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8993,7 +8996,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -9007,7 +9010,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9021,7 +9024,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9041,7 +9044,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9060,7 +9063,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9071,7 +9074,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9082,7 +9085,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9098,7 +9101,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9113,7 +9116,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9124,7 +9127,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9135,7 +9138,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9151,7 +9154,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9166,7 +9169,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9177,7 +9180,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9188,7 +9191,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9204,7 +9207,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9219,7 +9222,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9230,7 +9233,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9241,7 +9244,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9257,7 +9260,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9272,7 +9275,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9283,7 +9286,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9294,7 +9297,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9310,7 +9313,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9325,7 +9328,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9336,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9347,7 +9350,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9363,7 +9366,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9378,7 +9381,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9389,7 +9392,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9400,7 +9403,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9416,7 +9419,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9431,7 +9434,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9442,7 +9445,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9453,7 +9456,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9469,7 +9472,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9484,7 +9487,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9495,7 +9498,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9506,7 +9509,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9522,7 +9525,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9537,7 +9540,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9548,7 +9551,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9559,7 +9562,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9575,7 +9578,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9590,7 +9593,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9601,7 +9604,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9612,7 +9615,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9628,7 +9631,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9643,7 +9646,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9654,7 +9657,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9665,7 +9668,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9681,7 +9684,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9696,7 +9699,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9707,7 +9710,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9718,7 +9721,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9734,7 +9737,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9749,7 +9752,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9760,7 +9763,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9771,7 +9774,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9787,7 +9790,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9802,7 +9805,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9813,7 +9816,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9824,7 +9827,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9840,7 +9843,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9855,7 +9858,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9866,7 +9869,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9877,7 +9880,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9893,7 +9896,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9908,7 +9911,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9919,7 +9922,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9930,7 +9933,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9946,7 +9949,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9961,7 +9964,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9972,7 +9975,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9983,7 +9986,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -9999,7 +10002,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10014,7 +10017,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10025,7 +10028,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10036,7 +10039,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10052,7 +10055,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10067,7 +10070,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10078,7 +10081,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10089,7 +10092,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10105,7 +10108,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10120,7 +10123,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10131,7 +10134,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10142,7 +10145,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10158,7 +10161,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10173,7 +10176,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10184,7 +10187,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10195,7 +10198,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10211,7 +10214,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10226,7 +10229,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10237,7 +10240,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10248,7 +10251,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10264,7 +10267,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10278,7 +10281,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10288,7 +10291,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10298,7 +10301,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10314,7 +10317,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10334,7 +10337,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10354,7 +10357,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10374,7 +10377,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10394,7 +10397,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10414,7 +10417,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10434,7 +10437,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10454,7 +10457,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10474,7 +10477,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10494,7 +10497,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10514,7 +10517,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10534,7 +10537,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10554,7 +10557,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10574,7 +10577,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10594,7 +10597,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10614,7 +10617,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10634,7 +10637,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10654,7 +10657,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10674,7 +10677,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10694,7 +10697,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10714,7 +10717,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10734,7 +10737,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10754,7 +10757,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10774,7 +10777,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10794,7 +10797,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10814,7 +10817,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10834,7 +10837,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10854,7 +10857,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10874,7 +10877,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10894,7 +10897,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10914,7 +10917,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10934,7 +10937,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10954,7 +10957,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10974,7 +10977,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10994,7 +10997,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19158,7 +19161,7 @@
         <v>689</v>
       </c>
       <c r="AQ2" t="str">
-        <f t="shared" ref="AQ2:AQ8" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
+        <f>IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
         <v>[689]={</v>
       </c>
     </row>
@@ -19200,7 +19203,7 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00DD",colScreenHead="#FFFF00",nColAlpha=221,bScreenHead=true,},},},</v>
       </c>
     </row>
@@ -19233,8 +19236,8 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=29048,nLevel=1,nIcon=3293,szName="塔内",nScrutinyType=1,szNote="被防御塔瞄准",col={255,127,255,},[1]={bBuffList=true,bFullScreen=true,},[2]={},},</v>
+        <f>IF(B4&lt;&gt;"",IF(IFERROR(VALUE(C3),0)&lt;=0,"["&amp;B4&amp;"]={","},["&amp;B4&amp;"]={"),IF(C4&gt;0,"{dwID="&amp;C4&amp;","&amp;"nLevel="&amp;D4&amp;","&amp;IF(E4&gt;0,"nCount="&amp;E4&amp;",","")&amp;IF(F4&gt;0,"nIcon="&amp;F4&amp;",","")&amp;IF(G4&lt;&gt;"","szName="""&amp;G4&amp;""",","")&amp;IF(H4&gt;0,"bCheckLevel=true,","")&amp;IF(I4&gt;0,"nScrutinyType="&amp;I4&amp;",","")&amp;IF(J4&lt;&gt;"","tKungFu={"&amp;J4&amp;"},","")&amp;IF(K4&lt;&gt;"","szNote="""&amp;K4&amp;""",","")&amp;IF(L4&lt;&gt;"","col={"&amp;L4&amp;"},","")&amp;"[1]={"&amp;IF(M4&lt;&gt;"","tMark={"&amp;M4&amp;"},","")&amp;IF(N4&lt;&gt;"","szVoice="""&amp;N4&amp;""",","")&amp;IF(O4&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P4&gt;0,"bTeamChannel=true,","")&amp;IF(Q4&gt;0,"bWhisperChannel=true,","")&amp;IF(R4&gt;0,"bCenterAlarm=true,","")&amp;IF(S4&gt;0,"bScreenHead=true,","")&amp;IF(T4&gt;0,"bPartyBuffList=true,","")&amp;IF(U4&gt;0,"bBuffList=true,","")&amp;IF(V4&gt;0,"bFullScreen=true,","")&amp;IF(W4&gt;0,"bTeamPanel=true,","")&amp;IF(X4&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y4&lt;&gt;"","szVoice="""&amp;Y4&amp;""",","")&amp;IF(Z4&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA4&gt;0,"bTeamChannel=true,","")&amp;IF(AB4&gt;0,"bWhisperChannel=true,","")&amp;IF(AC4&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD4&gt;0,AH4&lt;&gt;"",AI4&gt;0,AJ4&lt;&gt;"",AK4&lt;&gt;"",AL4&gt;0,AM4&gt;0,AN4&gt;0,AO4&gt;0),"aCataclysmBuff={{"&amp;IF(AD4&gt;0,"nStackNum="&amp;AD4&amp;",","")&amp;IF(AE4&lt;&gt;"","szStackOp="""&amp;AE4&amp;""",","")&amp;IF(AF4&gt;0,"bOnlyMine=true,","")&amp;IF(AG4&gt;0,"bOnlyMe=true,","")&amp;IF(AH4&lt;&gt;"","szReminder="""&amp;AH4&amp;""",","")&amp;IF(AI4&gt;0,"nPriority="&amp;AI4&amp;",","")&amp;IF(AJ4&lt;&gt;"","col="""&amp;AJ4&amp;""",","")&amp;IF(AK4&lt;&gt;"","colScreenHead="""&amp;AK4&amp;""",","")&amp;IF(AL4&gt;0,"nColAlpha="&amp;AL4&amp;",","")&amp;IF(AM4&gt;0,"bAttention=true,","")&amp;IF(AN4&gt;0,"bCaution=true,","")&amp;IF(AO4&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP4&amp;"},","")&amp;IF(AR4&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR4:AAC4)&amp;"},","")&amp;"},",IF(C3&gt;0,"},","")&amp;IF(AND(B4="",C4="",OR(B3&lt;&gt;"",C3&lt;&gt;"")),"},}","")))</f>
+        <v>{dwID=29048,nLevel=1,nIcon=3293,szName="塔内",nScrutinyType=1,szNote="被防御塔瞄准",col={153,26,26,},[1]={bBuffList=true,bFullScreen=true,},[2]={},},</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -19260,7 +19263,7 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B5&lt;&gt;"",IF(IFERROR(VALUE(C4),0)&lt;=0,"["&amp;B5&amp;"]={","},["&amp;B5&amp;"]={"),IF(C5&gt;0,"{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nCount="&amp;E5&amp;",","")&amp;IF(F5&gt;0,"nIcon="&amp;F5&amp;",","")&amp;IF(G5&lt;&gt;"","szName="""&amp;G5&amp;""",","")&amp;IF(H5&gt;0,"bCheckLevel=true,","")&amp;IF(I5&gt;0,"nScrutinyType="&amp;I5&amp;",","")&amp;IF(J5&lt;&gt;"","tKungFu={"&amp;J5&amp;"},","")&amp;IF(K5&lt;&gt;"","szNote="""&amp;K5&amp;""",","")&amp;IF(L5&lt;&gt;"","col={"&amp;L5&amp;"},","")&amp;"[1]={"&amp;IF(M5&lt;&gt;"","tMark={"&amp;M5&amp;"},","")&amp;IF(N5&lt;&gt;"","szVoice="""&amp;N5&amp;""",","")&amp;IF(O5&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P5&gt;0,"bTeamChannel=true,","")&amp;IF(Q5&gt;0,"bWhisperChannel=true,","")&amp;IF(R5&gt;0,"bCenterAlarm=true,","")&amp;IF(S5&gt;0,"bScreenHead=true,","")&amp;IF(T5&gt;0,"bPartyBuffList=true,","")&amp;IF(U5&gt;0,"bBuffList=true,","")&amp;IF(V5&gt;0,"bFullScreen=true,","")&amp;IF(W5&gt;0,"bTeamPanel=true,","")&amp;IF(X5&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y5&lt;&gt;"","szVoice="""&amp;Y5&amp;""",","")&amp;IF(Z5&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA5&gt;0,"bTeamChannel=true,","")&amp;IF(AB5&gt;0,"bWhisperChannel=true,","")&amp;IF(AC5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD5&gt;0,AH5&lt;&gt;"",AI5&gt;0,AJ5&lt;&gt;"",AK5&lt;&gt;"",AL5&gt;0,AM5&gt;0,AN5&gt;0,AO5&gt;0),"aCataclysmBuff={{"&amp;IF(AD5&gt;0,"nStackNum="&amp;AD5&amp;",","")&amp;IF(AE5&lt;&gt;"","szStackOp="""&amp;AE5&amp;""",","")&amp;IF(AF5&gt;0,"bOnlyMine=true,","")&amp;IF(AG5&gt;0,"bOnlyMe=true,","")&amp;IF(AH5&lt;&gt;"","szReminder="""&amp;AH5&amp;""",","")&amp;IF(AI5&gt;0,"nPriority="&amp;AI5&amp;",","")&amp;IF(AJ5&lt;&gt;"","col="""&amp;AJ5&amp;""",","")&amp;IF(AK5&lt;&gt;"","colScreenHead="""&amp;AK5&amp;""",","")&amp;IF(AL5&gt;0,"nColAlpha="&amp;AL5&amp;",","")&amp;IF(AM5&gt;0,"bAttention=true,","")&amp;IF(AN5&gt;0,"bCaution=true,","")&amp;IF(AO5&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP5&amp;"},","")&amp;IF(AR5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR5:AAC5)&amp;"},","")&amp;"},",IF(C4&gt;0,"},","")&amp;IF(AND(B5="",C5="",OR(B4&lt;&gt;"",C4&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=29019,nLevel=1,nIcon=77,szName="抗摔",nScrutinyType=1,szNote="家园卫士出门抗摔",[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
@@ -19308,19 +19311,19 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B6&lt;&gt;"",IF(IFERROR(VALUE(C5),0)&lt;=0,"["&amp;B6&amp;"]={","},["&amp;B6&amp;"]={"),IF(C6&gt;0,"{dwID="&amp;C6&amp;","&amp;"nLevel="&amp;D6&amp;","&amp;IF(E6&gt;0,"nCount="&amp;E6&amp;",","")&amp;IF(F6&gt;0,"nIcon="&amp;F6&amp;",","")&amp;IF(G6&lt;&gt;"","szName="""&amp;G6&amp;""",","")&amp;IF(H6&gt;0,"bCheckLevel=true,","")&amp;IF(I6&gt;0,"nScrutinyType="&amp;I6&amp;",","")&amp;IF(J6&lt;&gt;"","tKungFu={"&amp;J6&amp;"},","")&amp;IF(K6&lt;&gt;"","szNote="""&amp;K6&amp;""",","")&amp;IF(L6&lt;&gt;"","col={"&amp;L6&amp;"},","")&amp;"[1]={"&amp;IF(M6&lt;&gt;"","tMark={"&amp;M6&amp;"},","")&amp;IF(N6&lt;&gt;"","szVoice="""&amp;N6&amp;""",","")&amp;IF(O6&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P6&gt;0,"bTeamChannel=true,","")&amp;IF(Q6&gt;0,"bWhisperChannel=true,","")&amp;IF(R6&gt;0,"bCenterAlarm=true,","")&amp;IF(S6&gt;0,"bScreenHead=true,","")&amp;IF(T6&gt;0,"bPartyBuffList=true,","")&amp;IF(U6&gt;0,"bBuffList=true,","")&amp;IF(V6&gt;0,"bFullScreen=true,","")&amp;IF(W6&gt;0,"bTeamPanel=true,","")&amp;IF(X6&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y6&lt;&gt;"","szVoice="""&amp;Y6&amp;""",","")&amp;IF(Z6&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA6&gt;0,"bTeamChannel=true,","")&amp;IF(AB6&gt;0,"bWhisperChannel=true,","")&amp;IF(AC6&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD6&gt;0,AH6&lt;&gt;"",AI6&gt;0,AJ6&lt;&gt;"",AK6&lt;&gt;"",AL6&gt;0,AM6&gt;0,AN6&gt;0,AO6&gt;0),"aCataclysmBuff={{"&amp;IF(AD6&gt;0,"nStackNum="&amp;AD6&amp;",","")&amp;IF(AE6&lt;&gt;"","szStackOp="""&amp;AE6&amp;""",","")&amp;IF(AF6&gt;0,"bOnlyMine=true,","")&amp;IF(AG6&gt;0,"bOnlyMe=true,","")&amp;IF(AH6&lt;&gt;"","szReminder="""&amp;AH6&amp;""",","")&amp;IF(AI6&gt;0,"nPriority="&amp;AI6&amp;",","")&amp;IF(AJ6&lt;&gt;"","col="""&amp;AJ6&amp;""",","")&amp;IF(AK6&lt;&gt;"","colScreenHead="""&amp;AK6&amp;""",","")&amp;IF(AL6&gt;0,"nColAlpha="&amp;AL6&amp;",","")&amp;IF(AM6&gt;0,"bAttention=true,","")&amp;IF(AN6&gt;0,"bCaution=true,","")&amp;IF(AO6&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP6&amp;"},","")&amp;IF(AR6&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR6:AAC6)&amp;"},","")&amp;"},",IF(C5&gt;0,"},","")&amp;IF(AND(B6="",C6="",OR(B5&lt;&gt;"",C5&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=29097,nLevel=1,szNote="隐匿草丛",col={255,204,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="藏",nPriority=3,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="7" spans="1:44">
       <c r="AQ7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B7&lt;&gt;"",IF(IFERROR(VALUE(C6),0)&lt;=0,"["&amp;B7&amp;"]={","},["&amp;B7&amp;"]={"),IF(C7&gt;0,"{dwID="&amp;C7&amp;","&amp;"nLevel="&amp;D7&amp;","&amp;IF(E7&gt;0,"nCount="&amp;E7&amp;",","")&amp;IF(F7&gt;0,"nIcon="&amp;F7&amp;",","")&amp;IF(G7&lt;&gt;"","szName="""&amp;G7&amp;""",","")&amp;IF(H7&gt;0,"bCheckLevel=true,","")&amp;IF(I7&gt;0,"nScrutinyType="&amp;I7&amp;",","")&amp;IF(J7&lt;&gt;"","tKungFu={"&amp;J7&amp;"},","")&amp;IF(K7&lt;&gt;"","szNote="""&amp;K7&amp;""",","")&amp;IF(L7&lt;&gt;"","col={"&amp;L7&amp;"},","")&amp;"[1]={"&amp;IF(M7&lt;&gt;"","tMark={"&amp;M7&amp;"},","")&amp;IF(N7&lt;&gt;"","szVoice="""&amp;N7&amp;""",","")&amp;IF(O7&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P7&gt;0,"bTeamChannel=true,","")&amp;IF(Q7&gt;0,"bWhisperChannel=true,","")&amp;IF(R7&gt;0,"bCenterAlarm=true,","")&amp;IF(S7&gt;0,"bScreenHead=true,","")&amp;IF(T7&gt;0,"bPartyBuffList=true,","")&amp;IF(U7&gt;0,"bBuffList=true,","")&amp;IF(V7&gt;0,"bFullScreen=true,","")&amp;IF(W7&gt;0,"bTeamPanel=true,","")&amp;IF(X7&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y7&lt;&gt;"","szVoice="""&amp;Y7&amp;""",","")&amp;IF(Z7&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA7&gt;0,"bTeamChannel=true,","")&amp;IF(AB7&gt;0,"bWhisperChannel=true,","")&amp;IF(AC7&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD7&gt;0,AH7&lt;&gt;"",AI7&gt;0,AJ7&lt;&gt;"",AK7&lt;&gt;"",AL7&gt;0,AM7&gt;0,AN7&gt;0,AO7&gt;0),"aCataclysmBuff={{"&amp;IF(AD7&gt;0,"nStackNum="&amp;AD7&amp;",","")&amp;IF(AE7&lt;&gt;"","szStackOp="""&amp;AE7&amp;""",","")&amp;IF(AF7&gt;0,"bOnlyMine=true,","")&amp;IF(AG7&gt;0,"bOnlyMe=true,","")&amp;IF(AH7&lt;&gt;"","szReminder="""&amp;AH7&amp;""",","")&amp;IF(AI7&gt;0,"nPriority="&amp;AI7&amp;",","")&amp;IF(AJ7&lt;&gt;"","col="""&amp;AJ7&amp;""",","")&amp;IF(AK7&lt;&gt;"","colScreenHead="""&amp;AK7&amp;""",","")&amp;IF(AL7&gt;0,"nColAlpha="&amp;AL7&amp;",","")&amp;IF(AM7&gt;0,"bAttention=true,","")&amp;IF(AN7&gt;0,"bCaution=true,","")&amp;IF(AO7&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP7&amp;"},","")&amp;IF(AR7&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR7:AAC7)&amp;"},","")&amp;"},",IF(C6&gt;0,"},","")&amp;IF(AND(B7="",C7="",OR(B6&lt;&gt;"",C6&lt;&gt;"")),"},}","")))</f>
         <v>},},}</v>
       </c>
     </row>
     <row r="8" spans="1:44">
       <c r="AQ8" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B8&lt;&gt;"",IF(IFERROR(VALUE(C7),0)&lt;=0,"["&amp;B8&amp;"]={","},["&amp;B8&amp;"]={"),IF(C8&gt;0,"{dwID="&amp;C8&amp;","&amp;"nLevel="&amp;D8&amp;","&amp;IF(E8&gt;0,"nCount="&amp;E8&amp;",","")&amp;IF(F8&gt;0,"nIcon="&amp;F8&amp;",","")&amp;IF(G8&lt;&gt;"","szName="""&amp;G8&amp;""",","")&amp;IF(H8&gt;0,"bCheckLevel=true,","")&amp;IF(I8&gt;0,"nScrutinyType="&amp;I8&amp;",","")&amp;IF(J8&lt;&gt;"","tKungFu={"&amp;J8&amp;"},","")&amp;IF(K8&lt;&gt;"","szNote="""&amp;K8&amp;""",","")&amp;IF(L8&lt;&gt;"","col={"&amp;L8&amp;"},","")&amp;"[1]={"&amp;IF(M8&lt;&gt;"","tMark={"&amp;M8&amp;"},","")&amp;IF(N8&lt;&gt;"","szVoice="""&amp;N8&amp;""",","")&amp;IF(O8&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P8&gt;0,"bTeamChannel=true,","")&amp;IF(Q8&gt;0,"bWhisperChannel=true,","")&amp;IF(R8&gt;0,"bCenterAlarm=true,","")&amp;IF(S8&gt;0,"bScreenHead=true,","")&amp;IF(T8&gt;0,"bPartyBuffList=true,","")&amp;IF(U8&gt;0,"bBuffList=true,","")&amp;IF(V8&gt;0,"bFullScreen=true,","")&amp;IF(W8&gt;0,"bTeamPanel=true,","")&amp;IF(X8&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y8&lt;&gt;"","szVoice="""&amp;Y8&amp;""",","")&amp;IF(Z8&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA8&gt;0,"bTeamChannel=true,","")&amp;IF(AB8&gt;0,"bWhisperChannel=true,","")&amp;IF(AC8&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD8&gt;0,AH8&lt;&gt;"",AI8&gt;0,AJ8&lt;&gt;"",AK8&lt;&gt;"",AL8&gt;0,AM8&gt;0,AN8&gt;0,AO8&gt;0),"aCataclysmBuff={{"&amp;IF(AD8&gt;0,"nStackNum="&amp;AD8&amp;",","")&amp;IF(AE8&lt;&gt;"","szStackOp="""&amp;AE8&amp;""",","")&amp;IF(AF8&gt;0,"bOnlyMine=true,","")&amp;IF(AG8&gt;0,"bOnlyMe=true,","")&amp;IF(AH8&lt;&gt;"","szReminder="""&amp;AH8&amp;""",","")&amp;IF(AI8&gt;0,"nPriority="&amp;AI8&amp;",","")&amp;IF(AJ8&lt;&gt;"","col="""&amp;AJ8&amp;""",","")&amp;IF(AK8&lt;&gt;"","colScreenHead="""&amp;AK8&amp;""",","")&amp;IF(AL8&gt;0,"nColAlpha="&amp;AL8&amp;",","")&amp;IF(AM8&gt;0,"bAttention=true,","")&amp;IF(AN8&gt;0,"bCaution=true,","")&amp;IF(AO8&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP8&amp;"},","")&amp;IF(AR8&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR8:AAC8)&amp;"},","")&amp;"},",IF(C7&gt;0,"},","")&amp;IF(AND(B8="",C8="",OR(B7&lt;&gt;"",C7&lt;&gt;"")),"},}","")))</f>
         <v/>
       </c>
     </row>
@@ -19596,7 +19599,7 @@
         <v>1540</v>
       </c>
       <c r="L6" t="s">
-        <v>1523</v>
+        <v>1541</v>
       </c>
       <c r="U6">
         <v>1</v>
@@ -19606,10 +19609,10 @@
         <v>{dwID=29176,nLevel=1,szName="封轻功",nScrutinyType=1,szNote="立足不稳",col={255,127,255,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=3442,nFrame=2,nTime=1800,szName="进入塔内·封轻功·不可骑乘",key="立足不稳",},{nClass=2,nIcon=3442,nFrame=5,nTime=2,szName="已出塔·可骑乘·可轻功",key="立足不稳",},},},</v>
       </c>
       <c r="AR6" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="AS6" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="7" spans="1:45">
@@ -19620,16 +19623,16 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L7" t="s">
-        <v>1523</v>
+        <v>1541</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -19641,10 +19644,10 @@
         <v>37</v>
       </c>
       <c r="AJ7" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="AK7" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="AL7">
         <v>255</v>
@@ -19654,12 +19657,12 @@
         <v>{dwID=29080,nLevel=1,szName="易伤",nScrutinyType=1,szNote="经脉受损",col={255,127,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#FF80FFFF",colScreenHead="#FF80FF",nColAlpha=255,},},tCountdown={{nClass=2,nIcon=16300,nFrame=5,nTime=2,szName="经脉受损·已经移除",key="经脉受损",},},},</v>
       </c>
       <c r="AR7" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="8" spans="1:45">
       <c r="A8" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B8">
         <v>-2</v>
@@ -19680,7 +19683,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -19695,7 +19698,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:45">
       <c r="A10" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B10">
         <v>-21</v>
@@ -19716,7 +19719,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="U11">
         <v>1</v>
@@ -19783,43 +19786,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="M1" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="N1" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="O1" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="P1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="Q1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="R1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="S1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="T1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="U1" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="V1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="W1" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="X1" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
@@ -19845,14 +19848,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="X3" t="str">
         <f>IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(D3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(D2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nIcon="&amp;E3&amp;",","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H3&gt;0,"nScrutinyType="&amp;H3&amp;",","")&amp;IF(I3&lt;&gt;"","tKungFu={"&amp;I3&amp;"},","")&amp;IF(J3&lt;&gt;"","szNote="""&amp;J3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;"[9]={"&amp;IF(L3&lt;&gt;"","tMark={"&amp;L3&amp;"},","")&amp;IF(M3&lt;&gt;"","szVoice="""&amp;M3&amp;""",","")&amp;IF(N3&gt;0,"bTeamChannel=true,","")&amp;IF(O3&gt;0,"bWhisperChannel=true,","")&amp;IF(P3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q3&lt;&gt;"","tMark={"&amp;Q3&amp;"},","")&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;IF(V3&gt;0,"bScreenHead=true,","")&amp;IF(W3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y3:AAC3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19863,14 +19866,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="X4" t="str">
         <f>IF(ISBLANK(B4)=FALSE,IF(ISBLANK(B3),"},["&amp;B4&amp;"]={","["&amp;B4&amp;"]={"),IF(AND(ISBLANK(B4),ISBLANK(C4),ISBLANK(D4),OR(ISBLANK(B3)=FALSE,ISBLANK(C3)=FALSE,ISBLANK(D3)=FALSE)),"},},}",IF(ISBLANK(C4),"","{dwID="&amp;C4&amp;","&amp;"nLevel="&amp;D4&amp;","&amp;IF(E4&gt;0,"nIcon="&amp;E4&amp;",","")&amp;IF(F4&lt;&gt;"","szName="""&amp;F4&amp;""",","")&amp;IF(G4&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H4&gt;0,"nScrutinyType="&amp;H4&amp;",","")&amp;IF(I4&lt;&gt;"","tKungFu={"&amp;I4&amp;"},","")&amp;IF(J4&lt;&gt;"","szNote="""&amp;J4&amp;""",","")&amp;IF(K4&lt;&gt;"","col={"&amp;K4&amp;"},","")&amp;"[9]={"&amp;IF(L4&lt;&gt;"","tMark={"&amp;L4&amp;"},","")&amp;IF(M4&lt;&gt;"","szVoice="""&amp;M4&amp;""",","")&amp;IF(N4&gt;0,"bTeamChannel=true,","")&amp;IF(O4&gt;0,"bWhisperChannel=true,","")&amp;IF(P4&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q4&lt;&gt;"","tMark={"&amp;Q4&amp;"},","")&amp;IF(R4&lt;&gt;"","szVoice="""&amp;R4&amp;""",","")&amp;IF(S4&gt;0,"bTeamChannel=true,","")&amp;IF(T4&gt;0,"bWhisperChannel=true,","")&amp;IF(U4&gt;0,"bCenterAlarm=true,","")&amp;IF(V4&gt;0,"bScreenHead=true,","")&amp;IF(W4&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y4&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y4:AAC4)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19881,14 +19884,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="X5" t="str">
         <f>IF(ISBLANK(B5)=FALSE,IF(ISBLANK(B4),"},["&amp;B5&amp;"]={","["&amp;B5&amp;"]={"),IF(AND(ISBLANK(B5),ISBLANK(C5),ISBLANK(D5),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C5),"","{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nIcon="&amp;E5&amp;",","")&amp;IF(F5&lt;&gt;"","szName="""&amp;F5&amp;""",","")&amp;IF(G5&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H5&gt;0,"nScrutinyType="&amp;H5&amp;",","")&amp;IF(I5&lt;&gt;"","tKungFu={"&amp;I5&amp;"},","")&amp;IF(J5&lt;&gt;"","szNote="""&amp;J5&amp;""",","")&amp;IF(K5&lt;&gt;"","col={"&amp;K5&amp;"},","")&amp;"[9]={"&amp;IF(L5&lt;&gt;"","tMark={"&amp;L5&amp;"},","")&amp;IF(M5&lt;&gt;"","szVoice="""&amp;M5&amp;""",","")&amp;IF(N5&gt;0,"bTeamChannel=true,","")&amp;IF(O5&gt;0,"bWhisperChannel=true,","")&amp;IF(P5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q5&lt;&gt;"","tMark={"&amp;Q5&amp;"},","")&amp;IF(R5&lt;&gt;"","szVoice="""&amp;R5&amp;""",","")&amp;IF(S5&gt;0,"bTeamChannel=true,","")&amp;IF(T5&gt;0,"bWhisperChannel=true,","")&amp;IF(U5&gt;0,"bCenterAlarm=true,","")&amp;IF(V5&gt;0,"bScreenHead=true,","")&amp;IF(W5&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y5:AAC5)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19927,10 +19930,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19945,43 +19948,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="L1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="M1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="N1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="O1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="P1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="Q1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="R1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="S1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="T1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="U1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -19989,7 +19992,7 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -20007,7 +20010,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -20016,7 +20019,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20025,7 +20028,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -20043,7 +20046,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -20052,7 +20055,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -20079,10 +20082,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="V7" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -20097,16 +20100,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="J8" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -20121,10 +20124,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="V9" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20139,10 +20142,10 @@
         <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="V10" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20157,7 +20160,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20166,7 +20169,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20181,7 +20184,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20190,7 +20193,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20205,7 +20208,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20214,7 +20217,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20229,7 +20232,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="J14" t="s">
         <v>582</v>
@@ -20238,7 +20241,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
@@ -20253,7 +20256,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20262,17 +20265,17 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="Y15" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20283,7 +20286,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="J16" t="s">
         <v>640</v>
@@ -20292,14 +20295,14 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X16" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="3:25">
@@ -20310,10 +20313,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="V17" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20328,7 +20331,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20337,7 +20340,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20352,7 +20355,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20361,7 +20364,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20376,7 +20379,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="J20" t="s">
         <v>582</v>
@@ -20385,7 +20388,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
@@ -20400,7 +20403,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="J21" t="s">
         <v>582</v>
@@ -20409,7 +20412,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -20424,7 +20427,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20433,17 +20436,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="Y22" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20454,7 +20457,7 @@
         <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="J23" t="s">
         <v>640</v>
@@ -20463,14 +20466,14 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X23" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="24" spans="3:25">
@@ -20481,7 +20484,7 @@
         <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="J24" t="s">
         <v>640</v>
@@ -20490,17 +20493,17 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X24" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="Y24" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="25" spans="3:25">
@@ -20511,10 +20514,10 @@
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="V25" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
@@ -20557,10 +20560,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20575,40 +20578,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="K1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="L1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="N1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="O1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="P1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="Q1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="R1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="S1" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20616,7 +20619,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -20631,7 +20634,7 @@
         <v>8848</v>
       </c>
       <c r="H3" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20640,7 +20643,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20652,7 +20655,7 @@
         <v>8849</v>
       </c>
       <c r="H4" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20661,7 +20664,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20673,7 +20676,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20682,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20694,7 +20697,7 @@
         <v>8851</v>
       </c>
       <c r="H6" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20703,7 +20706,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20715,7 +20718,7 @@
         <v>8852</v>
       </c>
       <c r="H7" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20724,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20748,7 +20751,7 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="I9" t="s">
         <v>640</v>
@@ -20760,7 +20763,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20810,7 +20813,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20819,31 +20822,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="I1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="J1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="K1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="L1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="M1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="N1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="O1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20851,7 +20854,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20863,43 +20866,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D3" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D4" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="E4" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
       <c r="A5" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B5">
         <v>-2</v>
@@ -20911,13 +20914,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D6" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="E6" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20930,18 +20933,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D7" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="E7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20954,12 +20957,12 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B8">
         <v>-21</v>
@@ -20971,13 +20974,13 @@
     </row>
     <row r="9" customFormat="1" spans="1:16">
       <c r="C9" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D9" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="E9" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20990,18 +20993,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P9" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:16">
       <c r="C10" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D10" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="E10" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -21014,7 +21017,7 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -21031,13 +21034,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D12" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="E12" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -21047,18 +21050,18 @@
         <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D13" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="E13" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -21068,18 +21071,18 @@
         <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D14" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="E14" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -21089,18 +21092,18 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="C15" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D15" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="E15" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -21110,42 +21113,42 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="D16" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P16" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="17" spans="3:16">
       <c r="D17" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P17" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D18" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="E18" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -21158,7 +21161,7 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P18" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="19" spans="3:16">
@@ -21194,7 +21197,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21203,31 +21206,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="G1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="I1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="J1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="K1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="L1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="M1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="N1" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21247,46 +21250,46 @@
     </row>
     <row r="3" spans="1:15">
       <c r="C3" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="C5" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="C6" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D6" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -21296,63 +21299,63 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O7" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="C8" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="C9" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="C10" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="C11" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="D11" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -21362,27 +21365,27 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="C12" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="D13" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21392,15 +21395,15 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D14" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21410,15 +21413,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D15" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -21428,15 +21431,15 @@
         <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D16" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21446,36 +21449,36 @@
         <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -21485,27 +21488,27 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="C21" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="D21" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E21" t="s">
         <v>582</v>
@@ -21521,15 +21524,15 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="D22" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="E22" t="s">
         <v>582</v>
@@ -21544,85 +21547,85 @@
     </row>
     <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="P23" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="P24" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="Q24" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="R24" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="P25" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="Q25" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="R25" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="P26" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="Q26" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="R26" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:18">
       <c r="A27" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B27">
         <v>-2</v>
@@ -21634,10 +21637,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:18">
       <c r="C28" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="D28" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -21647,15 +21650,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="D29" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21665,27 +21668,27 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="C30" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D30" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B31">
         <v>-21</v>
@@ -21697,10 +21700,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="D32" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21710,15 +21713,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="3:15">
       <c r="C33" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="D33" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21728,22 +21731,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="3:15">
       <c r="C34" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D34" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="35" spans="3:15">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -4623,7 +4623,7 @@
     <t>153,26,26,</t>
   </si>
   <si>
-    <t>抗摔</t>
+    <t>弹射</t>
   </si>
   <si>
     <t>家园卫士出门抗摔</t>
@@ -5178,7 +5178,7 @@
     <t>蓝方成功开启全局迷雾视野\n</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},</t>
+    <t>{nClass=20,nIcon=25111,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},</t>
   </si>
   <si>
     <t>红方成功击败了古猿\n</t>
@@ -5211,7 +5211,7 @@
     <t>红方成功开启全局迷雾视野\n</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},</t>
+    <t>{nClass=20,nIcon=25109,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},</t>
@@ -6758,7 +6758,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1787747567000,</v>
+        <v>nTimeStamp = 1787853525000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -19161,7 +19161,7 @@
         <v>689</v>
       </c>
       <c r="AQ2" t="str">
-        <f>IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AQ2:AQ8" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
         <v>[689]={</v>
       </c>
     </row>
@@ -19203,7 +19203,7 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="str">
-        <f>IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" si="0"/>
         <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00DD",colScreenHead="#FFFF00",nColAlpha=221,bScreenHead=true,},},},</v>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="str">
-        <f>IF(B4&lt;&gt;"",IF(IFERROR(VALUE(C3),0)&lt;=0,"["&amp;B4&amp;"]={","},["&amp;B4&amp;"]={"),IF(C4&gt;0,"{dwID="&amp;C4&amp;","&amp;"nLevel="&amp;D4&amp;","&amp;IF(E4&gt;0,"nCount="&amp;E4&amp;",","")&amp;IF(F4&gt;0,"nIcon="&amp;F4&amp;",","")&amp;IF(G4&lt;&gt;"","szName="""&amp;G4&amp;""",","")&amp;IF(H4&gt;0,"bCheckLevel=true,","")&amp;IF(I4&gt;0,"nScrutinyType="&amp;I4&amp;",","")&amp;IF(J4&lt;&gt;"","tKungFu={"&amp;J4&amp;"},","")&amp;IF(K4&lt;&gt;"","szNote="""&amp;K4&amp;""",","")&amp;IF(L4&lt;&gt;"","col={"&amp;L4&amp;"},","")&amp;"[1]={"&amp;IF(M4&lt;&gt;"","tMark={"&amp;M4&amp;"},","")&amp;IF(N4&lt;&gt;"","szVoice="""&amp;N4&amp;""",","")&amp;IF(O4&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P4&gt;0,"bTeamChannel=true,","")&amp;IF(Q4&gt;0,"bWhisperChannel=true,","")&amp;IF(R4&gt;0,"bCenterAlarm=true,","")&amp;IF(S4&gt;0,"bScreenHead=true,","")&amp;IF(T4&gt;0,"bPartyBuffList=true,","")&amp;IF(U4&gt;0,"bBuffList=true,","")&amp;IF(V4&gt;0,"bFullScreen=true,","")&amp;IF(W4&gt;0,"bTeamPanel=true,","")&amp;IF(X4&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y4&lt;&gt;"","szVoice="""&amp;Y4&amp;""",","")&amp;IF(Z4&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA4&gt;0,"bTeamChannel=true,","")&amp;IF(AB4&gt;0,"bWhisperChannel=true,","")&amp;IF(AC4&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD4&gt;0,AH4&lt;&gt;"",AI4&gt;0,AJ4&lt;&gt;"",AK4&lt;&gt;"",AL4&gt;0,AM4&gt;0,AN4&gt;0,AO4&gt;0),"aCataclysmBuff={{"&amp;IF(AD4&gt;0,"nStackNum="&amp;AD4&amp;",","")&amp;IF(AE4&lt;&gt;"","szStackOp="""&amp;AE4&amp;""",","")&amp;IF(AF4&gt;0,"bOnlyMine=true,","")&amp;IF(AG4&gt;0,"bOnlyMe=true,","")&amp;IF(AH4&lt;&gt;"","szReminder="""&amp;AH4&amp;""",","")&amp;IF(AI4&gt;0,"nPriority="&amp;AI4&amp;",","")&amp;IF(AJ4&lt;&gt;"","col="""&amp;AJ4&amp;""",","")&amp;IF(AK4&lt;&gt;"","colScreenHead="""&amp;AK4&amp;""",","")&amp;IF(AL4&gt;0,"nColAlpha="&amp;AL4&amp;",","")&amp;IF(AM4&gt;0,"bAttention=true,","")&amp;IF(AN4&gt;0,"bCaution=true,","")&amp;IF(AO4&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP4&amp;"},","")&amp;IF(AR4&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR4:AAC4)&amp;"},","")&amp;"},",IF(C3&gt;0,"},","")&amp;IF(AND(B4="",C4="",OR(B3&lt;&gt;"",C3&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" si="0"/>
         <v>{dwID=29048,nLevel=1,nIcon=3293,szName="塔内",nScrutinyType=1,szNote="被防御塔瞄准",col={153,26,26,},[1]={bBuffList=true,bFullScreen=true,},[2]={},},</v>
       </c>
     </row>
@@ -19248,7 +19248,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>77</v>
+        <v>4573</v>
       </c>
       <c r="G5" t="s">
         <v>1524</v>
@@ -19263,8 +19263,8 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="str">
-        <f>IF(B5&lt;&gt;"",IF(IFERROR(VALUE(C4),0)&lt;=0,"["&amp;B5&amp;"]={","},["&amp;B5&amp;"]={"),IF(C5&gt;0,"{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nCount="&amp;E5&amp;",","")&amp;IF(F5&gt;0,"nIcon="&amp;F5&amp;",","")&amp;IF(G5&lt;&gt;"","szName="""&amp;G5&amp;""",","")&amp;IF(H5&gt;0,"bCheckLevel=true,","")&amp;IF(I5&gt;0,"nScrutinyType="&amp;I5&amp;",","")&amp;IF(J5&lt;&gt;"","tKungFu={"&amp;J5&amp;"},","")&amp;IF(K5&lt;&gt;"","szNote="""&amp;K5&amp;""",","")&amp;IF(L5&lt;&gt;"","col={"&amp;L5&amp;"},","")&amp;"[1]={"&amp;IF(M5&lt;&gt;"","tMark={"&amp;M5&amp;"},","")&amp;IF(N5&lt;&gt;"","szVoice="""&amp;N5&amp;""",","")&amp;IF(O5&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P5&gt;0,"bTeamChannel=true,","")&amp;IF(Q5&gt;0,"bWhisperChannel=true,","")&amp;IF(R5&gt;0,"bCenterAlarm=true,","")&amp;IF(S5&gt;0,"bScreenHead=true,","")&amp;IF(T5&gt;0,"bPartyBuffList=true,","")&amp;IF(U5&gt;0,"bBuffList=true,","")&amp;IF(V5&gt;0,"bFullScreen=true,","")&amp;IF(W5&gt;0,"bTeamPanel=true,","")&amp;IF(X5&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y5&lt;&gt;"","szVoice="""&amp;Y5&amp;""",","")&amp;IF(Z5&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA5&gt;0,"bTeamChannel=true,","")&amp;IF(AB5&gt;0,"bWhisperChannel=true,","")&amp;IF(AC5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD5&gt;0,AH5&lt;&gt;"",AI5&gt;0,AJ5&lt;&gt;"",AK5&lt;&gt;"",AL5&gt;0,AM5&gt;0,AN5&gt;0,AO5&gt;0),"aCataclysmBuff={{"&amp;IF(AD5&gt;0,"nStackNum="&amp;AD5&amp;",","")&amp;IF(AE5&lt;&gt;"","szStackOp="""&amp;AE5&amp;""",","")&amp;IF(AF5&gt;0,"bOnlyMine=true,","")&amp;IF(AG5&gt;0,"bOnlyMe=true,","")&amp;IF(AH5&lt;&gt;"","szReminder="""&amp;AH5&amp;""",","")&amp;IF(AI5&gt;0,"nPriority="&amp;AI5&amp;",","")&amp;IF(AJ5&lt;&gt;"","col="""&amp;AJ5&amp;""",","")&amp;IF(AK5&lt;&gt;"","colScreenHead="""&amp;AK5&amp;""",","")&amp;IF(AL5&gt;0,"nColAlpha="&amp;AL5&amp;",","")&amp;IF(AM5&gt;0,"bAttention=true,","")&amp;IF(AN5&gt;0,"bCaution=true,","")&amp;IF(AO5&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP5&amp;"},","")&amp;IF(AR5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR5:AAC5)&amp;"},","")&amp;"},",IF(C4&gt;0,"},","")&amp;IF(AND(B5="",C5="",OR(B4&lt;&gt;"",C4&lt;&gt;"")),"},}","")))</f>
-        <v>{dwID=29019,nLevel=1,nIcon=77,szName="抗摔",nScrutinyType=1,szNote="家园卫士出门抗摔",[1]={bBuffList=true,},[2]={},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=29019,nLevel=1,nIcon=4573,szName="弹射",nScrutinyType=1,szNote="家园卫士出门抗摔",[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="6" spans="1:44">
@@ -19311,19 +19311,19 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="str">
-        <f>IF(B6&lt;&gt;"",IF(IFERROR(VALUE(C5),0)&lt;=0,"["&amp;B6&amp;"]={","},["&amp;B6&amp;"]={"),IF(C6&gt;0,"{dwID="&amp;C6&amp;","&amp;"nLevel="&amp;D6&amp;","&amp;IF(E6&gt;0,"nCount="&amp;E6&amp;",","")&amp;IF(F6&gt;0,"nIcon="&amp;F6&amp;",","")&amp;IF(G6&lt;&gt;"","szName="""&amp;G6&amp;""",","")&amp;IF(H6&gt;0,"bCheckLevel=true,","")&amp;IF(I6&gt;0,"nScrutinyType="&amp;I6&amp;",","")&amp;IF(J6&lt;&gt;"","tKungFu={"&amp;J6&amp;"},","")&amp;IF(K6&lt;&gt;"","szNote="""&amp;K6&amp;""",","")&amp;IF(L6&lt;&gt;"","col={"&amp;L6&amp;"},","")&amp;"[1]={"&amp;IF(M6&lt;&gt;"","tMark={"&amp;M6&amp;"},","")&amp;IF(N6&lt;&gt;"","szVoice="""&amp;N6&amp;""",","")&amp;IF(O6&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P6&gt;0,"bTeamChannel=true,","")&amp;IF(Q6&gt;0,"bWhisperChannel=true,","")&amp;IF(R6&gt;0,"bCenterAlarm=true,","")&amp;IF(S6&gt;0,"bScreenHead=true,","")&amp;IF(T6&gt;0,"bPartyBuffList=true,","")&amp;IF(U6&gt;0,"bBuffList=true,","")&amp;IF(V6&gt;0,"bFullScreen=true,","")&amp;IF(W6&gt;0,"bTeamPanel=true,","")&amp;IF(X6&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y6&lt;&gt;"","szVoice="""&amp;Y6&amp;""",","")&amp;IF(Z6&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA6&gt;0,"bTeamChannel=true,","")&amp;IF(AB6&gt;0,"bWhisperChannel=true,","")&amp;IF(AC6&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD6&gt;0,AH6&lt;&gt;"",AI6&gt;0,AJ6&lt;&gt;"",AK6&lt;&gt;"",AL6&gt;0,AM6&gt;0,AN6&gt;0,AO6&gt;0),"aCataclysmBuff={{"&amp;IF(AD6&gt;0,"nStackNum="&amp;AD6&amp;",","")&amp;IF(AE6&lt;&gt;"","szStackOp="""&amp;AE6&amp;""",","")&amp;IF(AF6&gt;0,"bOnlyMine=true,","")&amp;IF(AG6&gt;0,"bOnlyMe=true,","")&amp;IF(AH6&lt;&gt;"","szReminder="""&amp;AH6&amp;""",","")&amp;IF(AI6&gt;0,"nPriority="&amp;AI6&amp;",","")&amp;IF(AJ6&lt;&gt;"","col="""&amp;AJ6&amp;""",","")&amp;IF(AK6&lt;&gt;"","colScreenHead="""&amp;AK6&amp;""",","")&amp;IF(AL6&gt;0,"nColAlpha="&amp;AL6&amp;",","")&amp;IF(AM6&gt;0,"bAttention=true,","")&amp;IF(AN6&gt;0,"bCaution=true,","")&amp;IF(AO6&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP6&amp;"},","")&amp;IF(AR6&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR6:AAC6)&amp;"},","")&amp;"},",IF(C5&gt;0,"},","")&amp;IF(AND(B6="",C6="",OR(B5&lt;&gt;"",C5&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" si="0"/>
         <v>{dwID=29097,nLevel=1,szNote="隐匿草丛",col={255,204,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="藏",nPriority=3,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="7" spans="1:44">
       <c r="AQ7" t="str">
-        <f>IF(B7&lt;&gt;"",IF(IFERROR(VALUE(C6),0)&lt;=0,"["&amp;B7&amp;"]={","},["&amp;B7&amp;"]={"),IF(C7&gt;0,"{dwID="&amp;C7&amp;","&amp;"nLevel="&amp;D7&amp;","&amp;IF(E7&gt;0,"nCount="&amp;E7&amp;",","")&amp;IF(F7&gt;0,"nIcon="&amp;F7&amp;",","")&amp;IF(G7&lt;&gt;"","szName="""&amp;G7&amp;""",","")&amp;IF(H7&gt;0,"bCheckLevel=true,","")&amp;IF(I7&gt;0,"nScrutinyType="&amp;I7&amp;",","")&amp;IF(J7&lt;&gt;"","tKungFu={"&amp;J7&amp;"},","")&amp;IF(K7&lt;&gt;"","szNote="""&amp;K7&amp;""",","")&amp;IF(L7&lt;&gt;"","col={"&amp;L7&amp;"},","")&amp;"[1]={"&amp;IF(M7&lt;&gt;"","tMark={"&amp;M7&amp;"},","")&amp;IF(N7&lt;&gt;"","szVoice="""&amp;N7&amp;""",","")&amp;IF(O7&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P7&gt;0,"bTeamChannel=true,","")&amp;IF(Q7&gt;0,"bWhisperChannel=true,","")&amp;IF(R7&gt;0,"bCenterAlarm=true,","")&amp;IF(S7&gt;0,"bScreenHead=true,","")&amp;IF(T7&gt;0,"bPartyBuffList=true,","")&amp;IF(U7&gt;0,"bBuffList=true,","")&amp;IF(V7&gt;0,"bFullScreen=true,","")&amp;IF(W7&gt;0,"bTeamPanel=true,","")&amp;IF(X7&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y7&lt;&gt;"","szVoice="""&amp;Y7&amp;""",","")&amp;IF(Z7&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA7&gt;0,"bTeamChannel=true,","")&amp;IF(AB7&gt;0,"bWhisperChannel=true,","")&amp;IF(AC7&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD7&gt;0,AH7&lt;&gt;"",AI7&gt;0,AJ7&lt;&gt;"",AK7&lt;&gt;"",AL7&gt;0,AM7&gt;0,AN7&gt;0,AO7&gt;0),"aCataclysmBuff={{"&amp;IF(AD7&gt;0,"nStackNum="&amp;AD7&amp;",","")&amp;IF(AE7&lt;&gt;"","szStackOp="""&amp;AE7&amp;""",","")&amp;IF(AF7&gt;0,"bOnlyMine=true,","")&amp;IF(AG7&gt;0,"bOnlyMe=true,","")&amp;IF(AH7&lt;&gt;"","szReminder="""&amp;AH7&amp;""",","")&amp;IF(AI7&gt;0,"nPriority="&amp;AI7&amp;",","")&amp;IF(AJ7&lt;&gt;"","col="""&amp;AJ7&amp;""",","")&amp;IF(AK7&lt;&gt;"","colScreenHead="""&amp;AK7&amp;""",","")&amp;IF(AL7&gt;0,"nColAlpha="&amp;AL7&amp;",","")&amp;IF(AM7&gt;0,"bAttention=true,","")&amp;IF(AN7&gt;0,"bCaution=true,","")&amp;IF(AO7&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP7&amp;"},","")&amp;IF(AR7&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR7:AAC7)&amp;"},","")&amp;"},",IF(C6&gt;0,"},","")&amp;IF(AND(B7="",C7="",OR(B6&lt;&gt;"",C6&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
     </row>
     <row r="8" spans="1:44">
       <c r="AQ8" t="str">
-        <f>IF(B8&lt;&gt;"",IF(IFERROR(VALUE(C7),0)&lt;=0,"["&amp;B8&amp;"]={","},["&amp;B8&amp;"]={"),IF(C8&gt;0,"{dwID="&amp;C8&amp;","&amp;"nLevel="&amp;D8&amp;","&amp;IF(E8&gt;0,"nCount="&amp;E8&amp;",","")&amp;IF(F8&gt;0,"nIcon="&amp;F8&amp;",","")&amp;IF(G8&lt;&gt;"","szName="""&amp;G8&amp;""",","")&amp;IF(H8&gt;0,"bCheckLevel=true,","")&amp;IF(I8&gt;0,"nScrutinyType="&amp;I8&amp;",","")&amp;IF(J8&lt;&gt;"","tKungFu={"&amp;J8&amp;"},","")&amp;IF(K8&lt;&gt;"","szNote="""&amp;K8&amp;""",","")&amp;IF(L8&lt;&gt;"","col={"&amp;L8&amp;"},","")&amp;"[1]={"&amp;IF(M8&lt;&gt;"","tMark={"&amp;M8&amp;"},","")&amp;IF(N8&lt;&gt;"","szVoice="""&amp;N8&amp;""",","")&amp;IF(O8&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P8&gt;0,"bTeamChannel=true,","")&amp;IF(Q8&gt;0,"bWhisperChannel=true,","")&amp;IF(R8&gt;0,"bCenterAlarm=true,","")&amp;IF(S8&gt;0,"bScreenHead=true,","")&amp;IF(T8&gt;0,"bPartyBuffList=true,","")&amp;IF(U8&gt;0,"bBuffList=true,","")&amp;IF(V8&gt;0,"bFullScreen=true,","")&amp;IF(W8&gt;0,"bTeamPanel=true,","")&amp;IF(X8&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y8&lt;&gt;"","szVoice="""&amp;Y8&amp;""",","")&amp;IF(Z8&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA8&gt;0,"bTeamChannel=true,","")&amp;IF(AB8&gt;0,"bWhisperChannel=true,","")&amp;IF(AC8&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD8&gt;0,AH8&lt;&gt;"",AI8&gt;0,AJ8&lt;&gt;"",AK8&lt;&gt;"",AL8&gt;0,AM8&gt;0,AN8&gt;0,AO8&gt;0),"aCataclysmBuff={{"&amp;IF(AD8&gt;0,"nStackNum="&amp;AD8&amp;",","")&amp;IF(AE8&lt;&gt;"","szStackOp="""&amp;AE8&amp;""",","")&amp;IF(AF8&gt;0,"bOnlyMine=true,","")&amp;IF(AG8&gt;0,"bOnlyMe=true,","")&amp;IF(AH8&lt;&gt;"","szReminder="""&amp;AH8&amp;""",","")&amp;IF(AI8&gt;0,"nPriority="&amp;AI8&amp;",","")&amp;IF(AJ8&lt;&gt;"","col="""&amp;AJ8&amp;""",","")&amp;IF(AK8&lt;&gt;"","colScreenHead="""&amp;AK8&amp;""",","")&amp;IF(AL8&gt;0,"nColAlpha="&amp;AL8&amp;",","")&amp;IF(AM8&gt;0,"bAttention=true,","")&amp;IF(AN8&gt;0,"bCaution=true,","")&amp;IF(AO8&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP8&amp;"},","")&amp;IF(AR8&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR8:AAC8)&amp;"},","")&amp;"},",IF(C7&gt;0,"},","")&amp;IF(AND(B8="",C8="",OR(B7&lt;&gt;"",C7&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15839,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
+        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25111,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O7" t="s">
         <v>1709</v>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=15838,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
+        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25109,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
         <v>1720</v>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="1829">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4608,7 +4608,7 @@
     <t>骑御</t>
   </si>
   <si>
-    <t>#FFFF00DD</t>
+    <t>#FFFF0000</t>
   </si>
   <si>
     <t>#FFFF00</t>
@@ -4809,7 +4809,7 @@
     <t>帮会联赛·闻千瞬</t>
   </si>
   <si>
-    <t>{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="闻千瞬·争霸赛",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>出行大炮</t>
@@ -4944,6 +4944,15 @@
     <t>{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},</t>
   </si>
   <si>
+    <t>麒麟珠</t>
+  </si>
+  <si>
+    <t>50,255,255,</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="麒麟珠·交互",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
     <t>准备刷新</t>
   </si>
   <si>
@@ -5011,12 +5020,6 @@
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="联赛·冠军·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>麒麟珠</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="麒麟珠·交互",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>喊话内容</t>
@@ -6758,7 +6761,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1787853525000,</v>
+        <v>nTimeStamp = 1788502790000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8684,7 +8687,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8697,13 +8700,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="C2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8712,13 +8715,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B3" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C3" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8727,13 +8730,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="C4" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8742,13 +8745,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B5" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C5" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8757,7 +8760,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8766,13 +8769,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B7" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C7" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8781,13 +8784,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B8" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="C8" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8796,13 +8799,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B9" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C9" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8811,13 +8814,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B10" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C10" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8826,13 +8829,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B11" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="C11" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8841,7 +8844,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8850,10 +8853,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="C13" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8862,10 +8865,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C14" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8874,10 +8877,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="C15" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8886,10 +8889,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C16" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8898,10 +8901,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C17" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8910,7 +8913,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8919,7 +8922,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8928,7 +8931,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8937,7 +8940,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8946,7 +8949,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8979,7 +8982,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8996,7 +8999,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -9010,7 +9013,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9024,7 +9027,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9044,7 +9047,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9063,7 +9066,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9074,7 +9077,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9085,7 +9088,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9101,7 +9104,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9116,7 +9119,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9127,7 +9130,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9138,7 +9141,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9154,7 +9157,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9169,7 +9172,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9180,7 +9183,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9191,7 +9194,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9207,7 +9210,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9222,7 +9225,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9233,7 +9236,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9244,7 +9247,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9260,7 +9263,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9275,7 +9278,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9286,7 +9289,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9297,7 +9300,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9313,7 +9316,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9328,7 +9331,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9339,7 +9342,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9350,7 +9353,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9366,7 +9369,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9381,7 +9384,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9392,7 +9395,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9403,7 +9406,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9419,7 +9422,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9434,7 +9437,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9445,7 +9448,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9456,7 +9459,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9472,7 +9475,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9487,7 +9490,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9498,7 +9501,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9509,7 +9512,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9525,7 +9528,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9540,7 +9543,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9551,7 +9554,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9562,7 +9565,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9578,7 +9581,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9593,7 +9596,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9604,7 +9607,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9615,7 +9618,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9631,7 +9634,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9646,7 +9649,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9657,7 +9660,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9668,7 +9671,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9684,7 +9687,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9699,7 +9702,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9710,7 +9713,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9721,7 +9724,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9737,7 +9740,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9752,7 +9755,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9763,7 +9766,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9774,7 +9777,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9790,7 +9793,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9805,7 +9808,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9816,7 +9819,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9827,7 +9830,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9843,7 +9846,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9858,7 +9861,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9869,7 +9872,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9880,7 +9883,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9896,7 +9899,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9911,7 +9914,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9922,7 +9925,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9933,7 +9936,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9949,7 +9952,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9964,7 +9967,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9975,7 +9978,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9986,7 +9989,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -10002,7 +10005,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10017,7 +10020,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10028,7 +10031,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10039,7 +10042,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10055,7 +10058,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10070,7 +10073,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10081,7 +10084,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10092,7 +10095,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10108,7 +10111,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10123,7 +10126,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10134,7 +10137,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10145,7 +10148,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10161,7 +10164,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10176,7 +10179,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10187,7 +10190,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10198,7 +10201,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10214,7 +10217,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10229,7 +10232,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10240,7 +10243,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10251,7 +10254,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10267,7 +10270,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10281,7 +10284,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10291,7 +10294,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10301,7 +10304,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10317,7 +10320,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10337,7 +10340,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10357,7 +10360,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10377,7 +10380,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10397,7 +10400,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10417,7 +10420,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10437,7 +10440,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10457,7 +10460,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10477,7 +10480,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10497,7 +10500,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10517,7 +10520,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10537,7 +10540,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10557,7 +10560,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10577,7 +10580,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10597,7 +10600,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10617,7 +10620,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10637,7 +10640,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10657,7 +10660,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10677,7 +10680,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10697,7 +10700,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10717,7 +10720,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10737,7 +10740,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10757,7 +10760,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10777,7 +10780,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10797,7 +10800,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10817,7 +10820,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10837,7 +10840,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10857,7 +10860,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10877,7 +10880,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10897,7 +10900,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10917,7 +10920,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10937,7 +10940,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10957,7 +10960,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10977,7 +10980,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -10997,7 +11000,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19197,14 +19200,14 @@
         <v>1520</v>
       </c>
       <c r="AL3">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>1</v>
       </c>
       <c r="AQ3" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF00DD",colScreenHead="#FFFF00",nColAlpha=221,bScreenHead=true,},},},</v>
+        <v>{dwID=244,nLevel=1,szName="骑御中",szNote="骑御",col={255,255,0,},[1]={bScreenHead=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=40,col="#FFFF0000",colScreenHead="#FFFF00",bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -19910,7 +19913,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="9" max="9" width="21.375" customWidth="1"/>
@@ -20022,8 +20025,8 @@
         <v>1586</v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W26" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" ref="W3:W28" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="闻千瞬·争霸赛",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -20059,7 +20062,7 @@
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=103373,nFrame=47,szNote="帮会联赛·闻千瞬",col={0,255,0,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="闻千瞬·争霸赛",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -20508,31 +20511,55 @@
     </row>
     <row r="25" spans="3:25">
       <c r="C25">
-        <v>128941</v>
+        <v>129144</v>
       </c>
       <c r="D25">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I25" t="s">
         <v>1631</v>
       </c>
+      <c r="J25" t="s">
+        <v>1632</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
       <c r="V25" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=128941,nFrame=52,szNote="准备刷新",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="准备刷新·30秒",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=129144,nFrame=47,szNote="麒麟珠",col={50,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="麒麟珠·交互",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="26" spans="3:25">
+      <c r="C26">
+        <v>128941</v>
+      </c>
+      <c r="D26">
+        <v>52</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1634</v>
+      </c>
+      <c r="V26" t="s">
+        <v>1635</v>
+      </c>
       <c r="W26" t="str">
         <f t="shared" si="0"/>
-        <v>},},}</v>
+        <v>{dwID=128941,nFrame=52,szNote="准备刷新",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="准备刷新·30秒",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="27" spans="3:25">
       <c r="W27" t="str">
-        <f t="shared" ref="W27" si="1">IF(ISBLANK(B27)=FALSE,IF(ISBLANK(B26),"},["&amp;B27&amp;"]={","["&amp;B27&amp;"]={"),IF(AND(ISBLANK(B27),ISBLANK(D27),ISBLANK(C27),OR(ISBLANK(B26)=FALSE,ISBLANK(D26)=FALSE,ISBLANK(C26)=FALSE)),"},},}",IF(ISBLANK(C27),"","{dwID="&amp;C27&amp;","&amp;"nFrame="&amp;D27&amp;","&amp;IF(E27&gt;0,"nCount="&amp;E27&amp;",","")&amp;IF(F27&gt;0,"bAllLeave=true,","")&amp;IF(G27&lt;&gt;"","szName="""&amp;G27&amp;""",","")&amp;IF(H27&lt;&gt;"","tKungFu={"&amp;H27&amp;"},","")&amp;IF(I27&lt;&gt;"","szNote="""&amp;I27&amp;""",","")&amp;IF(J27&lt;&gt;"","col={"&amp;J27&amp;"},","")&amp;"[3]={"&amp;IF(K27&lt;&gt;"","tMark={"&amp;K27&amp;"},","")&amp;IF(L27&lt;&gt;"","szVoice="""&amp;L27&amp;""",","")&amp;IF(M27&gt;0,"bTeamChannel=true,","")&amp;IF(N27&gt;0,"bWhisperChannel=true,","")&amp;IF(O27&gt;0,"bCenterAlarm=true,","")&amp;IF(P27&gt;0,"bScreenHead=true,","")&amp;IF(Q27&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R27&lt;&gt;"","szVoice="""&amp;R27&amp;""",","")&amp;IF(S27&gt;0,"bTeamChannel=true,","")&amp;IF(T27&gt;0,"bWhisperChannel=true,","")&amp;IF(U27&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V27&lt;&gt;"","aFocus={"&amp;V27&amp;"},","")&amp;IF(X27&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X27:AAA27)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
+        <v>},},}</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25">
+      <c r="W28" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -20578,40 +20605,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="K1" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="L1" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="M1" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="N1" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="O1" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="P1" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="Q1" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="R1" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="S1" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20634,7 +20661,7 @@
         <v>8848</v>
       </c>
       <c r="H3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20643,10 +20670,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="U3" t="str">
-        <f t="shared" ref="U3:U10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="U3:U11" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=8848,szNote="联赛八强服务器宝堆",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="联赛·八强·宝堆",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -20655,7 +20682,7 @@
         <v>8849</v>
       </c>
       <c r="H4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20664,7 +20691,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20676,7 +20703,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20685,7 +20712,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20697,7 +20724,7 @@
         <v>8851</v>
       </c>
       <c r="H6" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20706,7 +20733,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20718,7 +20745,7 @@
         <v>8852</v>
       </c>
       <c r="H7" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20727,7 +20754,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20751,10 +20778,10 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1654</v>
+        <v>1631</v>
       </c>
       <c r="I9" t="s">
-        <v>640</v>
+        <v>1632</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -20763,11 +20790,11 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1655</v>
+        <v>1633</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=10781,szNote="麒麟珠",col={255,50,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="麒麟珠·交互",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10781,szNote="麒麟珠",col={50,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="麒麟珠·交互",nMaxDistance=6,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -20778,7 +20805,7 @@
     </row>
     <row r="11" spans="1:22">
       <c r="U11" t="str">
-        <f t="shared" ref="U11" si="1">IF(ISBLANK(B11)=FALSE,IF(ISBLANK(B10),"},["&amp;B11&amp;"]={","["&amp;B11&amp;"]={"),IF(AND(ISBLANK(B11),ISBLANK(C11),OR(ISBLANK(B10)=FALSE,ISBLANK(C10)=FALSE)),"},},}",IF(ISBLANK(C11),"","{dwID="&amp;C11&amp;","&amp;IF(D11&gt;0,"nCount="&amp;D11&amp;",","")&amp;IF(E11&gt;0,"bAllLeave=true,","")&amp;IF(F11&lt;&gt;"","szName="""&amp;F11&amp;""",","")&amp;IF(G11&lt;&gt;"","tKungFu={"&amp;G11&amp;"},","")&amp;IF(H11&lt;&gt;"","szNote="""&amp;H11&amp;""",","")&amp;IF(I11&lt;&gt;"","col={"&amp;I11&amp;"},","")&amp;"[17]={"&amp;IF(J11&lt;&gt;"","szVoice="""&amp;J11&amp;""",","")&amp;IF(K11&gt;0,"bTeamChannel=true,","")&amp;IF(L11&gt;0,"bWhisperChannel=true,","")&amp;IF(M11&gt;0,"bCenterAlarm=true,","")&amp;IF(N11&gt;0,"bScreenHead=true,","")&amp;IF(O11&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P11&lt;&gt;"","szVoice="""&amp;P11&amp;""",","")&amp;IF(Q11&gt;0,"bTeamChannel=true,","")&amp;IF(R11&gt;0,"bWhisperChannel=true,","")&amp;IF(S11&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T11&lt;&gt;"","aFocus={"&amp;T11&amp;"},","")&amp;IF(V11&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V11:AAA11)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -20813,7 +20840,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20822,31 +20849,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="I1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="J1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="K1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="L1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="M1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="N1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="O1" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20854,7 +20881,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20866,38 +20893,38 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="E3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D4" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E4" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
@@ -20914,13 +20941,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D6" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="E6" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20933,18 +20960,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20957,7 +20984,7 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -20974,13 +21001,13 @@
     </row>
     <row r="9" customFormat="1" spans="1:16">
       <c r="C9" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D9" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="E9" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20993,18 +21020,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P9" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:16">
       <c r="C10" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D10" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E10" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -21017,7 +21044,7 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -21034,13 +21061,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D12" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="E12" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -21050,18 +21077,18 @@
         <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D13" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="E13" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -21071,18 +21098,18 @@
         <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D14" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="E14" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -21092,18 +21119,18 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="C15" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D15" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="E15" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -21113,42 +21140,42 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="D16" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P16" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="17" spans="3:16">
       <c r="D17" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P17" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D18" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="E18" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -21161,7 +21188,7 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P18" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="19" spans="3:16">
@@ -21197,7 +21224,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21206,31 +21233,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="G1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="I1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="J1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="K1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="L1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="M1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="N1" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21250,46 +21277,46 @@
     </row>
     <row r="3" spans="1:15">
       <c r="C3" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="C5" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="C6" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="D6" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -21299,63 +21326,63 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25111,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O7" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="C8" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="C9" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="C10" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="C11" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="D11" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -21365,27 +21392,27 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="C12" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25109,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D13" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21395,15 +21422,15 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D14" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21413,15 +21440,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="D15" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -21431,15 +21458,15 @@
         <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="D16" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21449,36 +21476,36 @@
         <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -21488,27 +21515,27 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="C21" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="D21" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="E21" t="s">
         <v>582</v>
@@ -21524,15 +21551,15 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="D22" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="E22" t="s">
         <v>582</v>
@@ -21547,80 +21574,80 @@
     </row>
     <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="P23" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="P24" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="Q24" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="R24" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="P25" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="Q25" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="R25" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="P26" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="Q26" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="R26" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:18">
@@ -21637,10 +21664,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:18">
       <c r="C28" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="D28" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -21650,15 +21677,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="D29" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21668,22 +21695,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="C30" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="D30" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -21700,10 +21727,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="D32" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21713,15 +21740,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="3:15">
       <c r="C33" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="D33" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21731,22 +21758,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="3:15">
       <c r="C34" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="D34" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="35" spans="3:15">

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="1830">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4702,6 +4702,9 @@
   </si>
   <si>
     <t>消极参战</t>
+  </si>
+  <si>
+    <t>逃</t>
   </si>
   <si>
     <t>门派的数据</t>
@@ -6761,7 +6764,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1788502790000,</v>
+        <v>nTimeStamp = 1788703819000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8687,7 +8690,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8700,13 +8703,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C2" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8715,13 +8718,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B3" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C3" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8730,13 +8733,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B4" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C4" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8745,13 +8748,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B5" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C5" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8760,7 +8763,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8769,13 +8772,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B7" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C7" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8784,13 +8787,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B8" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C8" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8799,13 +8802,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B9" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C9" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8814,13 +8817,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B10" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C10" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8829,13 +8832,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B11" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C11" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8844,7 +8847,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8853,10 +8856,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C13" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8865,10 +8868,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="C14" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8877,10 +8880,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C15" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8889,10 +8892,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C16" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8901,10 +8904,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C17" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8913,7 +8916,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8922,7 +8925,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8931,7 +8934,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8940,7 +8943,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8949,7 +8952,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8982,7 +8985,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -8999,7 +9002,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -9013,7 +9016,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9027,7 +9030,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9047,7 +9050,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9066,7 +9069,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9077,7 +9080,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9088,7 +9091,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9104,7 +9107,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9119,7 +9122,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9130,7 +9133,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9141,7 +9144,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9157,7 +9160,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9172,7 +9175,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9183,7 +9186,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9194,7 +9197,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9210,7 +9213,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9225,7 +9228,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9236,7 +9239,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9247,7 +9250,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9263,7 +9266,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9278,7 +9281,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9289,7 +9292,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9300,7 +9303,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9316,7 +9319,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9331,7 +9334,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9342,7 +9345,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9353,7 +9356,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9369,7 +9372,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9384,7 +9387,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9395,7 +9398,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9406,7 +9409,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9422,7 +9425,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9437,7 +9440,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9448,7 +9451,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9459,7 +9462,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9475,7 +9478,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9490,7 +9493,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9501,7 +9504,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9512,7 +9515,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9528,7 +9531,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9543,7 +9546,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9554,7 +9557,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9565,7 +9568,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9581,7 +9584,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9596,7 +9599,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9607,7 +9610,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9618,7 +9621,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9634,7 +9637,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9649,7 +9652,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9660,7 +9663,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9671,7 +9674,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9687,7 +9690,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9702,7 +9705,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9713,7 +9716,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9724,7 +9727,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9740,7 +9743,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9755,7 +9758,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9766,7 +9769,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9777,7 +9780,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9793,7 +9796,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9808,7 +9811,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9819,7 +9822,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9830,7 +9833,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9846,7 +9849,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9861,7 +9864,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9872,7 +9875,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9883,7 +9886,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9899,7 +9902,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9914,7 +9917,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9925,7 +9928,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9936,7 +9939,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9952,7 +9955,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9967,7 +9970,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9978,7 +9981,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9989,7 +9992,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -10005,7 +10008,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10020,7 +10023,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10031,7 +10034,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10042,7 +10045,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10058,7 +10061,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10073,7 +10076,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10084,7 +10087,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10095,7 +10098,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10111,7 +10114,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10126,7 +10129,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10137,7 +10140,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10148,7 +10151,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10164,7 +10167,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10179,7 +10182,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10190,7 +10193,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10201,7 +10204,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10217,7 +10220,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10232,7 +10235,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10243,7 +10246,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10254,7 +10257,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10270,7 +10273,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10284,7 +10287,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10294,7 +10297,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10304,7 +10307,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10320,7 +10323,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10340,7 +10343,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10360,7 +10363,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10380,7 +10383,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10400,7 +10403,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10420,7 +10423,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10440,7 +10443,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10460,7 +10463,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10480,7 +10483,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10500,7 +10503,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10520,7 +10523,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10540,7 +10543,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10560,7 +10563,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10580,7 +10583,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10600,7 +10603,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10620,7 +10623,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10640,7 +10643,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10660,7 +10663,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10680,7 +10683,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10700,7 +10703,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10720,7 +10723,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10740,7 +10743,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10760,7 +10763,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10780,7 +10783,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10800,7 +10803,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10820,7 +10823,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10840,7 +10843,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10860,7 +10863,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10880,7 +10883,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10900,7 +10903,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10920,7 +10923,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10940,7 +10943,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10960,7 +10963,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10980,7 +10983,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -11000,7 +11003,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -19694,14 +19697,20 @@
       <c r="W9">
         <v>1</v>
       </c>
+      <c r="AH9" t="s">
+        <v>1551</v>
+      </c>
+      <c r="AI9">
+        <v>43</v>
+      </c>
       <c r="AQ9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=18913,nLevel=1,nScrutinyType=2,szNote="消极参战",[1]={bBuffList=true,bTeamPanel=true,},[2]={},},</v>
+        <v>{dwID=18913,nLevel=1,nScrutinyType=2,szNote="消极参战",[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="逃",nPriority=43,},},},</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:45">
       <c r="A10" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B10">
         <v>-21</v>
@@ -19730,9 +19739,15 @@
       <c r="W11">
         <v>1</v>
       </c>
+      <c r="AH11" t="s">
+        <v>1551</v>
+      </c>
+      <c r="AI11">
+        <v>43</v>
+      </c>
       <c r="AQ11" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=18913,nLevel=1,nScrutinyType=2,szNote="消极参战",[1]={bBuffList=true,bTeamPanel=true,},[2]={},},</v>
+        <v>{dwID=18913,nLevel=1,nScrutinyType=2,szNote="消极参战",[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="逃",nPriority=43,},},},</v>
       </c>
     </row>
     <row r="12" spans="1:45">
@@ -19789,43 +19804,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="M1" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="N1" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="O1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="P1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="Q1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="R1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="S1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="T1" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="U1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="V1" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="W1" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="X1" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>
@@ -19851,14 +19866,14 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="X3" t="str">
         <f>IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(D3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(D2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nIcon="&amp;E3&amp;",","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H3&gt;0,"nScrutinyType="&amp;H3&amp;",","")&amp;IF(I3&lt;&gt;"","tKungFu={"&amp;I3&amp;"},","")&amp;IF(J3&lt;&gt;"","szNote="""&amp;J3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;"[9]={"&amp;IF(L3&lt;&gt;"","tMark={"&amp;L3&amp;"},","")&amp;IF(M3&lt;&gt;"","szVoice="""&amp;M3&amp;""",","")&amp;IF(N3&gt;0,"bTeamChannel=true,","")&amp;IF(O3&gt;0,"bWhisperChannel=true,","")&amp;IF(P3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q3&lt;&gt;"","tMark={"&amp;Q3&amp;"},","")&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;IF(V3&gt;0,"bScreenHead=true,","")&amp;IF(W3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y3:AAC3)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38265,nLevel=1,szNote="扫尾",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime=3,szName="九渊麒麟·扫尾",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y3" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -19869,14 +19884,14 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="X4" t="str">
         <f>IF(ISBLANK(B4)=FALSE,IF(ISBLANK(B3),"},["&amp;B4&amp;"]={","["&amp;B4&amp;"]={"),IF(AND(ISBLANK(B4),ISBLANK(C4),ISBLANK(D4),OR(ISBLANK(B3)=FALSE,ISBLANK(C3)=FALSE,ISBLANK(D3)=FALSE)),"},},}",IF(ISBLANK(C4),"","{dwID="&amp;C4&amp;","&amp;"nLevel="&amp;D4&amp;","&amp;IF(E4&gt;0,"nIcon="&amp;E4&amp;",","")&amp;IF(F4&lt;&gt;"","szName="""&amp;F4&amp;""",","")&amp;IF(G4&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H4&gt;0,"nScrutinyType="&amp;H4&amp;",","")&amp;IF(I4&lt;&gt;"","tKungFu={"&amp;I4&amp;"},","")&amp;IF(J4&lt;&gt;"","szNote="""&amp;J4&amp;""",","")&amp;IF(K4&lt;&gt;"","col={"&amp;K4&amp;"},","")&amp;"[9]={"&amp;IF(L4&lt;&gt;"","tMark={"&amp;L4&amp;"},","")&amp;IF(M4&lt;&gt;"","szVoice="""&amp;M4&amp;""",","")&amp;IF(N4&gt;0,"bTeamChannel=true,","")&amp;IF(O4&gt;0,"bWhisperChannel=true,","")&amp;IF(P4&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q4&lt;&gt;"","tMark={"&amp;Q4&amp;"},","")&amp;IF(R4&lt;&gt;"","szVoice="""&amp;R4&amp;""",","")&amp;IF(S4&gt;0,"bTeamChannel=true,","")&amp;IF(T4&gt;0,"bWhisperChannel=true,","")&amp;IF(U4&gt;0,"bCenterAlarm=true,","")&amp;IF(V4&gt;0,"bScreenHead=true,","")&amp;IF(W4&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y4&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y4:AAC4)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38263,nLevel=1,szNote="渊迴龙吟",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="8,狂风吐息·旋转扫射;30,渊迴龙吟·躲面向",szName="九渊麒麟·技能",nRefresh=4,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y4" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -19887,14 +19902,14 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="X5" t="str">
         <f>IF(ISBLANK(B5)=FALSE,IF(ISBLANK(B4),"},["&amp;B5&amp;"]={","["&amp;B5&amp;"]={"),IF(AND(ISBLANK(B5),ISBLANK(C5),ISBLANK(D5),OR(ISBLANK(B4)=FALSE,ISBLANK(C4)=FALSE,ISBLANK(D4)=FALSE)),"},},}",IF(ISBLANK(C5),"","{dwID="&amp;C5&amp;","&amp;"nLevel="&amp;D5&amp;","&amp;IF(E5&gt;0,"nIcon="&amp;E5&amp;",","")&amp;IF(F5&lt;&gt;"","szName="""&amp;F5&amp;""",","")&amp;IF(G5&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H5&gt;0,"nScrutinyType="&amp;H5&amp;",","")&amp;IF(I5&lt;&gt;"","tKungFu={"&amp;I5&amp;"},","")&amp;IF(J5&lt;&gt;"","szNote="""&amp;J5&amp;""",","")&amp;IF(K5&lt;&gt;"","col={"&amp;K5&amp;"},","")&amp;"[9]={"&amp;IF(L5&lt;&gt;"","tMark={"&amp;L5&amp;"},","")&amp;IF(M5&lt;&gt;"","szVoice="""&amp;M5&amp;""",","")&amp;IF(N5&gt;0,"bTeamChannel=true,","")&amp;IF(O5&gt;0,"bWhisperChannel=true,","")&amp;IF(P5&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q5&lt;&gt;"","tMark={"&amp;Q5&amp;"},","")&amp;IF(R5&lt;&gt;"","szVoice="""&amp;R5&amp;""",","")&amp;IF(S5&gt;0,"bTeamChannel=true,","")&amp;IF(T5&gt;0,"bWhisperChannel=true,","")&amp;IF(U5&gt;0,"bCenterAlarm=true,","")&amp;IF(V5&gt;0,"bScreenHead=true,","")&amp;IF(W5&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Y5&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Y5:AAC5)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=38264,nLevel=1,szNote="狂风吐息",[9]={},[8]={},tCountdown={{nClass=8,nIcon=13,nFrame=5,nTime="22,渊迴龙吟·躲面向;30,狂风吐息·旋转扫射",szName="九渊麒麟·技能",nRefresh=11,key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="Y5" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -19933,10 +19948,10 @@
         <v>1479</v>
       </c>
       <c r="E1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G1" t="s">
         <v>1480</v>
@@ -19951,43 +19966,43 @@
         <v>1484</v>
       </c>
       <c r="K1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="L1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="M1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="N1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="O1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="P1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="Q1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="R1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="S1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="T1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="U1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="V1" t="s">
         <v>296</v>
       </c>
       <c r="W1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="X1" t="s">
         <v>316</v>
@@ -20013,7 +20028,7 @@
         <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="J3" t="s">
         <v>613</v>
@@ -20022,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W28" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nFrame="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"bAllLeave=true,","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&lt;&gt;"","tKungFu={"&amp;H3&amp;"},","")&amp;IF(I3&lt;&gt;"","szNote="""&amp;I3&amp;""",","")&amp;IF(J3&lt;&gt;"","col={"&amp;J3&amp;"},","")&amp;"[3]={"&amp;IF(K3&lt;&gt;"","tMark={"&amp;K3&amp;"},","")&amp;IF(L3&lt;&gt;"","szVoice="""&amp;L3&amp;""",","")&amp;IF(M3&gt;0,"bTeamChannel=true,","")&amp;IF(N3&gt;0,"bWhisperChannel=true,","")&amp;IF(O3&gt;0,"bCenterAlarm=true,","")&amp;IF(P3&gt;0,"bScreenHead=true,","")&amp;IF(Q3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V3&lt;&gt;"","aFocus={"&amp;V3&amp;"},","")&amp;IF(X3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20031,7 +20046,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B4">
         <v>-21</v>
@@ -20049,7 +20064,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="J5" t="s">
         <v>613</v>
@@ -20058,7 +20073,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="0"/>
@@ -20085,10 +20100,10 @@
         <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="V7" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="0"/>
@@ -20103,16 +20118,16 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="J8" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
@@ -20127,10 +20142,10 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="V9" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
@@ -20145,10 +20160,10 @@
         <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="V10" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
@@ -20163,7 +20178,7 @@
         <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="J11" t="s">
         <v>582</v>
@@ -20172,7 +20187,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="0"/>
@@ -20187,7 +20202,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="J12" t="s">
         <v>582</v>
@@ -20196,7 +20211,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -20211,7 +20226,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="J13" t="s">
         <v>582</v>
@@ -20220,7 +20235,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -20235,7 +20250,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J14" t="s">
         <v>582</v>
@@ -20244,7 +20259,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
@@ -20259,7 +20274,7 @@
         <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="J15" t="s">
         <v>640</v>
@@ -20268,17 +20283,17 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128557,nFrame=57,szNote="红方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,红方·古猿·刷新剩余;95,红方·古猿·即将刷新",szName="红方古猿·刷新剩余",nRefresh=2,key="红方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X15" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="Y15" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -20289,7 +20304,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="J16" t="s">
         <v>640</v>
@@ -20298,14 +20313,14 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128556,nFrame=57,szNote="红方·混沌元晶·洞",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="红方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,红方·混沌元晶·刷新剩余;65,红方·混沌元晶·即将刷新",szName="红方·混沌元晶·刷新剩余",nRefresh=0,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="X16" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="3:25">
@@ -20316,10 +20331,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="V17" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
@@ -20334,7 +20349,7 @@
         <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J18" t="s">
         <v>582</v>
@@ -20343,7 +20358,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="0"/>
@@ -20358,7 +20373,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="J19" t="s">
         <v>582</v>
@@ -20367,7 +20382,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -20382,7 +20397,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="J20" t="s">
         <v>582</v>
@@ -20391,7 +20406,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="0"/>
@@ -20406,7 +20421,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="J21" t="s">
         <v>582</v>
@@ -20415,7 +20430,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -20430,7 +20445,7 @@
         <v>57</v>
       </c>
       <c r="I22" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="J22" t="s">
         <v>640</v>
@@ -20439,17 +20454,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128559,nFrame=57,szNote="蓝方·古猿",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·古猿·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·古猿",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2671,nFrame=4,nTime="90,蓝方·古猿·刷新剩余;95,蓝方·古猿·即将刷新",szName="蓝方古猿·刷新剩余",nRefresh=2,key="蓝方·古猿",},{nClass=12,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=2,key="通用·古猿",},},},</v>
       </c>
       <c r="X22" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="Y22" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="23" spans="3:25">
@@ -20460,7 +20475,7 @@
         <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="J23" t="s">
         <v>640</v>
@@ -20469,14 +20484,14 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128558,nFrame=57,szNote="蓝方·混沌元晶·皓",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="蓝方·元晶·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="蓝方·元晶",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2672,nFrame=4,nTime="60,蓝方·混沌元晶·刷新剩余;65,蓝方·混沌元晶·即将刷新",szName="蓝方·混沌元晶·刷新剩余",nRefresh=0,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="X23" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="24" spans="3:25">
@@ -20487,7 +20502,7 @@
         <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="J24" t="s">
         <v>640</v>
@@ -20496,17 +20511,17 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=128576,nFrame=57,szNote="九渊麒麟",col={255,50,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九渊麒麟·15尺",nMaxDistance=15,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},{nClass=4,nIcon=13,nTime=0,szName="九渊麒麟·技能",key="九渊麒麟·技能",},},},</v>
       </c>
       <c r="X24" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="Y24" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="25" spans="3:25">
@@ -20517,16 +20532,16 @@
         <v>47</v>
       </c>
       <c r="I25" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="J25" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="P25">
         <v>1</v>
       </c>
       <c r="V25" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
@@ -20541,10 +20556,10 @@
         <v>52</v>
       </c>
       <c r="I26" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="V26" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="W26" t="str">
         <f t="shared" si="0"/>
@@ -20587,10 +20602,10 @@
         <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F1" t="s">
         <v>1480</v>
@@ -20605,40 +20620,40 @@
         <v>1484</v>
       </c>
       <c r="J1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="K1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="L1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="M1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="N1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="O1" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="P1" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="Q1" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="R1" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="S1" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="T1" t="s">
         <v>296</v>
       </c>
       <c r="U1" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="V1" t="s">
         <v>316</v>
@@ -20661,7 +20676,7 @@
         <v>8848</v>
       </c>
       <c r="H3" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="I3" t="s">
         <v>622</v>
@@ -20670,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U11" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;IF(D3&gt;0,"nCount="&amp;D3&amp;",","")&amp;IF(E3&gt;0,"bAllLeave=true,","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&lt;&gt;"","tKungFu={"&amp;G3&amp;"},","")&amp;IF(H3&lt;&gt;"","szNote="""&amp;H3&amp;""",","")&amp;IF(I3&lt;&gt;"","col={"&amp;I3&amp;"},","")&amp;"[17]={"&amp;IF(J3&lt;&gt;"","szVoice="""&amp;J3&amp;""",","")&amp;IF(K3&gt;0,"bTeamChannel=true,","")&amp;IF(L3&gt;0,"bWhisperChannel=true,","")&amp;IF(M3&gt;0,"bCenterAlarm=true,","")&amp;IF(N3&gt;0,"bScreenHead=true,","")&amp;IF(O3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P3&lt;&gt;"","szVoice="""&amp;P3&amp;""",","")&amp;IF(Q3&gt;0,"bTeamChannel=true,","")&amp;IF(R3&gt;0,"bWhisperChannel=true,","")&amp;IF(S3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T3&lt;&gt;"","aFocus={"&amp;T3&amp;"},","")&amp;IF(V3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V3:AAA3)&amp;"},","")&amp;"},")))</f>
@@ -20682,7 +20697,7 @@
         <v>8849</v>
       </c>
       <c r="H4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="I4" t="s">
         <v>622</v>
@@ -20691,7 +20706,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
@@ -20703,7 +20718,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="I5" t="s">
         <v>622</v>
@@ -20712,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -20724,7 +20739,7 @@
         <v>8851</v>
       </c>
       <c r="H6" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="I6" t="s">
         <v>622</v>
@@ -20733,7 +20748,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20745,7 +20760,7 @@
         <v>8852</v>
       </c>
       <c r="H7" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="I7" t="s">
         <v>622</v>
@@ -20754,7 +20769,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -20778,10 +20793,10 @@
         <v>10781</v>
       </c>
       <c r="H9" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="I9" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -20790,7 +20805,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -20840,7 +20855,7 @@
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
@@ -20849,31 +20864,31 @@
         <v>1484</v>
       </c>
       <c r="G1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="I1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="J1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="K1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="L1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="M1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="N1" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="O1" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="P1" t="s">
         <v>316</v>
@@ -20881,7 +20896,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -20893,38 +20908,38 @@
     </row>
     <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="E3" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O19" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(G3),ISBLANK(H3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(G2)=FALSE,ISBLANK(H2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(F3&lt;&gt;"","col={"&amp;F3&amp;"},","")&amp;IF(G3&gt;0,"bSearch=true,","")&amp;IF(H3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(I3&gt;0,"szVoice="""&amp;I3&amp;""",","")&amp;IF(J3&gt;0,"bTeamChannel=true,","")&amp;IF(K3&gt;0,"bWhisperChannel=true,","")&amp;IF(L3&gt;0,"bCenterAlarm=true,","")&amp;IF(M3&gt;0,"bScreenHead=true,","")&amp;IF(N3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(P3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,P3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[帮会总管]邵卿城：诸位兄弟，愿此行战无不胜，扬我帮威！",szTarget="%",szNote="武林争霸赛·已经报名",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·已经报名",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D4" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="E4" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="【武林争霸赛】本届武林争霸赛正式已开启！风起云涌，一朝闻名天下知！已报名的帮会侠士，可前往各大主城或各门派，闻千瞬处对话进入参与对决！！！帮会帮主及核心成员优先进入，以免造成不便！！！",szTarget="%",szNote="武林争霸赛·正式开启",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="武林争霸赛·正式开启",nRefresh=1,key="武林争霸赛",},},},</v>
       </c>
       <c r="P4" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:16">
@@ -20941,13 +20956,13 @@
     </row>
     <row r="6" customFormat="1" spans="1:16">
       <c r="C6" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D6" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="E6" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20960,18 +20975,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P6" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:16">
       <c r="C7" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E7" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20984,12 +20999,12 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P7" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B8">
         <v>-21</v>
@@ -21001,13 +21016,13 @@
     </row>
     <row r="9" customFormat="1" spans="1:16">
       <c r="C9" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D9" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="E9" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -21020,18 +21035,18 @@
         <v>{szContent="^报名成功：【(.-)】已报名本届《(.-)》【(.-)】场次(.-)！！！",szTarget="%",szNote="[{$1}]·{$4}报名·《{$2}·{$3}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,nTime=30,szName="报名·{$2}·{$3}",nRefresh=2,key="武林争霸赛",},},},</v>
       </c>
       <c r="P9" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:16">
       <c r="C10" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D10" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E10" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -21044,7 +21059,7 @@
         <v>{szContent="^取消报名：【(.-)】已取消武林争霸赛【(.-)】场次的报名！！！请检查在线人数，抓紧时间再次报名！！！",szTarget="%",szNote="[{$1}]·取消报名·《武林争霸赛·{$2}》",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,nTime="30,取消报名·武林争霸赛·{$2};40,注意·重新报名·武林争霸赛",szName="取消报名·武林争霸赛·{$2}",nRefresh=0,key="武林争霸赛",},},},</v>
       </c>
       <c r="P10" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -21061,13 +21076,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D12" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="E12" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -21077,18 +21092,18 @@
         <v>{szContent="敌方拾取麒麟珠\n",szTarget="%",szNote="敌方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P12" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D13" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="E13" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -21098,18 +21113,18 @@
         <v>{szContent="我方拾取麒麟珠\n",szTarget="%",szNote="我方·获得·麒麟珠",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P13" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D14" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="E14" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -21119,18 +21134,18 @@
         <v>{szContent="蓝方成功击败了九渊麒麟",szTarget="%",szNote="蓝方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P14" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="C15" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D15" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="E15" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -21140,42 +21155,42 @@
         <v>{szContent="红方成功击败了九渊麒麟",szTarget="%",szNote="红方·击伤·九渊麒麟",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="P15" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="D16" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗已被摧毁，本场比赛结束！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·失利",key="战斗开始",},},},</v>
       </c>
       <c r="P16" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="17" spans="3:16">
       <c r="D17" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="成功摧毁敌方大旗，您获得本场比赛胜利！",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,nTime=30,szName="本场比赛·胜利",key="战斗开始",},},},</v>
       </c>
       <c r="P17" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D18" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="E18" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -21188,7 +21203,7 @@
         <v>{szContent="我方第(%d-)次鼓舞士气成功！",szTarget="%",szNote="鼓舞士气·{$1}次",bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,nTime=10,szName="我方·鼓舞士气·{$1}次",key="鼓舞士气",},},},</v>
       </c>
       <c r="P18" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="19" spans="3:16">
@@ -21224,7 +21239,7 @@
         <v>1477</v>
       </c>
       <c r="C1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -21233,31 +21248,31 @@
         <v>1484</v>
       </c>
       <c r="F1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="G1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="I1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="J1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="K1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="L1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="M1" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="N1" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="O1" t="s">
         <v>316</v>
@@ -21277,46 +21292,46 @@
     </row>
     <row r="3" spans="1:15">
       <c r="C3" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O4" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="C5" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O5" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="C6" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="D6" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -21326,63 +21341,63 @@
         <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25111,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O7" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="C8" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O8" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="C9" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O9" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="C10" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O10" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="C11" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D11" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -21392,27 +21407,27 @@
         <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O11" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="C12" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25109,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="D13" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -21422,15 +21437,15 @@
         <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O13" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D14" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -21440,15 +21455,15 @@
         <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D15" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -21458,15 +21473,15 @@
         <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="D16" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -21476,36 +21491,36 @@
         <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -21515,27 +21530,27 @@
         <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="C21" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D21" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E21" t="s">
         <v>582</v>
@@ -21551,15 +21566,15 @@
         <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="D22" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="E22" t="s">
         <v>582</v>
@@ -21574,80 +21589,80 @@
     </row>
     <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="P23" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="P24" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="Q24" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="R24" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="P25" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="Q25" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="R25" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O26" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="P26" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="Q26" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="R26" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:18">
@@ -21664,10 +21679,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:18">
       <c r="C28" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D28" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -21677,15 +21692,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D29" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -21695,27 +21710,27 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="C30" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="D30" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B31">
         <v>-21</v>
@@ -21727,10 +21742,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D32" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21740,15 +21755,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="3:15">
       <c r="C33" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D33" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21758,22 +21773,22 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="3:15">
       <c r="C34" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="D34" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="35" spans="3:15">
